--- a/outputs/daily/hr_rankings_2026-08-09_remaining.xlsx
+++ b/outputs/daily/hr_rankings_2026-08-09_remaining.xlsx
@@ -784,7 +784,7 @@
         </is>
       </c>
       <c r="L2" t="n">
-        <v>73.40000000000001</v>
+        <v>74</v>
       </c>
       <c r="M2" t="inlineStr">
         <is>
@@ -798,7 +798,7 @@
       </c>
       <c r="O2" t="inlineStr">
         <is>
-          <t>Projected Lineup, Elite Power, Strong Barrel, Premium Lineup Spot, Platoon Edge</t>
+          <t>Elite Power, Strong Barrel, Premium Lineup Spot, Platoon Edge</t>
         </is>
       </c>
       <c r="P2" t="n">
@@ -811,7 +811,7 @@
         <v>58.1</v>
       </c>
       <c r="S2" t="n">
-        <v>95.5</v>
+        <v>100</v>
       </c>
       <c r="T2" t="n">
         <v>80</v>
@@ -821,39 +821,35 @@
       </c>
       <c r="V2" t="inlineStr">
         <is>
+          <t>Yes</t>
+        </is>
+      </c>
+      <c r="W2" t="inlineStr">
+        <is>
+          <t>Yes</t>
+        </is>
+      </c>
+      <c r="X2" t="inlineStr">
+        <is>
+          <t>2</t>
+        </is>
+      </c>
+      <c r="Y2" t="inlineStr">
+        <is>
+          <t>Yes</t>
+        </is>
+      </c>
+      <c r="Z2" t="inlineStr">
+        <is>
           <t>No</t>
         </is>
       </c>
-      <c r="W2" t="inlineStr">
-        <is>
-          <t>No</t>
-        </is>
-      </c>
-      <c r="X2" t="inlineStr">
-        <is>
-          <t>2</t>
-        </is>
-      </c>
-      <c r="Y2" t="inlineStr">
-        <is>
-          <t>Yes</t>
-        </is>
-      </c>
-      <c r="Z2" t="inlineStr">
-        <is>
-          <t>Yes</t>
-        </is>
-      </c>
       <c r="AA2" t="inlineStr">
         <is>
-          <t>RotoWire projected lineup; MLB probable pitchers</t>
-        </is>
-      </c>
-      <c r="AB2" t="inlineStr">
-        <is>
-          <t>lineup projected / unconfirmed</t>
-        </is>
-      </c>
+          <t>MLB Stats API; RotoWire</t>
+        </is>
+      </c>
+      <c r="AB2" t="inlineStr"/>
       <c r="AC2" t="inlineStr">
         <is>
           <t>H:2026/2025 P:2026/2025</t>
@@ -1019,24 +1015,24 @@
       </c>
       <c r="B3" t="inlineStr">
         <is>
-          <t>701538</t>
+          <t>666211</t>
         </is>
       </c>
       <c r="C3" t="inlineStr">
         <is>
-          <t>Jackson Merrill</t>
+          <t>Taylor Trammell</t>
         </is>
       </c>
       <c r="D3" t="inlineStr">
         <is>
+          <t>HOU</t>
+        </is>
+      </c>
+      <c r="E3" t="inlineStr">
+        <is>
           <t>SD</t>
         </is>
       </c>
-      <c r="E3" t="inlineStr">
-        <is>
-          <t>HOU</t>
-        </is>
-      </c>
       <c r="F3" t="inlineStr">
         <is>
           <t>2026-08-10T00:20:00Z</t>
@@ -1054,12 +1050,12 @@
       </c>
       <c r="I3" t="inlineStr">
         <is>
-          <t>Cristian Javier</t>
+          <t>Randy Vásquez</t>
         </is>
       </c>
       <c r="J3" t="inlineStr">
         <is>
-          <t>664299</t>
+          <t>681190</t>
         </is>
       </c>
       <c r="K3" t="inlineStr">
@@ -1068,7 +1064,7 @@
         </is>
       </c>
       <c r="L3" t="n">
-        <v>56.9</v>
+        <v>59</v>
       </c>
       <c r="M3" t="inlineStr">
         <is>
@@ -1082,14 +1078,14 @@
       </c>
       <c r="O3" t="inlineStr">
         <is>
-          <t>Strong Barrel, Platoon Edge, Hot Hitter/Streak</t>
+          <t>Strong Barrel, Platoon Edge</t>
         </is>
       </c>
       <c r="P3" t="n">
-        <v>48.3</v>
+        <v>40.5</v>
       </c>
       <c r="Q3" t="n">
-        <v>39</v>
+        <v>62.7</v>
       </c>
       <c r="R3" t="n">
         <v>58.1</v>
@@ -1101,7 +1097,7 @@
         <v>80</v>
       </c>
       <c r="U3" t="n">
-        <v>72.2</v>
+        <v>51.3</v>
       </c>
       <c r="V3" t="inlineStr">
         <is>
@@ -1153,12 +1149,12 @@
       </c>
       <c r="AH3" t="inlineStr">
         <is>
-          <t>10</t>
+          <t>5</t>
         </is>
       </c>
       <c r="AI3" t="inlineStr">
         <is>
-          <t>28</t>
+          <t>23</t>
         </is>
       </c>
       <c r="AJ3" t="inlineStr">
@@ -1173,107 +1169,107 @@
       </c>
       <c r="AL3" t="inlineStr">
         <is>
-          <t>platoon edge; pitcher baseline 7.7% barrel, 3.7 HR allowed</t>
+          <t>platoon edge; pitcher baseline 11.0% barrel, 14.6 HR allowed</t>
         </is>
       </c>
       <c r="AM3" t="inlineStr">
         <is>
-          <t>neutral batted-ball profile; pitcher allows elevated contact</t>
+          <t>neutral batted-ball profile; pitcher fly-ball pressure modest</t>
         </is>
       </c>
       <c r="AN3" t="inlineStr">
         <is>
-          <t>11.46</t>
+          <t>11.02</t>
         </is>
       </c>
       <c r="AO3" t="inlineStr">
         <is>
-          <t>45.35</t>
+          <t>36.73</t>
         </is>
       </c>
       <c r="AP3" t="inlineStr">
         <is>
-          <t>89.98</t>
+          <t>89.11</t>
         </is>
       </c>
       <c r="AQ3" t="inlineStr">
         <is>
-          <t>100.5329</t>
+          <t>100.7812</t>
         </is>
       </c>
       <c r="AR3" t="inlineStr">
         <is>
-          <t>0.4627</t>
+          <t>0.3854</t>
         </is>
       </c>
       <c r="AS3" t="inlineStr">
         <is>
-          <t>0.2053</t>
+          <t>0.1809</t>
         </is>
       </c>
       <c r="AT3" t="inlineStr">
         <is>
-          <t>0.3309</t>
+          <t>0.3025</t>
         </is>
       </c>
       <c r="AU3" t="inlineStr">
         <is>
-          <t>72.88</t>
+          <t>75.44</t>
         </is>
       </c>
       <c r="AV3" t="inlineStr">
         <is>
-          <t>26.98</t>
+          <t>55.07</t>
         </is>
       </c>
       <c r="AW3" t="inlineStr">
         <is>
-          <t>37.91</t>
+          <t>46.19</t>
         </is>
       </c>
       <c r="AX3" t="inlineStr">
         <is>
-          <t>28.94</t>
+          <t>30.09</t>
         </is>
       </c>
       <c r="AY3" t="inlineStr">
         <is>
-          <t>16.7</t>
+          <t>5.8</t>
         </is>
       </c>
       <c r="AZ3" t="inlineStr">
         <is>
-          <t>0.172</t>
+          <t>0.1696</t>
         </is>
       </c>
       <c r="BA3" t="inlineStr">
         <is>
-          <t>7.69</t>
+          <t>11.04</t>
         </is>
       </c>
       <c r="BB3" t="inlineStr">
         <is>
-          <t>37.81</t>
+          <t>43.01</t>
         </is>
       </c>
       <c r="BC3" t="inlineStr">
         <is>
-          <t>89.39</t>
+          <t>90.71</t>
         </is>
       </c>
       <c r="BD3" t="inlineStr">
         <is>
-          <t>0.3942</t>
+          <t>0.5055</t>
         </is>
       </c>
       <c r="BE3" t="inlineStr">
         <is>
-          <t>0.1474</t>
+          <t>0.2189</t>
         </is>
       </c>
       <c r="BF3" t="inlineStr">
         <is>
-          <t>37.54</t>
+          <t>29.3</t>
         </is>
       </c>
       <c r="BG3" t="inlineStr">
@@ -1299,24 +1295,24 @@
       </c>
       <c r="B4" t="inlineStr">
         <is>
-          <t>572233</t>
+          <t>701538</t>
         </is>
       </c>
       <c r="C4" t="inlineStr">
         <is>
-          <t>Christian Walker</t>
+          <t>Jackson Merrill</t>
         </is>
       </c>
       <c r="D4" t="inlineStr">
         <is>
+          <t>SD</t>
+        </is>
+      </c>
+      <c r="E4" t="inlineStr">
+        <is>
           <t>HOU</t>
         </is>
       </c>
-      <c r="E4" t="inlineStr">
-        <is>
-          <t>SD</t>
-        </is>
-      </c>
       <c r="F4" t="inlineStr">
         <is>
           <t>2026-08-10T00:20:00Z</t>
@@ -1334,12 +1330,12 @@
       </c>
       <c r="I4" t="inlineStr">
         <is>
-          <t>Randy Vásquez</t>
+          <t>Cristian Javier</t>
         </is>
       </c>
       <c r="J4" t="inlineStr">
         <is>
-          <t>681190</t>
+          <t>664299</t>
         </is>
       </c>
       <c r="K4" t="inlineStr">
@@ -1348,7 +1344,7 @@
         </is>
       </c>
       <c r="L4" t="n">
-        <v>55.6</v>
+        <v>56.9</v>
       </c>
       <c r="M4" t="inlineStr">
         <is>
@@ -1362,62 +1358,58 @@
       </c>
       <c r="O4" t="inlineStr">
         <is>
-          <t>Projected Lineup, Strong Barrel</t>
+          <t>Strong Barrel, Platoon Edge, Hot Hitter/Streak</t>
         </is>
       </c>
       <c r="P4" t="n">
-        <v>42.9</v>
+        <v>48.3</v>
       </c>
       <c r="Q4" t="n">
-        <v>62.7</v>
+        <v>39</v>
       </c>
       <c r="R4" t="n">
         <v>58.1</v>
       </c>
       <c r="S4" t="n">
-        <v>81.90000000000001</v>
+        <v>86.40000000000001</v>
       </c>
       <c r="T4" t="n">
-        <v>50</v>
+        <v>80</v>
       </c>
       <c r="U4" t="n">
-        <v>33.9</v>
+        <v>72.2</v>
       </c>
       <c r="V4" t="inlineStr">
         <is>
+          <t>Yes</t>
+        </is>
+      </c>
+      <c r="W4" t="inlineStr">
+        <is>
+          <t>Yes</t>
+        </is>
+      </c>
+      <c r="X4" t="inlineStr">
+        <is>
+          <t>5</t>
+        </is>
+      </c>
+      <c r="Y4" t="inlineStr">
+        <is>
+          <t>Yes</t>
+        </is>
+      </c>
+      <c r="Z4" t="inlineStr">
+        <is>
           <t>No</t>
         </is>
       </c>
-      <c r="W4" t="inlineStr">
-        <is>
-          <t>No</t>
-        </is>
-      </c>
-      <c r="X4" t="inlineStr">
-        <is>
-          <t>5</t>
-        </is>
-      </c>
-      <c r="Y4" t="inlineStr">
-        <is>
-          <t>Yes</t>
-        </is>
-      </c>
-      <c r="Z4" t="inlineStr">
-        <is>
-          <t>Yes</t>
-        </is>
-      </c>
       <c r="AA4" t="inlineStr">
         <is>
-          <t>RotoWire projected lineup; MLB probable pitchers</t>
-        </is>
-      </c>
-      <c r="AB4" t="inlineStr">
-        <is>
-          <t>lineup projected / unconfirmed</t>
-        </is>
-      </c>
+          <t>MLB Stats API; RotoWire</t>
+        </is>
+      </c>
+      <c r="AB4" t="inlineStr"/>
       <c r="AC4" t="inlineStr">
         <is>
           <t>H:2026/2025 P:2026/2025</t>
@@ -1437,127 +1429,127 @@
       </c>
       <c r="AH4" t="inlineStr">
         <is>
-          <t>9</t>
+          <t>10</t>
         </is>
       </c>
       <c r="AI4" t="inlineStr">
         <is>
-          <t>26</t>
+          <t>28</t>
         </is>
       </c>
       <c r="AJ4" t="inlineStr">
         <is>
-          <t>0</t>
+          <t>2</t>
         </is>
       </c>
       <c r="AK4" t="inlineStr">
         <is>
-          <t>Contact streak: 9/26 over last 7 games</t>
+          <t>Hot streak: 2 HR in last 7 games</t>
         </is>
       </c>
       <c r="AL4" t="inlineStr">
         <is>
-          <t>same-side matchup; pitcher baseline 11.0% barrel, 14.6 HR allowed</t>
+          <t>platoon edge; pitcher baseline 7.7% barrel, 3.7 HR allowed</t>
         </is>
       </c>
       <c r="AM4" t="inlineStr">
         <is>
-          <t>neutral batted-ball profile; pitcher fly-ball pressure modest</t>
+          <t>neutral batted-ball profile; pitcher allows elevated contact</t>
         </is>
       </c>
       <c r="AN4" t="inlineStr">
         <is>
-          <t>10.59</t>
+          <t>11.46</t>
         </is>
       </c>
       <c r="AO4" t="inlineStr">
         <is>
-          <t>43.51</t>
+          <t>45.35</t>
         </is>
       </c>
       <c r="AP4" t="inlineStr">
         <is>
-          <t>89.92</t>
+          <t>89.98</t>
         </is>
       </c>
       <c r="AQ4" t="inlineStr">
         <is>
-          <t>101.6508</t>
+          <t>100.5329</t>
         </is>
       </c>
       <c r="AR4" t="inlineStr">
         <is>
-          <t>0.4042</t>
+          <t>0.4627</t>
         </is>
       </c>
       <c r="AS4" t="inlineStr">
         <is>
-          <t>0.175</t>
+          <t>0.2053</t>
         </is>
       </c>
       <c r="AT4" t="inlineStr">
         <is>
-          <t>0.3098</t>
+          <t>0.3309</t>
         </is>
       </c>
       <c r="AU4" t="inlineStr">
         <is>
-          <t>74.31</t>
+          <t>72.88</t>
         </is>
       </c>
       <c r="AV4" t="inlineStr">
         <is>
-          <t>43.55</t>
+          <t>26.98</t>
         </is>
       </c>
       <c r="AW4" t="inlineStr">
         <is>
-          <t>43.04</t>
+          <t>37.91</t>
         </is>
       </c>
       <c r="AX4" t="inlineStr">
         <is>
-          <t>28.42</t>
+          <t>28.94</t>
         </is>
       </c>
       <c r="AY4" t="inlineStr">
         <is>
-          <t>23.5</t>
+          <t>16.7</t>
         </is>
       </c>
       <c r="AZ4" t="inlineStr">
         <is>
-          <t>0.2075</t>
+          <t>0.172</t>
         </is>
       </c>
       <c r="BA4" t="inlineStr">
         <is>
-          <t>11.04</t>
+          <t>7.69</t>
         </is>
       </c>
       <c r="BB4" t="inlineStr">
         <is>
-          <t>43.01</t>
+          <t>37.81</t>
         </is>
       </c>
       <c r="BC4" t="inlineStr">
         <is>
-          <t>90.71</t>
+          <t>89.39</t>
         </is>
       </c>
       <c r="BD4" t="inlineStr">
         <is>
-          <t>0.5055</t>
+          <t>0.3942</t>
         </is>
       </c>
       <c r="BE4" t="inlineStr">
         <is>
-          <t>0.2189</t>
+          <t>0.1474</t>
         </is>
       </c>
       <c r="BF4" t="inlineStr">
         <is>
-          <t>29.3</t>
+          <t>37.54</t>
         </is>
       </c>
       <c r="BG4" t="inlineStr">
@@ -1583,24 +1575,24 @@
       </c>
       <c r="B5" t="inlineStr">
         <is>
-          <t>666211</t>
+          <t>665487</t>
         </is>
       </c>
       <c r="C5" t="inlineStr">
         <is>
-          <t>Taylor Trammell</t>
+          <t>Fernando Tatis Jr.</t>
         </is>
       </c>
       <c r="D5" t="inlineStr">
         <is>
+          <t>SD</t>
+        </is>
+      </c>
+      <c r="E5" t="inlineStr">
+        <is>
           <t>HOU</t>
         </is>
       </c>
-      <c r="E5" t="inlineStr">
-        <is>
-          <t>SD</t>
-        </is>
-      </c>
       <c r="F5" t="inlineStr">
         <is>
           <t>2026-08-10T00:20:00Z</t>
@@ -1613,17 +1605,17 @@
       </c>
       <c r="H5" t="inlineStr">
         <is>
-          <t>7</t>
+          <t>1</t>
         </is>
       </c>
       <c r="I5" t="inlineStr">
         <is>
-          <t>Randy Vásquez</t>
+          <t>Cristian Javier</t>
         </is>
       </c>
       <c r="J5" t="inlineStr">
         <is>
-          <t>681190</t>
+          <t>664299</t>
         </is>
       </c>
       <c r="K5" t="inlineStr">
@@ -1632,7 +1624,7 @@
         </is>
       </c>
       <c r="L5" t="n">
-        <v>55.3</v>
+        <v>55.2</v>
       </c>
       <c r="M5" t="inlineStr">
         <is>
@@ -1646,62 +1638,58 @@
       </c>
       <c r="O5" t="inlineStr">
         <is>
-          <t>Projected Lineup, Strong Barrel, Platoon Edge</t>
+          <t>Strong Barrel, Premium Lineup Spot</t>
         </is>
       </c>
       <c r="P5" t="n">
-        <v>40.5</v>
+        <v>51.8</v>
       </c>
       <c r="Q5" t="n">
-        <v>62.7</v>
+        <v>39</v>
       </c>
       <c r="R5" t="n">
         <v>58.1</v>
       </c>
       <c r="S5" t="n">
-        <v>59.8</v>
+        <v>93.2</v>
       </c>
       <c r="T5" t="n">
-        <v>80</v>
+        <v>50</v>
       </c>
       <c r="U5" t="n">
-        <v>51.3</v>
+        <v>50.8</v>
       </c>
       <c r="V5" t="inlineStr">
         <is>
+          <t>Yes</t>
+        </is>
+      </c>
+      <c r="W5" t="inlineStr">
+        <is>
+          <t>Yes</t>
+        </is>
+      </c>
+      <c r="X5" t="inlineStr">
+        <is>
+          <t>1</t>
+        </is>
+      </c>
+      <c r="Y5" t="inlineStr">
+        <is>
+          <t>Yes</t>
+        </is>
+      </c>
+      <c r="Z5" t="inlineStr">
+        <is>
           <t>No</t>
         </is>
       </c>
-      <c r="W5" t="inlineStr">
-        <is>
-          <t>No</t>
-        </is>
-      </c>
-      <c r="X5" t="inlineStr">
-        <is>
-          <t>7</t>
-        </is>
-      </c>
-      <c r="Y5" t="inlineStr">
-        <is>
-          <t>Yes</t>
-        </is>
-      </c>
-      <c r="Z5" t="inlineStr">
-        <is>
-          <t>Yes</t>
-        </is>
-      </c>
       <c r="AA5" t="inlineStr">
         <is>
-          <t>RotoWire projected lineup; MLB probable pitchers</t>
-        </is>
-      </c>
-      <c r="AB5" t="inlineStr">
-        <is>
-          <t>lineup projected / unconfirmed</t>
-        </is>
-      </c>
+          <t>MLB Stats API; RotoWire</t>
+        </is>
+      </c>
+      <c r="AB5" t="inlineStr"/>
       <c r="AC5" t="inlineStr">
         <is>
           <t>H:2026/2025 P:2026/2025</t>
@@ -1721,12 +1709,12 @@
       </c>
       <c r="AH5" t="inlineStr">
         <is>
-          <t>5</t>
+          <t>6</t>
         </is>
       </c>
       <c r="AI5" t="inlineStr">
         <is>
-          <t>23</t>
+          <t>28</t>
         </is>
       </c>
       <c r="AJ5" t="inlineStr">
@@ -1741,107 +1729,107 @@
       </c>
       <c r="AL5" t="inlineStr">
         <is>
-          <t>platoon edge; pitcher baseline 11.0% barrel, 14.6 HR allowed</t>
+          <t>same-side matchup; pitcher baseline 7.7% barrel, 3.7 HR allowed</t>
         </is>
       </c>
       <c r="AM5" t="inlineStr">
         <is>
-          <t>neutral batted-ball profile; pitcher fly-ball pressure modest</t>
+          <t>EV profile; pitcher allows elevated contact</t>
         </is>
       </c>
       <c r="AN5" t="inlineStr">
         <is>
-          <t>11.02</t>
+          <t>11.0</t>
         </is>
       </c>
       <c r="AO5" t="inlineStr">
         <is>
-          <t>36.73</t>
+          <t>52.29</t>
         </is>
       </c>
       <c r="AP5" t="inlineStr">
         <is>
-          <t>89.11</t>
+          <t>92.53</t>
         </is>
       </c>
       <c r="AQ5" t="inlineStr">
         <is>
-          <t>100.7812</t>
+          <t>104.2616</t>
         </is>
       </c>
       <c r="AR5" t="inlineStr">
         <is>
-          <t>0.3854</t>
+          <t>0.4593</t>
         </is>
       </c>
       <c r="AS5" t="inlineStr">
         <is>
-          <t>0.1809</t>
+          <t>0.1785</t>
         </is>
       </c>
       <c r="AT5" t="inlineStr">
         <is>
-          <t>0.3025</t>
+          <t>0.3602</t>
         </is>
       </c>
       <c r="AU5" t="inlineStr">
         <is>
-          <t>75.44</t>
+          <t>75.51</t>
         </is>
       </c>
       <c r="AV5" t="inlineStr">
         <is>
-          <t>55.07</t>
+          <t>57.7</t>
         </is>
       </c>
       <c r="AW5" t="inlineStr">
         <is>
-          <t>46.19</t>
+          <t>34.24</t>
         </is>
       </c>
       <c r="AX5" t="inlineStr">
         <is>
-          <t>30.09</t>
+          <t>21.87</t>
         </is>
       </c>
       <c r="AY5" t="inlineStr">
         <is>
-          <t>5.8</t>
+          <t>14.5</t>
         </is>
       </c>
       <c r="AZ5" t="inlineStr">
         <is>
-          <t>0.1696</t>
+          <t>0.143</t>
         </is>
       </c>
       <c r="BA5" t="inlineStr">
         <is>
-          <t>11.04</t>
+          <t>7.69</t>
         </is>
       </c>
       <c r="BB5" t="inlineStr">
         <is>
-          <t>43.01</t>
+          <t>37.81</t>
         </is>
       </c>
       <c r="BC5" t="inlineStr">
         <is>
-          <t>90.71</t>
+          <t>89.39</t>
         </is>
       </c>
       <c r="BD5" t="inlineStr">
         <is>
-          <t>0.5055</t>
+          <t>0.3942</t>
         </is>
       </c>
       <c r="BE5" t="inlineStr">
         <is>
-          <t>0.2189</t>
+          <t>0.1474</t>
         </is>
       </c>
       <c r="BF5" t="inlineStr">
         <is>
-          <t>29.3</t>
+          <t>37.54</t>
         </is>
       </c>
       <c r="BG5" t="inlineStr">
@@ -1867,24 +1855,24 @@
       </c>
       <c r="B6" t="inlineStr">
         <is>
-          <t>665487</t>
+          <t>572233</t>
         </is>
       </c>
       <c r="C6" t="inlineStr">
         <is>
-          <t>Fernando Tatis Jr.</t>
+          <t>Christian Walker</t>
         </is>
       </c>
       <c r="D6" t="inlineStr">
         <is>
+          <t>HOU</t>
+        </is>
+      </c>
+      <c r="E6" t="inlineStr">
+        <is>
           <t>SD</t>
         </is>
       </c>
-      <c r="E6" t="inlineStr">
-        <is>
-          <t>HOU</t>
-        </is>
-      </c>
       <c r="F6" t="inlineStr">
         <is>
           <t>2026-08-10T00:20:00Z</t>
@@ -1897,17 +1885,17 @@
       </c>
       <c r="H6" t="inlineStr">
         <is>
-          <t>1</t>
+          <t>6</t>
         </is>
       </c>
       <c r="I6" t="inlineStr">
         <is>
-          <t>Cristian Javier</t>
+          <t>Randy Vásquez</t>
         </is>
       </c>
       <c r="J6" t="inlineStr">
         <is>
-          <t>664299</t>
+          <t>681190</t>
         </is>
       </c>
       <c r="K6" t="inlineStr">
@@ -1916,7 +1904,7 @@
         </is>
       </c>
       <c r="L6" t="n">
-        <v>55.2</v>
+        <v>54.8</v>
       </c>
       <c r="M6" t="inlineStr">
         <is>
@@ -1930,26 +1918,26 @@
       </c>
       <c r="O6" t="inlineStr">
         <is>
-          <t>Strong Barrel, Premium Lineup Spot</t>
+          <t>Strong Barrel</t>
         </is>
       </c>
       <c r="P6" t="n">
-        <v>51.8</v>
+        <v>42.9</v>
       </c>
       <c r="Q6" t="n">
-        <v>39</v>
+        <v>62.7</v>
       </c>
       <c r="R6" t="n">
         <v>58.1</v>
       </c>
       <c r="S6" t="n">
-        <v>93.2</v>
+        <v>76.2</v>
       </c>
       <c r="T6" t="n">
         <v>50</v>
       </c>
       <c r="U6" t="n">
-        <v>50.8</v>
+        <v>33.9</v>
       </c>
       <c r="V6" t="inlineStr">
         <is>
@@ -1963,7 +1951,7 @@
       </c>
       <c r="X6" t="inlineStr">
         <is>
-          <t>1</t>
+          <t>6</t>
         </is>
       </c>
       <c r="Y6" t="inlineStr">
@@ -2001,127 +1989,127 @@
       </c>
       <c r="AH6" t="inlineStr">
         <is>
-          <t>6</t>
+          <t>9</t>
         </is>
       </c>
       <c r="AI6" t="inlineStr">
         <is>
-          <t>28</t>
+          <t>26</t>
         </is>
       </c>
       <c r="AJ6" t="inlineStr">
         <is>
-          <t>2</t>
+          <t>0</t>
         </is>
       </c>
       <c r="AK6" t="inlineStr">
         <is>
-          <t>Hot streak: 2 HR in last 7 games</t>
+          <t>Contact streak: 9/26 over last 7 games</t>
         </is>
       </c>
       <c r="AL6" t="inlineStr">
         <is>
-          <t>same-side matchup; pitcher baseline 7.7% barrel, 3.7 HR allowed</t>
+          <t>same-side matchup; pitcher baseline 11.0% barrel, 14.6 HR allowed</t>
         </is>
       </c>
       <c r="AM6" t="inlineStr">
         <is>
-          <t>EV profile; pitcher allows elevated contact</t>
+          <t>neutral batted-ball profile; pitcher fly-ball pressure modest</t>
         </is>
       </c>
       <c r="AN6" t="inlineStr">
         <is>
-          <t>11.0</t>
+          <t>10.59</t>
         </is>
       </c>
       <c r="AO6" t="inlineStr">
         <is>
-          <t>52.29</t>
+          <t>43.51</t>
         </is>
       </c>
       <c r="AP6" t="inlineStr">
         <is>
-          <t>92.53</t>
+          <t>89.92</t>
         </is>
       </c>
       <c r="AQ6" t="inlineStr">
         <is>
-          <t>104.2616</t>
+          <t>101.6508</t>
         </is>
       </c>
       <c r="AR6" t="inlineStr">
         <is>
-          <t>0.4593</t>
+          <t>0.4042</t>
         </is>
       </c>
       <c r="AS6" t="inlineStr">
         <is>
-          <t>0.1785</t>
+          <t>0.175</t>
         </is>
       </c>
       <c r="AT6" t="inlineStr">
         <is>
-          <t>0.3602</t>
+          <t>0.3098</t>
         </is>
       </c>
       <c r="AU6" t="inlineStr">
         <is>
-          <t>75.51</t>
+          <t>74.31</t>
         </is>
       </c>
       <c r="AV6" t="inlineStr">
         <is>
-          <t>57.7</t>
+          <t>43.55</t>
         </is>
       </c>
       <c r="AW6" t="inlineStr">
         <is>
-          <t>34.24</t>
+          <t>43.04</t>
         </is>
       </c>
       <c r="AX6" t="inlineStr">
         <is>
-          <t>21.87</t>
+          <t>28.42</t>
         </is>
       </c>
       <c r="AY6" t="inlineStr">
         <is>
-          <t>14.5</t>
+          <t>23.5</t>
         </is>
       </c>
       <c r="AZ6" t="inlineStr">
         <is>
-          <t>0.143</t>
+          <t>0.2075</t>
         </is>
       </c>
       <c r="BA6" t="inlineStr">
         <is>
-          <t>7.69</t>
+          <t>11.04</t>
         </is>
       </c>
       <c r="BB6" t="inlineStr">
         <is>
-          <t>37.81</t>
+          <t>43.01</t>
         </is>
       </c>
       <c r="BC6" t="inlineStr">
         <is>
-          <t>89.39</t>
+          <t>90.71</t>
         </is>
       </c>
       <c r="BD6" t="inlineStr">
         <is>
-          <t>0.3942</t>
+          <t>0.5055</t>
         </is>
       </c>
       <c r="BE6" t="inlineStr">
         <is>
-          <t>0.1474</t>
+          <t>0.2189</t>
         </is>
       </c>
       <c r="BF6" t="inlineStr">
         <is>
-          <t>37.54</t>
+          <t>29.3</t>
         </is>
       </c>
       <c r="BG6" t="inlineStr">
@@ -2147,24 +2135,24 @@
       </c>
       <c r="B7" t="inlineStr">
         <is>
-          <t>662139</t>
+          <t>592518</t>
         </is>
       </c>
       <c r="C7" t="inlineStr">
         <is>
-          <t>Daulton Varsho</t>
+          <t>Manny Machado</t>
         </is>
       </c>
       <c r="D7" t="inlineStr">
         <is>
+          <t>SD</t>
+        </is>
+      </c>
+      <c r="E7" t="inlineStr">
+        <is>
           <t>HOU</t>
         </is>
       </c>
-      <c r="E7" t="inlineStr">
-        <is>
-          <t>SD</t>
-        </is>
-      </c>
       <c r="F7" t="inlineStr">
         <is>
           <t>2026-08-10T00:20:00Z</t>
@@ -2177,17 +2165,17 @@
       </c>
       <c r="H7" t="inlineStr">
         <is>
-          <t>4</t>
+          <t>3</t>
         </is>
       </c>
       <c r="I7" t="inlineStr">
         <is>
-          <t>Randy Vásquez</t>
+          <t>Cristian Javier</t>
         </is>
       </c>
       <c r="J7" t="inlineStr">
         <is>
-          <t>681190</t>
+          <t>664299</t>
         </is>
       </c>
       <c r="K7" t="inlineStr">
@@ -2196,7 +2184,7 @@
         </is>
       </c>
       <c r="L7" t="n">
-        <v>54.8</v>
+        <v>53.3</v>
       </c>
       <c r="M7" t="inlineStr">
         <is>
@@ -2210,62 +2198,58 @@
       </c>
       <c r="O7" t="inlineStr">
         <is>
-          <t>Projected Lineup, Premium Lineup Spot, Platoon Edge</t>
+          <t>Strong Barrel, Premium Lineup Spot</t>
         </is>
       </c>
       <c r="P7" t="n">
-        <v>33.6</v>
+        <v>50.3</v>
       </c>
       <c r="Q7" t="n">
-        <v>62.7</v>
+        <v>39</v>
       </c>
       <c r="R7" t="n">
         <v>58.1</v>
       </c>
       <c r="S7" t="n">
-        <v>90.40000000000001</v>
+        <v>96.59999999999999</v>
       </c>
       <c r="T7" t="n">
-        <v>80</v>
+        <v>50</v>
       </c>
       <c r="U7" t="n">
-        <v>0.8</v>
+        <v>12</v>
       </c>
       <c r="V7" t="inlineStr">
         <is>
+          <t>Yes</t>
+        </is>
+      </c>
+      <c r="W7" t="inlineStr">
+        <is>
+          <t>Yes</t>
+        </is>
+      </c>
+      <c r="X7" t="inlineStr">
+        <is>
+          <t>3</t>
+        </is>
+      </c>
+      <c r="Y7" t="inlineStr">
+        <is>
+          <t>Yes</t>
+        </is>
+      </c>
+      <c r="Z7" t="inlineStr">
+        <is>
           <t>No</t>
         </is>
       </c>
-      <c r="W7" t="inlineStr">
-        <is>
-          <t>No</t>
-        </is>
-      </c>
-      <c r="X7" t="inlineStr">
-        <is>
-          <t>4</t>
-        </is>
-      </c>
-      <c r="Y7" t="inlineStr">
-        <is>
-          <t>Yes</t>
-        </is>
-      </c>
-      <c r="Z7" t="inlineStr">
-        <is>
-          <t>Yes</t>
-        </is>
-      </c>
       <c r="AA7" t="inlineStr">
         <is>
-          <t>RotoWire projected lineup; MLB probable pitchers</t>
-        </is>
-      </c>
-      <c r="AB7" t="inlineStr">
-        <is>
-          <t>lineup projected / unconfirmed</t>
-        </is>
-      </c>
+          <t>MLB Stats API; RotoWire</t>
+        </is>
+      </c>
+      <c r="AB7" t="inlineStr"/>
       <c r="AC7" t="inlineStr">
         <is>
           <t>H:2026/2025 P:2026/2025</t>
@@ -2285,12 +2269,12 @@
       </c>
       <c r="AH7" t="inlineStr">
         <is>
-          <t>3</t>
+          <t>5</t>
         </is>
       </c>
       <c r="AI7" t="inlineStr">
         <is>
-          <t>24</t>
+          <t>25</t>
         </is>
       </c>
       <c r="AJ7" t="inlineStr">
@@ -2300,112 +2284,112 @@
       </c>
       <c r="AK7" t="inlineStr">
         <is>
-          <t>Last 7 games: 3/24, 0 HR</t>
+          <t>Last 7 games: 5/25, 0 HR</t>
         </is>
       </c>
       <c r="AL7" t="inlineStr">
         <is>
-          <t>platoon edge; pitcher baseline 11.0% barrel, 14.6 HR allowed</t>
+          <t>same-side matchup; pitcher baseline 7.7% barrel, 3.7 HR allowed</t>
         </is>
       </c>
       <c r="AM7" t="inlineStr">
         <is>
-          <t>neutral batted-ball profile; pitcher fly-ball pressure modest</t>
+          <t>neutral batted-ball profile; pitcher allows elevated contact</t>
         </is>
       </c>
       <c r="AN7" t="inlineStr">
         <is>
-          <t>9.04</t>
+          <t>11.22</t>
         </is>
       </c>
       <c r="AO7" t="inlineStr">
         <is>
-          <t>37.64</t>
+          <t>46.32</t>
         </is>
       </c>
       <c r="AP7" t="inlineStr">
         <is>
-          <t>87.31</t>
+          <t>91.36</t>
         </is>
       </c>
       <c r="AQ7" t="inlineStr">
         <is>
-          <t>99.33</t>
+          <t>101.8619</t>
         </is>
       </c>
       <c r="AR7" t="inlineStr">
         <is>
-          <t>0.3967</t>
+          <t>0.4502</t>
         </is>
       </c>
       <c r="AS7" t="inlineStr">
         <is>
-          <t>0.1634</t>
+          <t>0.2002</t>
         </is>
       </c>
       <c r="AT7" t="inlineStr">
         <is>
-          <t>0.3018</t>
+          <t>0.3368</t>
         </is>
       </c>
       <c r="AU7" t="inlineStr">
         <is>
-          <t>73.78</t>
+          <t>74.64</t>
         </is>
       </c>
       <c r="AV7" t="inlineStr">
         <is>
-          <t>37.09</t>
+          <t>44.44</t>
         </is>
       </c>
       <c r="AW7" t="inlineStr">
         <is>
-          <t>42.2</t>
+          <t>40.5</t>
         </is>
       </c>
       <c r="AX7" t="inlineStr">
         <is>
-          <t>28.96</t>
+          <t>28.85</t>
         </is>
       </c>
       <c r="AY7" t="inlineStr">
         <is>
-          <t>10.9</t>
+          <t>24.2</t>
         </is>
       </c>
       <c r="AZ7" t="inlineStr">
         <is>
-          <t>0.1812</t>
+          <t>0.2018</t>
         </is>
       </c>
       <c r="BA7" t="inlineStr">
         <is>
-          <t>11.04</t>
+          <t>7.69</t>
         </is>
       </c>
       <c r="BB7" t="inlineStr">
         <is>
-          <t>43.01</t>
+          <t>37.81</t>
         </is>
       </c>
       <c r="BC7" t="inlineStr">
         <is>
-          <t>90.71</t>
+          <t>89.39</t>
         </is>
       </c>
       <c r="BD7" t="inlineStr">
         <is>
-          <t>0.5055</t>
+          <t>0.3942</t>
         </is>
       </c>
       <c r="BE7" t="inlineStr">
         <is>
-          <t>0.2189</t>
+          <t>0.1474</t>
         </is>
       </c>
       <c r="BF7" t="inlineStr">
         <is>
-          <t>29.3</t>
+          <t>37.54</t>
         </is>
       </c>
       <c r="BG7" t="inlineStr">
@@ -2431,24 +2415,24 @@
       </c>
       <c r="B8" t="inlineStr">
         <is>
-          <t>592518</t>
+          <t>665161</t>
         </is>
       </c>
       <c r="C8" t="inlineStr">
         <is>
-          <t>Manny Machado</t>
+          <t>Jeremy Peña</t>
         </is>
       </c>
       <c r="D8" t="inlineStr">
         <is>
+          <t>HOU</t>
+        </is>
+      </c>
+      <c r="E8" t="inlineStr">
+        <is>
           <t>SD</t>
         </is>
       </c>
-      <c r="E8" t="inlineStr">
-        <is>
-          <t>HOU</t>
-        </is>
-      </c>
       <c r="F8" t="inlineStr">
         <is>
           <t>2026-08-10T00:20:00Z</t>
@@ -2461,17 +2445,17 @@
       </c>
       <c r="H8" t="inlineStr">
         <is>
-          <t>3</t>
+          <t>1</t>
         </is>
       </c>
       <c r="I8" t="inlineStr">
         <is>
-          <t>Cristian Javier</t>
+          <t>Randy Vásquez</t>
         </is>
       </c>
       <c r="J8" t="inlineStr">
         <is>
-          <t>664299</t>
+          <t>681190</t>
         </is>
       </c>
       <c r="K8" t="inlineStr">
@@ -2480,7 +2464,7 @@
         </is>
       </c>
       <c r="L8" t="n">
-        <v>53.3</v>
+        <v>52.9</v>
       </c>
       <c r="M8" t="inlineStr">
         <is>
@@ -2494,26 +2478,26 @@
       </c>
       <c r="O8" t="inlineStr">
         <is>
-          <t>Strong Barrel, Premium Lineup Spot</t>
+          <t>Premium Lineup Spot</t>
         </is>
       </c>
       <c r="P8" t="n">
-        <v>50.3</v>
+        <v>31.1</v>
       </c>
       <c r="Q8" t="n">
-        <v>39</v>
+        <v>62.7</v>
       </c>
       <c r="R8" t="n">
         <v>58.1</v>
       </c>
       <c r="S8" t="n">
-        <v>96.59999999999999</v>
+        <v>93.2</v>
       </c>
       <c r="T8" t="n">
         <v>50</v>
       </c>
       <c r="U8" t="n">
-        <v>12</v>
+        <v>26.2</v>
       </c>
       <c r="V8" t="inlineStr">
         <is>
@@ -2527,7 +2511,7 @@
       </c>
       <c r="X8" t="inlineStr">
         <is>
-          <t>3</t>
+          <t>1</t>
         </is>
       </c>
       <c r="Y8" t="inlineStr">
@@ -2570,122 +2554,122 @@
       </c>
       <c r="AI8" t="inlineStr">
         <is>
-          <t>25</t>
+          <t>29</t>
         </is>
       </c>
       <c r="AJ8" t="inlineStr">
         <is>
-          <t>0</t>
+          <t>1</t>
         </is>
       </c>
       <c r="AK8" t="inlineStr">
         <is>
-          <t>Last 7 games: 5/25, 0 HR</t>
+          <t>Last 7 games: 5/29, 1 HR</t>
         </is>
       </c>
       <c r="AL8" t="inlineStr">
         <is>
-          <t>same-side matchup; pitcher baseline 7.7% barrel, 3.7 HR allowed</t>
+          <t>same-side matchup; pitcher baseline 11.0% barrel, 14.6 HR allowed</t>
         </is>
       </c>
       <c r="AM8" t="inlineStr">
         <is>
-          <t>neutral batted-ball profile; pitcher allows elevated contact</t>
+          <t>neutral batted-ball profile; pitcher fly-ball pressure modest</t>
         </is>
       </c>
       <c r="AN8" t="inlineStr">
         <is>
-          <t>11.22</t>
+          <t>6.31</t>
         </is>
       </c>
       <c r="AO8" t="inlineStr">
         <is>
-          <t>46.32</t>
+          <t>41.64</t>
         </is>
       </c>
       <c r="AP8" t="inlineStr">
         <is>
-          <t>91.36</t>
+          <t>88.41</t>
         </is>
       </c>
       <c r="AQ8" t="inlineStr">
         <is>
-          <t>101.8619</t>
+          <t>100.0639</t>
         </is>
       </c>
       <c r="AR8" t="inlineStr">
         <is>
-          <t>0.4502</t>
+          <t>0.4404</t>
         </is>
       </c>
       <c r="AS8" t="inlineStr">
         <is>
-          <t>0.2002</t>
+          <t>0.1522</t>
         </is>
       </c>
       <c r="AT8" t="inlineStr">
         <is>
-          <t>0.3368</t>
+          <t>0.3466</t>
         </is>
       </c>
       <c r="AU8" t="inlineStr">
         <is>
-          <t>74.64</t>
+          <t>72.23</t>
         </is>
       </c>
       <c r="AV8" t="inlineStr">
         <is>
-          <t>44.44</t>
+          <t>13.99</t>
         </is>
       </c>
       <c r="AW8" t="inlineStr">
         <is>
-          <t>40.5</t>
+          <t>46.06</t>
         </is>
       </c>
       <c r="AX8" t="inlineStr">
         <is>
-          <t>28.85</t>
+          <t>23.45</t>
         </is>
       </c>
       <c r="AY8" t="inlineStr">
         <is>
-          <t>24.2</t>
+          <t>14.2</t>
         </is>
       </c>
       <c r="AZ8" t="inlineStr">
         <is>
-          <t>0.2018</t>
+          <t>0.187</t>
         </is>
       </c>
       <c r="BA8" t="inlineStr">
         <is>
-          <t>7.69</t>
+          <t>11.04</t>
         </is>
       </c>
       <c r="BB8" t="inlineStr">
         <is>
-          <t>37.81</t>
+          <t>43.01</t>
         </is>
       </c>
       <c r="BC8" t="inlineStr">
         <is>
-          <t>89.39</t>
+          <t>90.71</t>
         </is>
       </c>
       <c r="BD8" t="inlineStr">
         <is>
-          <t>0.3942</t>
+          <t>0.5055</t>
         </is>
       </c>
       <c r="BE8" t="inlineStr">
         <is>
-          <t>0.1474</t>
+          <t>0.2189</t>
         </is>
       </c>
       <c r="BF8" t="inlineStr">
         <is>
-          <t>37.54</t>
+          <t>29.3</t>
         </is>
       </c>
       <c r="BG8" t="inlineStr">
@@ -2711,24 +2695,24 @@
       </c>
       <c r="B9" t="inlineStr">
         <is>
-          <t>665161</t>
+          <t>664034</t>
         </is>
       </c>
       <c r="C9" t="inlineStr">
         <is>
-          <t>Jeremy Pena</t>
+          <t>Ty France</t>
         </is>
       </c>
       <c r="D9" t="inlineStr">
         <is>
+          <t>SD</t>
+        </is>
+      </c>
+      <c r="E9" t="inlineStr">
+        <is>
           <t>HOU</t>
         </is>
       </c>
-      <c r="E9" t="inlineStr">
-        <is>
-          <t>SD</t>
-        </is>
-      </c>
       <c r="F9" t="inlineStr">
         <is>
           <t>2026-08-10T00:20:00Z</t>
@@ -2741,17 +2725,17 @@
       </c>
       <c r="H9" t="inlineStr">
         <is>
-          <t>1</t>
+          <t>4</t>
         </is>
       </c>
       <c r="I9" t="inlineStr">
         <is>
-          <t>Randy Vásquez</t>
+          <t>Cristian Javier</t>
         </is>
       </c>
       <c r="J9" t="inlineStr">
         <is>
-          <t>681190</t>
+          <t>664299</t>
         </is>
       </c>
       <c r="K9" t="inlineStr">
@@ -2760,7 +2744,7 @@
         </is>
       </c>
       <c r="L9" t="n">
-        <v>52.3</v>
+        <v>51.4</v>
       </c>
       <c r="M9" t="inlineStr">
         <is>
@@ -2774,62 +2758,58 @@
       </c>
       <c r="O9" t="inlineStr">
         <is>
-          <t>Projected Lineup, Premium Lineup Spot</t>
+          <t>Strong Barrel, Premium Lineup Spot</t>
         </is>
       </c>
       <c r="P9" t="n">
-        <v>31.1</v>
+        <v>45.1</v>
       </c>
       <c r="Q9" t="n">
-        <v>62.7</v>
+        <v>39</v>
       </c>
       <c r="R9" t="n">
         <v>58.1</v>
       </c>
       <c r="S9" t="n">
-        <v>88.7</v>
+        <v>94.90000000000001</v>
       </c>
       <c r="T9" t="n">
         <v>50</v>
       </c>
       <c r="U9" t="n">
-        <v>26.2</v>
+        <v>13.3</v>
       </c>
       <c r="V9" t="inlineStr">
         <is>
+          <t>Yes</t>
+        </is>
+      </c>
+      <c r="W9" t="inlineStr">
+        <is>
+          <t>Yes</t>
+        </is>
+      </c>
+      <c r="X9" t="inlineStr">
+        <is>
+          <t>4</t>
+        </is>
+      </c>
+      <c r="Y9" t="inlineStr">
+        <is>
+          <t>Yes</t>
+        </is>
+      </c>
+      <c r="Z9" t="inlineStr">
+        <is>
           <t>No</t>
         </is>
       </c>
-      <c r="W9" t="inlineStr">
-        <is>
-          <t>No</t>
-        </is>
-      </c>
-      <c r="X9" t="inlineStr">
-        <is>
-          <t>1</t>
-        </is>
-      </c>
-      <c r="Y9" t="inlineStr">
-        <is>
-          <t>Yes</t>
-        </is>
-      </c>
-      <c r="Z9" t="inlineStr">
-        <is>
-          <t>Yes</t>
-        </is>
-      </c>
       <c r="AA9" t="inlineStr">
         <is>
-          <t>RotoWire projected lineup; MLB probable pitchers</t>
-        </is>
-      </c>
-      <c r="AB9" t="inlineStr">
-        <is>
-          <t>lineup projected / unconfirmed</t>
-        </is>
-      </c>
+          <t>MLB Stats API; RotoWire</t>
+        </is>
+      </c>
+      <c r="AB9" t="inlineStr"/>
       <c r="AC9" t="inlineStr">
         <is>
           <t>H:2026/2025 P:2026/2025</t>
@@ -2854,122 +2834,122 @@
       </c>
       <c r="AI9" t="inlineStr">
         <is>
-          <t>29</t>
+          <t>24</t>
         </is>
       </c>
       <c r="AJ9" t="inlineStr">
         <is>
-          <t>1</t>
+          <t>0</t>
         </is>
       </c>
       <c r="AK9" t="inlineStr">
         <is>
-          <t>Last 7 games: 5/29, 1 HR</t>
+          <t>Last 7 games: 5/24, 0 HR</t>
         </is>
       </c>
       <c r="AL9" t="inlineStr">
         <is>
-          <t>same-side matchup; pitcher baseline 11.0% barrel, 14.6 HR allowed</t>
+          <t>same-side matchup; pitcher baseline 7.7% barrel, 3.7 HR allowed</t>
         </is>
       </c>
       <c r="AM9" t="inlineStr">
         <is>
-          <t>neutral batted-ball profile; pitcher fly-ball pressure modest</t>
+          <t>neutral batted-ball profile; pitcher allows elevated contact</t>
         </is>
       </c>
       <c r="AN9" t="inlineStr">
         <is>
-          <t>6.31</t>
+          <t>10.01</t>
         </is>
       </c>
       <c r="AO9" t="inlineStr">
         <is>
-          <t>41.64</t>
+          <t>47.63</t>
         </is>
       </c>
       <c r="AP9" t="inlineStr">
         <is>
-          <t>88.41</t>
+          <t>91.46</t>
         </is>
       </c>
       <c r="AQ9" t="inlineStr">
         <is>
-          <t>100.0639</t>
+          <t>101.3479</t>
         </is>
       </c>
       <c r="AR9" t="inlineStr">
         <is>
-          <t>0.4404</t>
+          <t>0.4376</t>
         </is>
       </c>
       <c r="AS9" t="inlineStr">
         <is>
-          <t>0.1522</t>
+          <t>0.1828</t>
         </is>
       </c>
       <c r="AT9" t="inlineStr">
         <is>
-          <t>0.3466</t>
+          <t>0.3301</t>
         </is>
       </c>
       <c r="AU9" t="inlineStr">
         <is>
-          <t>72.23</t>
+          <t>71.7</t>
         </is>
       </c>
       <c r="AV9" t="inlineStr">
         <is>
-          <t>13.99</t>
+          <t>18.48</t>
         </is>
       </c>
       <c r="AW9" t="inlineStr">
         <is>
-          <t>46.06</t>
+          <t>36.22</t>
         </is>
       </c>
       <c r="AX9" t="inlineStr">
         <is>
-          <t>23.45</t>
+          <t>24.76</t>
         </is>
       </c>
       <c r="AY9" t="inlineStr">
         <is>
-          <t>14.2</t>
+          <t>13.3</t>
         </is>
       </c>
       <c r="AZ9" t="inlineStr">
         <is>
-          <t>0.187</t>
+          <t>0.1933</t>
         </is>
       </c>
       <c r="BA9" t="inlineStr">
         <is>
-          <t>11.04</t>
+          <t>7.69</t>
         </is>
       </c>
       <c r="BB9" t="inlineStr">
         <is>
-          <t>43.01</t>
+          <t>37.81</t>
         </is>
       </c>
       <c r="BC9" t="inlineStr">
         <is>
-          <t>90.71</t>
+          <t>89.39</t>
         </is>
       </c>
       <c r="BD9" t="inlineStr">
         <is>
-          <t>0.5055</t>
+          <t>0.3942</t>
         </is>
       </c>
       <c r="BE9" t="inlineStr">
         <is>
-          <t>0.2189</t>
+          <t>0.1474</t>
         </is>
       </c>
       <c r="BF9" t="inlineStr">
         <is>
-          <t>29.3</t>
+          <t>37.54</t>
         </is>
       </c>
       <c r="BG9" t="inlineStr">
@@ -2995,12 +2975,12 @@
       </c>
       <c r="B10" t="inlineStr">
         <is>
-          <t>701358</t>
+          <t>662139</t>
         </is>
       </c>
       <c r="C10" t="inlineStr">
         <is>
-          <t>Cam Smith</t>
+          <t>Daulton Varsho</t>
         </is>
       </c>
       <c r="D10" t="inlineStr">
@@ -3025,7 +3005,7 @@
       </c>
       <c r="H10" t="inlineStr">
         <is>
-          <t>9</t>
+          <t>7</t>
         </is>
       </c>
       <c r="I10" t="inlineStr">
@@ -3044,7 +3024,7 @@
         </is>
       </c>
       <c r="L10" t="n">
-        <v>51.9</v>
+        <v>51.1</v>
       </c>
       <c r="M10" t="inlineStr">
         <is>
@@ -3058,11 +3038,11 @@
       </c>
       <c r="O10" t="inlineStr">
         <is>
-          <t>Projected Lineup, Strong Barrel, Hot Hitter/Streak</t>
+          <t>Platoon Edge</t>
         </is>
       </c>
       <c r="P10" t="n">
-        <v>42.2</v>
+        <v>33.6</v>
       </c>
       <c r="Q10" t="n">
         <v>62.7</v>
@@ -3071,49 +3051,45 @@
         <v>58.1</v>
       </c>
       <c r="S10" t="n">
-        <v>40.2</v>
+        <v>64.3</v>
       </c>
       <c r="T10" t="n">
-        <v>50</v>
+        <v>80</v>
       </c>
       <c r="U10" t="n">
-        <v>81.7</v>
+        <v>0.8</v>
       </c>
       <c r="V10" t="inlineStr">
         <is>
+          <t>Yes</t>
+        </is>
+      </c>
+      <c r="W10" t="inlineStr">
+        <is>
+          <t>Yes</t>
+        </is>
+      </c>
+      <c r="X10" t="inlineStr">
+        <is>
+          <t>7</t>
+        </is>
+      </c>
+      <c r="Y10" t="inlineStr">
+        <is>
+          <t>Yes</t>
+        </is>
+      </c>
+      <c r="Z10" t="inlineStr">
+        <is>
           <t>No</t>
         </is>
       </c>
-      <c r="W10" t="inlineStr">
-        <is>
-          <t>No</t>
-        </is>
-      </c>
-      <c r="X10" t="inlineStr">
-        <is>
-          <t>9</t>
-        </is>
-      </c>
-      <c r="Y10" t="inlineStr">
-        <is>
-          <t>Yes</t>
-        </is>
-      </c>
-      <c r="Z10" t="inlineStr">
-        <is>
-          <t>Yes</t>
-        </is>
-      </c>
       <c r="AA10" t="inlineStr">
         <is>
-          <t>RotoWire projected lineup; MLB probable pitchers</t>
-        </is>
-      </c>
-      <c r="AB10" t="inlineStr">
-        <is>
-          <t>lineup projected / unconfirmed</t>
-        </is>
-      </c>
+          <t>MLB Stats API; RotoWire</t>
+        </is>
+      </c>
+      <c r="AB10" t="inlineStr"/>
       <c r="AC10" t="inlineStr">
         <is>
           <t>H:2026/2025 P:2026/2025</t>
@@ -3133,27 +3109,27 @@
       </c>
       <c r="AH10" t="inlineStr">
         <is>
-          <t>10</t>
+          <t>3</t>
         </is>
       </c>
       <c r="AI10" t="inlineStr">
         <is>
-          <t>23</t>
+          <t>24</t>
         </is>
       </c>
       <c r="AJ10" t="inlineStr">
         <is>
-          <t>2</t>
+          <t>0</t>
         </is>
       </c>
       <c r="AK10" t="inlineStr">
         <is>
-          <t>Hot streak: 2 HR in last 7 games</t>
+          <t>Last 7 games: 3/24, 0 HR</t>
         </is>
       </c>
       <c r="AL10" t="inlineStr">
         <is>
-          <t>same-side matchup; pitcher baseline 11.0% barrel, 14.6 HR allowed</t>
+          <t>platoon edge; pitcher baseline 11.0% barrel, 14.6 HR allowed</t>
         </is>
       </c>
       <c r="AM10" t="inlineStr">
@@ -3163,67 +3139,67 @@
       </c>
       <c r="AN10" t="inlineStr">
         <is>
-          <t>10.19</t>
+          <t>9.04</t>
         </is>
       </c>
       <c r="AO10" t="inlineStr">
         <is>
-          <t>43.46</t>
+          <t>37.64</t>
         </is>
       </c>
       <c r="AP10" t="inlineStr">
         <is>
-          <t>88.95</t>
+          <t>87.31</t>
         </is>
       </c>
       <c r="AQ10" t="inlineStr">
         <is>
-          <t>101.5346</t>
+          <t>99.33</t>
         </is>
       </c>
       <c r="AR10" t="inlineStr">
         <is>
-          <t>0.418</t>
+          <t>0.3967</t>
         </is>
       </c>
       <c r="AS10" t="inlineStr">
         <is>
-          <t>0.1753</t>
+          <t>0.1634</t>
         </is>
       </c>
       <c r="AT10" t="inlineStr">
         <is>
-          <t>0.3215</t>
+          <t>0.3018</t>
         </is>
       </c>
       <c r="AU10" t="inlineStr">
         <is>
-          <t>76.67</t>
+          <t>73.78</t>
         </is>
       </c>
       <c r="AV10" t="inlineStr">
         <is>
-          <t>68.11</t>
+          <t>37.09</t>
         </is>
       </c>
       <c r="AW10" t="inlineStr">
         <is>
-          <t>37.42</t>
+          <t>42.2</t>
         </is>
       </c>
       <c r="AX10" t="inlineStr">
         <is>
-          <t>25.14</t>
+          <t>28.96</t>
         </is>
       </c>
       <c r="AY10" t="inlineStr">
         <is>
-          <t>13.2</t>
+          <t>10.9</t>
         </is>
       </c>
       <c r="AZ10" t="inlineStr">
         <is>
-          <t>0.1542</t>
+          <t>0.1812</t>
         </is>
       </c>
       <c r="BA10" t="inlineStr">
@@ -3279,24 +3255,24 @@
       </c>
       <c r="B11" t="inlineStr">
         <is>
-          <t>664034</t>
+          <t>514888</t>
         </is>
       </c>
       <c r="C11" t="inlineStr">
         <is>
-          <t>Ty France</t>
+          <t>Jose Altuve</t>
         </is>
       </c>
       <c r="D11" t="inlineStr">
         <is>
+          <t>HOU</t>
+        </is>
+      </c>
+      <c r="E11" t="inlineStr">
+        <is>
           <t>SD</t>
         </is>
       </c>
-      <c r="E11" t="inlineStr">
-        <is>
-          <t>HOU</t>
-        </is>
-      </c>
       <c r="F11" t="inlineStr">
         <is>
           <t>2026-08-10T00:20:00Z</t>
@@ -3314,12 +3290,12 @@
       </c>
       <c r="I11" t="inlineStr">
         <is>
-          <t>Cristian Javier</t>
+          <t>Randy Vásquez</t>
         </is>
       </c>
       <c r="J11" t="inlineStr">
         <is>
-          <t>664299</t>
+          <t>681190</t>
         </is>
       </c>
       <c r="K11" t="inlineStr">
@@ -3328,7 +3304,7 @@
         </is>
       </c>
       <c r="L11" t="n">
-        <v>51.4</v>
+        <v>49.7</v>
       </c>
       <c r="M11" t="inlineStr">
         <is>
@@ -3342,14 +3318,14 @@
       </c>
       <c r="O11" t="inlineStr">
         <is>
-          <t>Strong Barrel, Premium Lineup Spot</t>
+          <t>Premium Lineup Spot</t>
         </is>
       </c>
       <c r="P11" t="n">
-        <v>45.1</v>
+        <v>15.5</v>
       </c>
       <c r="Q11" t="n">
-        <v>39</v>
+        <v>62.7</v>
       </c>
       <c r="R11" t="n">
         <v>58.1</v>
@@ -3361,7 +3337,7 @@
         <v>50</v>
       </c>
       <c r="U11" t="n">
-        <v>13.3</v>
+        <v>61.4</v>
       </c>
       <c r="V11" t="inlineStr">
         <is>
@@ -3413,127 +3389,127 @@
       </c>
       <c r="AH11" t="inlineStr">
         <is>
-          <t>5</t>
+          <t>11</t>
         </is>
       </c>
       <c r="AI11" t="inlineStr">
         <is>
-          <t>24</t>
+          <t>27</t>
         </is>
       </c>
       <c r="AJ11" t="inlineStr">
         <is>
-          <t>0</t>
+          <t>1</t>
         </is>
       </c>
       <c r="AK11" t="inlineStr">
         <is>
-          <t>Last 7 games: 5/24, 0 HR</t>
+          <t>Contact streak: 11/27 over last 7 games</t>
         </is>
       </c>
       <c r="AL11" t="inlineStr">
         <is>
-          <t>same-side matchup; pitcher baseline 7.7% barrel, 3.7 HR allowed</t>
+          <t>same-side matchup; pitcher baseline 11.0% barrel, 14.6 HR allowed</t>
         </is>
       </c>
       <c r="AM11" t="inlineStr">
         <is>
-          <t>neutral batted-ball profile; pitcher allows elevated contact</t>
+          <t>neutral batted-ball profile; pitcher fly-ball pressure modest</t>
         </is>
       </c>
       <c r="AN11" t="inlineStr">
         <is>
-          <t>10.01</t>
+          <t>5.57</t>
         </is>
       </c>
       <c r="AO11" t="inlineStr">
         <is>
-          <t>47.63</t>
+          <t>31.88</t>
         </is>
       </c>
       <c r="AP11" t="inlineStr">
         <is>
-          <t>91.46</t>
+          <t>85.52</t>
         </is>
       </c>
       <c r="AQ11" t="inlineStr">
         <is>
-          <t>101.3479</t>
+          <t>97.1381</t>
         </is>
       </c>
       <c r="AR11" t="inlineStr">
         <is>
-          <t>0.4376</t>
+          <t>0.3511</t>
         </is>
       </c>
       <c r="AS11" t="inlineStr">
         <is>
-          <t>0.1828</t>
+          <t>0.1225</t>
         </is>
       </c>
       <c r="AT11" t="inlineStr">
         <is>
-          <t>0.3301</t>
+          <t>0.286</t>
         </is>
       </c>
       <c r="AU11" t="inlineStr">
         <is>
-          <t>71.7</t>
+          <t>69.07</t>
         </is>
       </c>
       <c r="AV11" t="inlineStr">
         <is>
-          <t>18.48</t>
+          <t>9.78</t>
         </is>
       </c>
       <c r="AW11" t="inlineStr">
         <is>
-          <t>36.22</t>
+          <t>46.2</t>
         </is>
       </c>
       <c r="AX11" t="inlineStr">
         <is>
-          <t>24.76</t>
+          <t>22.3</t>
         </is>
       </c>
       <c r="AY11" t="inlineStr">
         <is>
-          <t>13.3</t>
+          <t>16.9</t>
         </is>
       </c>
       <c r="AZ11" t="inlineStr">
         <is>
-          <t>0.1933</t>
+          <t>0.1602</t>
         </is>
       </c>
       <c r="BA11" t="inlineStr">
         <is>
-          <t>7.69</t>
+          <t>11.04</t>
         </is>
       </c>
       <c r="BB11" t="inlineStr">
         <is>
-          <t>37.81</t>
+          <t>43.01</t>
         </is>
       </c>
       <c r="BC11" t="inlineStr">
         <is>
-          <t>89.39</t>
+          <t>90.71</t>
         </is>
       </c>
       <c r="BD11" t="inlineStr">
         <is>
-          <t>0.3942</t>
+          <t>0.5055</t>
         </is>
       </c>
       <c r="BE11" t="inlineStr">
         <is>
-          <t>0.1474</t>
+          <t>0.2189</t>
         </is>
       </c>
       <c r="BF11" t="inlineStr">
         <is>
-          <t>37.54</t>
+          <t>29.3</t>
         </is>
       </c>
       <c r="BG11" t="inlineStr">
@@ -3608,7 +3584,7 @@
         </is>
       </c>
       <c r="L12" t="n">
-        <v>48</v>
+        <v>48.6</v>
       </c>
       <c r="M12" t="inlineStr">
         <is>
@@ -3622,7 +3598,7 @@
       </c>
       <c r="O12" t="inlineStr">
         <is>
-          <t>Projected Lineup, Premium Lineup Spot</t>
+          <t>Premium Lineup Spot</t>
         </is>
       </c>
       <c r="P12" t="n">
@@ -3635,7 +3611,7 @@
         <v>58.1</v>
       </c>
       <c r="S12" t="n">
-        <v>92.09999999999999</v>
+        <v>96.59999999999999</v>
       </c>
       <c r="T12" t="n">
         <v>50</v>
@@ -3645,39 +3621,35 @@
       </c>
       <c r="V12" t="inlineStr">
         <is>
+          <t>Yes</t>
+        </is>
+      </c>
+      <c r="W12" t="inlineStr">
+        <is>
+          <t>Yes</t>
+        </is>
+      </c>
+      <c r="X12" t="inlineStr">
+        <is>
+          <t>3</t>
+        </is>
+      </c>
+      <c r="Y12" t="inlineStr">
+        <is>
+          <t>Yes</t>
+        </is>
+      </c>
+      <c r="Z12" t="inlineStr">
+        <is>
           <t>No</t>
         </is>
       </c>
-      <c r="W12" t="inlineStr">
-        <is>
-          <t>No</t>
-        </is>
-      </c>
-      <c r="X12" t="inlineStr">
-        <is>
-          <t>3</t>
-        </is>
-      </c>
-      <c r="Y12" t="inlineStr">
-        <is>
-          <t>Yes</t>
-        </is>
-      </c>
-      <c r="Z12" t="inlineStr">
-        <is>
-          <t>Yes</t>
-        </is>
-      </c>
       <c r="AA12" t="inlineStr">
         <is>
-          <t>RotoWire projected lineup; MLB probable pitchers</t>
-        </is>
-      </c>
-      <c r="AB12" t="inlineStr">
-        <is>
-          <t>lineup projected / unconfirmed</t>
-        </is>
-      </c>
+          <t>MLB Stats API; RotoWire</t>
+        </is>
+      </c>
+      <c r="AB12" t="inlineStr"/>
       <c r="AC12" t="inlineStr">
         <is>
           <t>H:2026/2025 P:2026/2025</t>
@@ -3843,24 +3815,24 @@
       </c>
       <c r="B13" t="inlineStr">
         <is>
-          <t>514888</t>
+          <t>630105</t>
         </is>
       </c>
       <c r="C13" t="inlineStr">
         <is>
-          <t>Jose Altuve</t>
+          <t>Jake Cronenworth</t>
         </is>
       </c>
       <c r="D13" t="inlineStr">
         <is>
+          <t>SD</t>
+        </is>
+      </c>
+      <c r="E13" t="inlineStr">
+        <is>
           <t>HOU</t>
         </is>
       </c>
-      <c r="E13" t="inlineStr">
-        <is>
-          <t>SD</t>
-        </is>
-      </c>
       <c r="F13" t="inlineStr">
         <is>
           <t>2026-08-10T00:20:00Z</t>
@@ -3873,17 +3845,17 @@
       </c>
       <c r="H13" t="inlineStr">
         <is>
-          <t>6</t>
+          <t>2</t>
         </is>
       </c>
       <c r="I13" t="inlineStr">
         <is>
-          <t>Randy Vásquez</t>
+          <t>Cristian Javier</t>
         </is>
       </c>
       <c r="J13" t="inlineStr">
         <is>
-          <t>681190</t>
+          <t>664299</t>
         </is>
       </c>
       <c r="K13" t="inlineStr">
@@ -3892,7 +3864,7 @@
         </is>
       </c>
       <c r="L13" t="n">
-        <v>46.5</v>
+        <v>46.1</v>
       </c>
       <c r="M13" t="inlineStr">
         <is>
@@ -3906,62 +3878,58 @@
       </c>
       <c r="O13" t="inlineStr">
         <is>
-          <t>Projected Lineup</t>
+          <t>Premium Lineup Spot, Platoon Edge</t>
         </is>
       </c>
       <c r="P13" t="n">
-        <v>15.5</v>
+        <v>17.5</v>
       </c>
       <c r="Q13" t="n">
-        <v>62.7</v>
+        <v>39</v>
       </c>
       <c r="R13" t="n">
         <v>58.1</v>
       </c>
       <c r="S13" t="n">
-        <v>71.7</v>
+        <v>100</v>
       </c>
       <c r="T13" t="n">
-        <v>50</v>
+        <v>80</v>
       </c>
       <c r="U13" t="n">
-        <v>61.4</v>
+        <v>20.9</v>
       </c>
       <c r="V13" t="inlineStr">
         <is>
+          <t>Yes</t>
+        </is>
+      </c>
+      <c r="W13" t="inlineStr">
+        <is>
+          <t>Yes</t>
+        </is>
+      </c>
+      <c r="X13" t="inlineStr">
+        <is>
+          <t>2</t>
+        </is>
+      </c>
+      <c r="Y13" t="inlineStr">
+        <is>
+          <t>Yes</t>
+        </is>
+      </c>
+      <c r="Z13" t="inlineStr">
+        <is>
           <t>No</t>
         </is>
       </c>
-      <c r="W13" t="inlineStr">
-        <is>
-          <t>No</t>
-        </is>
-      </c>
-      <c r="X13" t="inlineStr">
-        <is>
-          <t>6</t>
-        </is>
-      </c>
-      <c r="Y13" t="inlineStr">
-        <is>
-          <t>Yes</t>
-        </is>
-      </c>
-      <c r="Z13" t="inlineStr">
-        <is>
-          <t>Yes</t>
-        </is>
-      </c>
       <c r="AA13" t="inlineStr">
         <is>
-          <t>RotoWire projected lineup; MLB probable pitchers</t>
-        </is>
-      </c>
-      <c r="AB13" t="inlineStr">
-        <is>
-          <t>lineup projected / unconfirmed</t>
-        </is>
-      </c>
+          <t>MLB Stats API; RotoWire</t>
+        </is>
+      </c>
+      <c r="AB13" t="inlineStr"/>
       <c r="AC13" t="inlineStr">
         <is>
           <t>H:2026/2025 P:2026/2025</t>
@@ -3981,7 +3949,7 @@
       </c>
       <c r="AH13" t="inlineStr">
         <is>
-          <t>11</t>
+          <t>7</t>
         </is>
       </c>
       <c r="AI13" t="inlineStr">
@@ -3991,117 +3959,117 @@
       </c>
       <c r="AJ13" t="inlineStr">
         <is>
-          <t>1</t>
+          <t>0</t>
         </is>
       </c>
       <c r="AK13" t="inlineStr">
         <is>
-          <t>Contact streak: 11/27 over last 7 games</t>
+          <t>Last 7 games: 7/27, 0 HR</t>
         </is>
       </c>
       <c r="AL13" t="inlineStr">
         <is>
-          <t>same-side matchup; pitcher baseline 11.0% barrel, 14.6 HR allowed</t>
+          <t>platoon edge; pitcher baseline 7.7% barrel, 3.7 HR allowed</t>
         </is>
       </c>
       <c r="AM13" t="inlineStr">
         <is>
-          <t>neutral batted-ball profile; pitcher fly-ball pressure modest</t>
+          <t>neutral batted-ball profile; pitcher allows elevated contact</t>
         </is>
       </c>
       <c r="AN13" t="inlineStr">
         <is>
-          <t>5.57</t>
+          <t>4.8</t>
         </is>
       </c>
       <c r="AO13" t="inlineStr">
         <is>
-          <t>31.88</t>
+          <t>33.75</t>
         </is>
       </c>
       <c r="AP13" t="inlineStr">
         <is>
-          <t>85.52</t>
+          <t>87.73</t>
         </is>
       </c>
       <c r="AQ13" t="inlineStr">
         <is>
-          <t>97.1381</t>
+          <t>98.1545</t>
         </is>
       </c>
       <c r="AR13" t="inlineStr">
         <is>
-          <t>0.3511</t>
+          <t>0.3355</t>
         </is>
       </c>
       <c r="AS13" t="inlineStr">
         <is>
-          <t>0.1225</t>
+          <t>0.1063</t>
         </is>
       </c>
       <c r="AT13" t="inlineStr">
         <is>
-          <t>0.286</t>
+          <t>0.3022</t>
         </is>
       </c>
       <c r="AU13" t="inlineStr">
         <is>
-          <t>69.07</t>
+          <t>71.39</t>
         </is>
       </c>
       <c r="AV13" t="inlineStr">
         <is>
-          <t>9.78</t>
+          <t>17.39</t>
         </is>
       </c>
       <c r="AW13" t="inlineStr">
         <is>
-          <t>46.2</t>
+          <t>31.54</t>
         </is>
       </c>
       <c r="AX13" t="inlineStr">
         <is>
-          <t>22.3</t>
+          <t>21.95</t>
         </is>
       </c>
       <c r="AY13" t="inlineStr">
         <is>
-          <t>16.9</t>
+          <t>5.4</t>
         </is>
       </c>
       <c r="AZ13" t="inlineStr">
         <is>
-          <t>0.1602</t>
+          <t>0.0876</t>
         </is>
       </c>
       <c r="BA13" t="inlineStr">
         <is>
-          <t>11.04</t>
+          <t>7.69</t>
         </is>
       </c>
       <c r="BB13" t="inlineStr">
         <is>
-          <t>43.01</t>
+          <t>37.81</t>
         </is>
       </c>
       <c r="BC13" t="inlineStr">
         <is>
-          <t>90.71</t>
+          <t>89.39</t>
         </is>
       </c>
       <c r="BD13" t="inlineStr">
         <is>
-          <t>0.5055</t>
+          <t>0.3942</t>
         </is>
       </c>
       <c r="BE13" t="inlineStr">
         <is>
-          <t>0.2189</t>
+          <t>0.1474</t>
         </is>
       </c>
       <c r="BF13" t="inlineStr">
         <is>
-          <t>29.3</t>
+          <t>37.54</t>
         </is>
       </c>
       <c r="BG13" t="inlineStr">
@@ -4127,24 +4095,24 @@
       </c>
       <c r="B14" t="inlineStr">
         <is>
-          <t>630105</t>
+          <t>673237</t>
         </is>
       </c>
       <c r="C14" t="inlineStr">
         <is>
-          <t>Jake Cronenworth</t>
+          <t>Yainer Diaz</t>
         </is>
       </c>
       <c r="D14" t="inlineStr">
         <is>
+          <t>HOU</t>
+        </is>
+      </c>
+      <c r="E14" t="inlineStr">
+        <is>
           <t>SD</t>
         </is>
       </c>
-      <c r="E14" t="inlineStr">
-        <is>
-          <t>HOU</t>
-        </is>
-      </c>
       <c r="F14" t="inlineStr">
         <is>
           <t>2026-08-10T00:20:00Z</t>
@@ -4157,17 +4125,17 @@
       </c>
       <c r="H14" t="inlineStr">
         <is>
-          <t>2</t>
+          <t>8</t>
         </is>
       </c>
       <c r="I14" t="inlineStr">
         <is>
-          <t>Cristian Javier</t>
+          <t>Randy Vásquez</t>
         </is>
       </c>
       <c r="J14" t="inlineStr">
         <is>
-          <t>664299</t>
+          <t>681190</t>
         </is>
       </c>
       <c r="K14" t="inlineStr">
@@ -4176,7 +4144,7 @@
         </is>
       </c>
       <c r="L14" t="n">
-        <v>46.1</v>
+        <v>45.9</v>
       </c>
       <c r="M14" t="inlineStr">
         <is>
@@ -4190,26 +4158,26 @@
       </c>
       <c r="O14" t="inlineStr">
         <is>
-          <t>Premium Lineup Spot, Platoon Edge</t>
+          <t>No major boost</t>
         </is>
       </c>
       <c r="P14" t="n">
-        <v>17.5</v>
+        <v>28.6</v>
       </c>
       <c r="Q14" t="n">
-        <v>39</v>
+        <v>62.7</v>
       </c>
       <c r="R14" t="n">
         <v>58.1</v>
       </c>
       <c r="S14" t="n">
-        <v>100</v>
+        <v>52.4</v>
       </c>
       <c r="T14" t="n">
-        <v>80</v>
+        <v>50</v>
       </c>
       <c r="U14" t="n">
-        <v>20.9</v>
+        <v>17.7</v>
       </c>
       <c r="V14" t="inlineStr">
         <is>
@@ -4223,7 +4191,7 @@
       </c>
       <c r="X14" t="inlineStr">
         <is>
-          <t>2</t>
+          <t>8</t>
         </is>
       </c>
       <c r="Y14" t="inlineStr">
@@ -4261,12 +4229,12 @@
       </c>
       <c r="AH14" t="inlineStr">
         <is>
-          <t>7</t>
+          <t>5</t>
         </is>
       </c>
       <c r="AI14" t="inlineStr">
         <is>
-          <t>27</t>
+          <t>21</t>
         </is>
       </c>
       <c r="AJ14" t="inlineStr">
@@ -4276,112 +4244,112 @@
       </c>
       <c r="AK14" t="inlineStr">
         <is>
-          <t>Last 7 games: 7/27, 0 HR</t>
+          <t>Last 7 games: 5/21, 0 HR</t>
         </is>
       </c>
       <c r="AL14" t="inlineStr">
         <is>
-          <t>platoon edge; pitcher baseline 7.7% barrel, 3.7 HR allowed</t>
+          <t>same-side matchup; pitcher baseline 11.0% barrel, 14.6 HR allowed</t>
         </is>
       </c>
       <c r="AM14" t="inlineStr">
         <is>
-          <t>neutral batted-ball profile; pitcher allows elevated contact</t>
+          <t>neutral batted-ball profile; pitcher fly-ball pressure modest</t>
         </is>
       </c>
       <c r="AN14" t="inlineStr">
         <is>
-          <t>4.8</t>
+          <t>6.66</t>
         </is>
       </c>
       <c r="AO14" t="inlineStr">
         <is>
-          <t>33.75</t>
+          <t>36.88</t>
         </is>
       </c>
       <c r="AP14" t="inlineStr">
         <is>
-          <t>87.73</t>
+          <t>88.22</t>
         </is>
       </c>
       <c r="AQ14" t="inlineStr">
         <is>
-          <t>98.1545</t>
+          <t>99.4273</t>
         </is>
       </c>
       <c r="AR14" t="inlineStr">
         <is>
-          <t>0.3355</t>
+          <t>0.4244</t>
         </is>
       </c>
       <c r="AS14" t="inlineStr">
         <is>
-          <t>0.1063</t>
+          <t>0.1557</t>
         </is>
       </c>
       <c r="AT14" t="inlineStr">
         <is>
-          <t>0.3022</t>
+          <t>0.3127</t>
         </is>
       </c>
       <c r="AU14" t="inlineStr">
         <is>
-          <t>71.39</t>
+          <t>72.48</t>
         </is>
       </c>
       <c r="AV14" t="inlineStr">
         <is>
-          <t>17.39</t>
+          <t>21.39</t>
         </is>
       </c>
       <c r="AW14" t="inlineStr">
         <is>
-          <t>31.54</t>
+          <t>36.35</t>
         </is>
       </c>
       <c r="AX14" t="inlineStr">
         <is>
-          <t>21.95</t>
+          <t>19.1</t>
         </is>
       </c>
       <c r="AY14" t="inlineStr">
         <is>
-          <t>5.4</t>
+          <t>11.6</t>
         </is>
       </c>
       <c r="AZ14" t="inlineStr">
         <is>
-          <t>0.0876</t>
+          <t>0.1533</t>
         </is>
       </c>
       <c r="BA14" t="inlineStr">
         <is>
-          <t>7.69</t>
+          <t>11.04</t>
         </is>
       </c>
       <c r="BB14" t="inlineStr">
         <is>
-          <t>37.81</t>
+          <t>43.01</t>
         </is>
       </c>
       <c r="BC14" t="inlineStr">
         <is>
-          <t>89.39</t>
+          <t>90.71</t>
         </is>
       </c>
       <c r="BD14" t="inlineStr">
         <is>
-          <t>0.3942</t>
+          <t>0.5055</t>
         </is>
       </c>
       <c r="BE14" t="inlineStr">
         <is>
-          <t>0.1474</t>
+          <t>0.2189</t>
         </is>
       </c>
       <c r="BF14" t="inlineStr">
         <is>
-          <t>37.54</t>
+          <t>29.3</t>
         </is>
       </c>
       <c r="BG14" t="inlineStr">
@@ -4687,12 +4655,12 @@
       </c>
       <c r="B16" t="inlineStr">
         <is>
-          <t>673237</t>
+          <t>664774</t>
         </is>
       </c>
       <c r="C16" t="inlineStr">
         <is>
-          <t>Yainer Diaz</t>
+          <t>LaMonte Wade Jr.</t>
         </is>
       </c>
       <c r="D16" t="inlineStr">
@@ -4717,7 +4685,7 @@
       </c>
       <c r="H16" t="inlineStr">
         <is>
-          <t>8</t>
+          <t>9</t>
         </is>
       </c>
       <c r="I16" t="inlineStr">
@@ -4736,7 +4704,7 @@
         </is>
       </c>
       <c r="L16" t="n">
-        <v>45.3</v>
+        <v>43.7</v>
       </c>
       <c r="M16" t="inlineStr">
         <is>
@@ -4750,11 +4718,11 @@
       </c>
       <c r="O16" t="inlineStr">
         <is>
-          <t>Projected Lineup</t>
+          <t>Platoon Edge</t>
         </is>
       </c>
       <c r="P16" t="n">
-        <v>28.6</v>
+        <v>13.9</v>
       </c>
       <c r="Q16" t="n">
         <v>62.7</v>
@@ -4763,49 +4731,45 @@
         <v>58.1</v>
       </c>
       <c r="S16" t="n">
-        <v>47.9</v>
+        <v>44.8</v>
       </c>
       <c r="T16" t="n">
-        <v>50</v>
+        <v>80</v>
       </c>
       <c r="U16" t="n">
-        <v>17.7</v>
+        <v>38.3</v>
       </c>
       <c r="V16" t="inlineStr">
         <is>
+          <t>Yes</t>
+        </is>
+      </c>
+      <c r="W16" t="inlineStr">
+        <is>
+          <t>Yes</t>
+        </is>
+      </c>
+      <c r="X16" t="inlineStr">
+        <is>
+          <t>9</t>
+        </is>
+      </c>
+      <c r="Y16" t="inlineStr">
+        <is>
+          <t>Yes</t>
+        </is>
+      </c>
+      <c r="Z16" t="inlineStr">
+        <is>
           <t>No</t>
         </is>
       </c>
-      <c r="W16" t="inlineStr">
-        <is>
-          <t>No</t>
-        </is>
-      </c>
-      <c r="X16" t="inlineStr">
-        <is>
-          <t>8</t>
-        </is>
-      </c>
-      <c r="Y16" t="inlineStr">
-        <is>
-          <t>Yes</t>
-        </is>
-      </c>
-      <c r="Z16" t="inlineStr">
-        <is>
-          <t>Yes</t>
-        </is>
-      </c>
       <c r="AA16" t="inlineStr">
         <is>
-          <t>RotoWire projected lineup; MLB probable pitchers</t>
-        </is>
-      </c>
-      <c r="AB16" t="inlineStr">
-        <is>
-          <t>lineup projected / unconfirmed</t>
-        </is>
-      </c>
+          <t>MLB Stats API; RotoWire</t>
+        </is>
+      </c>
+      <c r="AB16" t="inlineStr"/>
       <c r="AC16" t="inlineStr">
         <is>
           <t>H:2026/2025 P:2026/2025</t>
@@ -4825,12 +4789,12 @@
       </c>
       <c r="AH16" t="inlineStr">
         <is>
-          <t>5</t>
+          <t>6</t>
         </is>
       </c>
       <c r="AI16" t="inlineStr">
         <is>
-          <t>21</t>
+          <t>16</t>
         </is>
       </c>
       <c r="AJ16" t="inlineStr">
@@ -4840,12 +4804,12 @@
       </c>
       <c r="AK16" t="inlineStr">
         <is>
-          <t>Last 7 games: 5/21, 0 HR</t>
+          <t>Contact streak: 6/16 over last 7 games</t>
         </is>
       </c>
       <c r="AL16" t="inlineStr">
         <is>
-          <t>same-side matchup; pitcher baseline 11.0% barrel, 14.6 HR allowed</t>
+          <t>platoon edge; pitcher baseline 11.0% barrel, 14.6 HR allowed</t>
         </is>
       </c>
       <c r="AM16" t="inlineStr">
@@ -4855,67 +4819,67 @@
       </c>
       <c r="AN16" t="inlineStr">
         <is>
-          <t>6.66</t>
+          <t>4.01</t>
         </is>
       </c>
       <c r="AO16" t="inlineStr">
         <is>
-          <t>36.88</t>
+          <t>32.01</t>
         </is>
       </c>
       <c r="AP16" t="inlineStr">
         <is>
-          <t>88.22</t>
+          <t>86.76</t>
         </is>
       </c>
       <c r="AQ16" t="inlineStr">
         <is>
-          <t>99.4273</t>
+          <t>97.8228</t>
         </is>
       </c>
       <c r="AR16" t="inlineStr">
         <is>
-          <t>0.4244</t>
+          <t>0.2958</t>
         </is>
       </c>
       <c r="AS16" t="inlineStr">
         <is>
-          <t>0.1557</t>
+          <t>0.1013</t>
         </is>
       </c>
       <c r="AT16" t="inlineStr">
         <is>
-          <t>0.3127</t>
+          <t>0.2838</t>
         </is>
       </c>
       <c r="AU16" t="inlineStr">
         <is>
-          <t>72.48</t>
+          <t>70.98</t>
         </is>
       </c>
       <c r="AV16" t="inlineStr">
         <is>
-          <t>21.39</t>
+          <t>8.78</t>
         </is>
       </c>
       <c r="AW16" t="inlineStr">
         <is>
-          <t>36.35</t>
+          <t>38.82</t>
         </is>
       </c>
       <c r="AX16" t="inlineStr">
         <is>
-          <t>19.1</t>
+          <t>27.47</t>
         </is>
       </c>
       <c r="AY16" t="inlineStr">
         <is>
-          <t>11.6</t>
+          <t>2.0</t>
         </is>
       </c>
       <c r="AZ16" t="inlineStr">
         <is>
-          <t>0.1533</t>
+          <t>0.1248</t>
         </is>
       </c>
       <c r="BA16" t="inlineStr">
@@ -6186,7 +6150,7 @@
         </is>
       </c>
       <c r="L2" t="n">
-        <v>73.40000000000001</v>
+        <v>74</v>
       </c>
       <c r="M2" t="inlineStr">
         <is>
@@ -6200,7 +6164,7 @@
       </c>
       <c r="O2" t="inlineStr">
         <is>
-          <t>Projected Lineup, Elite Power, Strong Barrel, Premium Lineup Spot, Platoon Edge</t>
+          <t>Elite Power, Strong Barrel, Premium Lineup Spot, Platoon Edge</t>
         </is>
       </c>
       <c r="P2" t="n">
@@ -6213,7 +6177,7 @@
         <v>58.1</v>
       </c>
       <c r="S2" t="n">
-        <v>95.5</v>
+        <v>100</v>
       </c>
       <c r="T2" t="n">
         <v>80</v>
@@ -6223,39 +6187,35 @@
       </c>
       <c r="V2" t="inlineStr">
         <is>
+          <t>Yes</t>
+        </is>
+      </c>
+      <c r="W2" t="inlineStr">
+        <is>
+          <t>Yes</t>
+        </is>
+      </c>
+      <c r="X2" t="inlineStr">
+        <is>
+          <t>2</t>
+        </is>
+      </c>
+      <c r="Y2" t="inlineStr">
+        <is>
+          <t>Yes</t>
+        </is>
+      </c>
+      <c r="Z2" t="inlineStr">
+        <is>
           <t>No</t>
         </is>
       </c>
-      <c r="W2" t="inlineStr">
-        <is>
-          <t>No</t>
-        </is>
-      </c>
-      <c r="X2" t="inlineStr">
-        <is>
-          <t>2</t>
-        </is>
-      </c>
-      <c r="Y2" t="inlineStr">
-        <is>
-          <t>Yes</t>
-        </is>
-      </c>
-      <c r="Z2" t="inlineStr">
-        <is>
-          <t>Yes</t>
-        </is>
-      </c>
       <c r="AA2" t="inlineStr">
         <is>
-          <t>RotoWire projected lineup; MLB probable pitchers</t>
-        </is>
-      </c>
-      <c r="AB2" t="inlineStr">
-        <is>
-          <t>lineup projected / unconfirmed</t>
-        </is>
-      </c>
+          <t>MLB Stats API; RotoWire</t>
+        </is>
+      </c>
+      <c r="AB2" t="inlineStr"/>
       <c r="AC2" t="inlineStr">
         <is>
           <t>H:2026/2025 P:2026/2025</t>
@@ -6421,24 +6381,24 @@
       </c>
       <c r="B3" t="inlineStr">
         <is>
-          <t>701538</t>
+          <t>666211</t>
         </is>
       </c>
       <c r="C3" t="inlineStr">
         <is>
-          <t>Jackson Merrill</t>
+          <t>Taylor Trammell</t>
         </is>
       </c>
       <c r="D3" t="inlineStr">
         <is>
+          <t>HOU</t>
+        </is>
+      </c>
+      <c r="E3" t="inlineStr">
+        <is>
           <t>SD</t>
         </is>
       </c>
-      <c r="E3" t="inlineStr">
-        <is>
-          <t>HOU</t>
-        </is>
-      </c>
       <c r="F3" t="inlineStr">
         <is>
           <t>2026-08-10T00:20:00Z</t>
@@ -6456,12 +6416,12 @@
       </c>
       <c r="I3" t="inlineStr">
         <is>
-          <t>Cristian Javier</t>
+          <t>Randy Vásquez</t>
         </is>
       </c>
       <c r="J3" t="inlineStr">
         <is>
-          <t>664299</t>
+          <t>681190</t>
         </is>
       </c>
       <c r="K3" t="inlineStr">
@@ -6470,7 +6430,7 @@
         </is>
       </c>
       <c r="L3" t="n">
-        <v>56.9</v>
+        <v>59</v>
       </c>
       <c r="M3" t="inlineStr">
         <is>
@@ -6484,14 +6444,14 @@
       </c>
       <c r="O3" t="inlineStr">
         <is>
-          <t>Strong Barrel, Platoon Edge, Hot Hitter/Streak</t>
+          <t>Strong Barrel, Platoon Edge</t>
         </is>
       </c>
       <c r="P3" t="n">
-        <v>48.3</v>
+        <v>40.5</v>
       </c>
       <c r="Q3" t="n">
-        <v>39</v>
+        <v>62.7</v>
       </c>
       <c r="R3" t="n">
         <v>58.1</v>
@@ -6503,7 +6463,7 @@
         <v>80</v>
       </c>
       <c r="U3" t="n">
-        <v>72.2</v>
+        <v>51.3</v>
       </c>
       <c r="V3" t="inlineStr">
         <is>
@@ -6555,12 +6515,12 @@
       </c>
       <c r="AH3" t="inlineStr">
         <is>
-          <t>10</t>
+          <t>5</t>
         </is>
       </c>
       <c r="AI3" t="inlineStr">
         <is>
-          <t>28</t>
+          <t>23</t>
         </is>
       </c>
       <c r="AJ3" t="inlineStr">
@@ -6575,107 +6535,107 @@
       </c>
       <c r="AL3" t="inlineStr">
         <is>
-          <t>platoon edge; pitcher baseline 7.7% barrel, 3.7 HR allowed</t>
+          <t>platoon edge; pitcher baseline 11.0% barrel, 14.6 HR allowed</t>
         </is>
       </c>
       <c r="AM3" t="inlineStr">
         <is>
-          <t>neutral batted-ball profile; pitcher allows elevated contact</t>
+          <t>neutral batted-ball profile; pitcher fly-ball pressure modest</t>
         </is>
       </c>
       <c r="AN3" t="inlineStr">
         <is>
-          <t>11.46</t>
+          <t>11.02</t>
         </is>
       </c>
       <c r="AO3" t="inlineStr">
         <is>
-          <t>45.35</t>
+          <t>36.73</t>
         </is>
       </c>
       <c r="AP3" t="inlineStr">
         <is>
-          <t>89.98</t>
+          <t>89.11</t>
         </is>
       </c>
       <c r="AQ3" t="inlineStr">
         <is>
-          <t>100.5329</t>
+          <t>100.7812</t>
         </is>
       </c>
       <c r="AR3" t="inlineStr">
         <is>
-          <t>0.4627</t>
+          <t>0.3854</t>
         </is>
       </c>
       <c r="AS3" t="inlineStr">
         <is>
-          <t>0.2053</t>
+          <t>0.1809</t>
         </is>
       </c>
       <c r="AT3" t="inlineStr">
         <is>
-          <t>0.3309</t>
+          <t>0.3025</t>
         </is>
       </c>
       <c r="AU3" t="inlineStr">
         <is>
-          <t>72.88</t>
+          <t>75.44</t>
         </is>
       </c>
       <c r="AV3" t="inlineStr">
         <is>
-          <t>26.98</t>
+          <t>55.07</t>
         </is>
       </c>
       <c r="AW3" t="inlineStr">
         <is>
-          <t>37.91</t>
+          <t>46.19</t>
         </is>
       </c>
       <c r="AX3" t="inlineStr">
         <is>
-          <t>28.94</t>
+          <t>30.09</t>
         </is>
       </c>
       <c r="AY3" t="inlineStr">
         <is>
-          <t>16.7</t>
+          <t>5.8</t>
         </is>
       </c>
       <c r="AZ3" t="inlineStr">
         <is>
-          <t>0.172</t>
+          <t>0.1696</t>
         </is>
       </c>
       <c r="BA3" t="inlineStr">
         <is>
-          <t>7.69</t>
+          <t>11.04</t>
         </is>
       </c>
       <c r="BB3" t="inlineStr">
         <is>
-          <t>37.81</t>
+          <t>43.01</t>
         </is>
       </c>
       <c r="BC3" t="inlineStr">
         <is>
-          <t>89.39</t>
+          <t>90.71</t>
         </is>
       </c>
       <c r="BD3" t="inlineStr">
         <is>
-          <t>0.3942</t>
+          <t>0.5055</t>
         </is>
       </c>
       <c r="BE3" t="inlineStr">
         <is>
-          <t>0.1474</t>
+          <t>0.2189</t>
         </is>
       </c>
       <c r="BF3" t="inlineStr">
         <is>
-          <t>37.54</t>
+          <t>29.3</t>
         </is>
       </c>
       <c r="BG3" t="inlineStr">
@@ -6701,24 +6661,24 @@
       </c>
       <c r="B4" t="inlineStr">
         <is>
-          <t>572233</t>
+          <t>701538</t>
         </is>
       </c>
       <c r="C4" t="inlineStr">
         <is>
-          <t>Christian Walker</t>
+          <t>Jackson Merrill</t>
         </is>
       </c>
       <c r="D4" t="inlineStr">
         <is>
+          <t>SD</t>
+        </is>
+      </c>
+      <c r="E4" t="inlineStr">
+        <is>
           <t>HOU</t>
         </is>
       </c>
-      <c r="E4" t="inlineStr">
-        <is>
-          <t>SD</t>
-        </is>
-      </c>
       <c r="F4" t="inlineStr">
         <is>
           <t>2026-08-10T00:20:00Z</t>
@@ -6736,12 +6696,12 @@
       </c>
       <c r="I4" t="inlineStr">
         <is>
-          <t>Randy Vásquez</t>
+          <t>Cristian Javier</t>
         </is>
       </c>
       <c r="J4" t="inlineStr">
         <is>
-          <t>681190</t>
+          <t>664299</t>
         </is>
       </c>
       <c r="K4" t="inlineStr">
@@ -6750,7 +6710,7 @@
         </is>
       </c>
       <c r="L4" t="n">
-        <v>55.6</v>
+        <v>56.9</v>
       </c>
       <c r="M4" t="inlineStr">
         <is>
@@ -6764,62 +6724,58 @@
       </c>
       <c r="O4" t="inlineStr">
         <is>
-          <t>Projected Lineup, Strong Barrel</t>
+          <t>Strong Barrel, Platoon Edge, Hot Hitter/Streak</t>
         </is>
       </c>
       <c r="P4" t="n">
-        <v>42.9</v>
+        <v>48.3</v>
       </c>
       <c r="Q4" t="n">
-        <v>62.7</v>
+        <v>39</v>
       </c>
       <c r="R4" t="n">
         <v>58.1</v>
       </c>
       <c r="S4" t="n">
-        <v>81.90000000000001</v>
+        <v>86.40000000000001</v>
       </c>
       <c r="T4" t="n">
-        <v>50</v>
+        <v>80</v>
       </c>
       <c r="U4" t="n">
-        <v>33.9</v>
+        <v>72.2</v>
       </c>
       <c r="V4" t="inlineStr">
         <is>
+          <t>Yes</t>
+        </is>
+      </c>
+      <c r="W4" t="inlineStr">
+        <is>
+          <t>Yes</t>
+        </is>
+      </c>
+      <c r="X4" t="inlineStr">
+        <is>
+          <t>5</t>
+        </is>
+      </c>
+      <c r="Y4" t="inlineStr">
+        <is>
+          <t>Yes</t>
+        </is>
+      </c>
+      <c r="Z4" t="inlineStr">
+        <is>
           <t>No</t>
         </is>
       </c>
-      <c r="W4" t="inlineStr">
-        <is>
-          <t>No</t>
-        </is>
-      </c>
-      <c r="X4" t="inlineStr">
-        <is>
-          <t>5</t>
-        </is>
-      </c>
-      <c r="Y4" t="inlineStr">
-        <is>
-          <t>Yes</t>
-        </is>
-      </c>
-      <c r="Z4" t="inlineStr">
-        <is>
-          <t>Yes</t>
-        </is>
-      </c>
       <c r="AA4" t="inlineStr">
         <is>
-          <t>RotoWire projected lineup; MLB probable pitchers</t>
-        </is>
-      </c>
-      <c r="AB4" t="inlineStr">
-        <is>
-          <t>lineup projected / unconfirmed</t>
-        </is>
-      </c>
+          <t>MLB Stats API; RotoWire</t>
+        </is>
+      </c>
+      <c r="AB4" t="inlineStr"/>
       <c r="AC4" t="inlineStr">
         <is>
           <t>H:2026/2025 P:2026/2025</t>
@@ -6839,127 +6795,127 @@
       </c>
       <c r="AH4" t="inlineStr">
         <is>
-          <t>9</t>
+          <t>10</t>
         </is>
       </c>
       <c r="AI4" t="inlineStr">
         <is>
-          <t>26</t>
+          <t>28</t>
         </is>
       </c>
       <c r="AJ4" t="inlineStr">
         <is>
-          <t>0</t>
+          <t>2</t>
         </is>
       </c>
       <c r="AK4" t="inlineStr">
         <is>
-          <t>Contact streak: 9/26 over last 7 games</t>
+          <t>Hot streak: 2 HR in last 7 games</t>
         </is>
       </c>
       <c r="AL4" t="inlineStr">
         <is>
-          <t>same-side matchup; pitcher baseline 11.0% barrel, 14.6 HR allowed</t>
+          <t>platoon edge; pitcher baseline 7.7% barrel, 3.7 HR allowed</t>
         </is>
       </c>
       <c r="AM4" t="inlineStr">
         <is>
-          <t>neutral batted-ball profile; pitcher fly-ball pressure modest</t>
+          <t>neutral batted-ball profile; pitcher allows elevated contact</t>
         </is>
       </c>
       <c r="AN4" t="inlineStr">
         <is>
-          <t>10.59</t>
+          <t>11.46</t>
         </is>
       </c>
       <c r="AO4" t="inlineStr">
         <is>
-          <t>43.51</t>
+          <t>45.35</t>
         </is>
       </c>
       <c r="AP4" t="inlineStr">
         <is>
-          <t>89.92</t>
+          <t>89.98</t>
         </is>
       </c>
       <c r="AQ4" t="inlineStr">
         <is>
-          <t>101.6508</t>
+          <t>100.5329</t>
         </is>
       </c>
       <c r="AR4" t="inlineStr">
         <is>
-          <t>0.4042</t>
+          <t>0.4627</t>
         </is>
       </c>
       <c r="AS4" t="inlineStr">
         <is>
-          <t>0.175</t>
+          <t>0.2053</t>
         </is>
       </c>
       <c r="AT4" t="inlineStr">
         <is>
-          <t>0.3098</t>
+          <t>0.3309</t>
         </is>
       </c>
       <c r="AU4" t="inlineStr">
         <is>
-          <t>74.31</t>
+          <t>72.88</t>
         </is>
       </c>
       <c r="AV4" t="inlineStr">
         <is>
-          <t>43.55</t>
+          <t>26.98</t>
         </is>
       </c>
       <c r="AW4" t="inlineStr">
         <is>
-          <t>43.04</t>
+          <t>37.91</t>
         </is>
       </c>
       <c r="AX4" t="inlineStr">
         <is>
-          <t>28.42</t>
+          <t>28.94</t>
         </is>
       </c>
       <c r="AY4" t="inlineStr">
         <is>
-          <t>23.5</t>
+          <t>16.7</t>
         </is>
       </c>
       <c r="AZ4" t="inlineStr">
         <is>
-          <t>0.2075</t>
+          <t>0.172</t>
         </is>
       </c>
       <c r="BA4" t="inlineStr">
         <is>
-          <t>11.04</t>
+          <t>7.69</t>
         </is>
       </c>
       <c r="BB4" t="inlineStr">
         <is>
-          <t>43.01</t>
+          <t>37.81</t>
         </is>
       </c>
       <c r="BC4" t="inlineStr">
         <is>
-          <t>90.71</t>
+          <t>89.39</t>
         </is>
       </c>
       <c r="BD4" t="inlineStr">
         <is>
-          <t>0.5055</t>
+          <t>0.3942</t>
         </is>
       </c>
       <c r="BE4" t="inlineStr">
         <is>
-          <t>0.2189</t>
+          <t>0.1474</t>
         </is>
       </c>
       <c r="BF4" t="inlineStr">
         <is>
-          <t>29.3</t>
+          <t>37.54</t>
         </is>
       </c>
       <c r="BG4" t="inlineStr">
@@ -6985,24 +6941,24 @@
       </c>
       <c r="B5" t="inlineStr">
         <is>
-          <t>666211</t>
+          <t>665487</t>
         </is>
       </c>
       <c r="C5" t="inlineStr">
         <is>
-          <t>Taylor Trammell</t>
+          <t>Fernando Tatis Jr.</t>
         </is>
       </c>
       <c r="D5" t="inlineStr">
         <is>
+          <t>SD</t>
+        </is>
+      </c>
+      <c r="E5" t="inlineStr">
+        <is>
           <t>HOU</t>
         </is>
       </c>
-      <c r="E5" t="inlineStr">
-        <is>
-          <t>SD</t>
-        </is>
-      </c>
       <c r="F5" t="inlineStr">
         <is>
           <t>2026-08-10T00:20:00Z</t>
@@ -7015,17 +6971,17 @@
       </c>
       <c r="H5" t="inlineStr">
         <is>
-          <t>7</t>
+          <t>1</t>
         </is>
       </c>
       <c r="I5" t="inlineStr">
         <is>
-          <t>Randy Vásquez</t>
+          <t>Cristian Javier</t>
         </is>
       </c>
       <c r="J5" t="inlineStr">
         <is>
-          <t>681190</t>
+          <t>664299</t>
         </is>
       </c>
       <c r="K5" t="inlineStr">
@@ -7034,7 +6990,7 @@
         </is>
       </c>
       <c r="L5" t="n">
-        <v>55.3</v>
+        <v>55.2</v>
       </c>
       <c r="M5" t="inlineStr">
         <is>
@@ -7048,62 +7004,58 @@
       </c>
       <c r="O5" t="inlineStr">
         <is>
-          <t>Projected Lineup, Strong Barrel, Platoon Edge</t>
+          <t>Strong Barrel, Premium Lineup Spot</t>
         </is>
       </c>
       <c r="P5" t="n">
-        <v>40.5</v>
+        <v>51.8</v>
       </c>
       <c r="Q5" t="n">
-        <v>62.7</v>
+        <v>39</v>
       </c>
       <c r="R5" t="n">
         <v>58.1</v>
       </c>
       <c r="S5" t="n">
-        <v>59.8</v>
+        <v>93.2</v>
       </c>
       <c r="T5" t="n">
-        <v>80</v>
+        <v>50</v>
       </c>
       <c r="U5" t="n">
-        <v>51.3</v>
+        <v>50.8</v>
       </c>
       <c r="V5" t="inlineStr">
         <is>
+          <t>Yes</t>
+        </is>
+      </c>
+      <c r="W5" t="inlineStr">
+        <is>
+          <t>Yes</t>
+        </is>
+      </c>
+      <c r="X5" t="inlineStr">
+        <is>
+          <t>1</t>
+        </is>
+      </c>
+      <c r="Y5" t="inlineStr">
+        <is>
+          <t>Yes</t>
+        </is>
+      </c>
+      <c r="Z5" t="inlineStr">
+        <is>
           <t>No</t>
         </is>
       </c>
-      <c r="W5" t="inlineStr">
-        <is>
-          <t>No</t>
-        </is>
-      </c>
-      <c r="X5" t="inlineStr">
-        <is>
-          <t>7</t>
-        </is>
-      </c>
-      <c r="Y5" t="inlineStr">
-        <is>
-          <t>Yes</t>
-        </is>
-      </c>
-      <c r="Z5" t="inlineStr">
-        <is>
-          <t>Yes</t>
-        </is>
-      </c>
       <c r="AA5" t="inlineStr">
         <is>
-          <t>RotoWire projected lineup; MLB probable pitchers</t>
-        </is>
-      </c>
-      <c r="AB5" t="inlineStr">
-        <is>
-          <t>lineup projected / unconfirmed</t>
-        </is>
-      </c>
+          <t>MLB Stats API; RotoWire</t>
+        </is>
+      </c>
+      <c r="AB5" t="inlineStr"/>
       <c r="AC5" t="inlineStr">
         <is>
           <t>H:2026/2025 P:2026/2025</t>
@@ -7123,12 +7075,12 @@
       </c>
       <c r="AH5" t="inlineStr">
         <is>
-          <t>5</t>
+          <t>6</t>
         </is>
       </c>
       <c r="AI5" t="inlineStr">
         <is>
-          <t>23</t>
+          <t>28</t>
         </is>
       </c>
       <c r="AJ5" t="inlineStr">
@@ -7143,107 +7095,107 @@
       </c>
       <c r="AL5" t="inlineStr">
         <is>
-          <t>platoon edge; pitcher baseline 11.0% barrel, 14.6 HR allowed</t>
+          <t>same-side matchup; pitcher baseline 7.7% barrel, 3.7 HR allowed</t>
         </is>
       </c>
       <c r="AM5" t="inlineStr">
         <is>
-          <t>neutral batted-ball profile; pitcher fly-ball pressure modest</t>
+          <t>EV profile; pitcher allows elevated contact</t>
         </is>
       </c>
       <c r="AN5" t="inlineStr">
         <is>
-          <t>11.02</t>
+          <t>11.0</t>
         </is>
       </c>
       <c r="AO5" t="inlineStr">
         <is>
-          <t>36.73</t>
+          <t>52.29</t>
         </is>
       </c>
       <c r="AP5" t="inlineStr">
         <is>
-          <t>89.11</t>
+          <t>92.53</t>
         </is>
       </c>
       <c r="AQ5" t="inlineStr">
         <is>
-          <t>100.7812</t>
+          <t>104.2616</t>
         </is>
       </c>
       <c r="AR5" t="inlineStr">
         <is>
-          <t>0.3854</t>
+          <t>0.4593</t>
         </is>
       </c>
       <c r="AS5" t="inlineStr">
         <is>
-          <t>0.1809</t>
+          <t>0.1785</t>
         </is>
       </c>
       <c r="AT5" t="inlineStr">
         <is>
-          <t>0.3025</t>
+          <t>0.3602</t>
         </is>
       </c>
       <c r="AU5" t="inlineStr">
         <is>
-          <t>75.44</t>
+          <t>75.51</t>
         </is>
       </c>
       <c r="AV5" t="inlineStr">
         <is>
-          <t>55.07</t>
+          <t>57.7</t>
         </is>
       </c>
       <c r="AW5" t="inlineStr">
         <is>
-          <t>46.19</t>
+          <t>34.24</t>
         </is>
       </c>
       <c r="AX5" t="inlineStr">
         <is>
-          <t>30.09</t>
+          <t>21.87</t>
         </is>
       </c>
       <c r="AY5" t="inlineStr">
         <is>
-          <t>5.8</t>
+          <t>14.5</t>
         </is>
       </c>
       <c r="AZ5" t="inlineStr">
         <is>
-          <t>0.1696</t>
+          <t>0.143</t>
         </is>
       </c>
       <c r="BA5" t="inlineStr">
         <is>
-          <t>11.04</t>
+          <t>7.69</t>
         </is>
       </c>
       <c r="BB5" t="inlineStr">
         <is>
-          <t>43.01</t>
+          <t>37.81</t>
         </is>
       </c>
       <c r="BC5" t="inlineStr">
         <is>
-          <t>90.71</t>
+          <t>89.39</t>
         </is>
       </c>
       <c r="BD5" t="inlineStr">
         <is>
-          <t>0.5055</t>
+          <t>0.3942</t>
         </is>
       </c>
       <c r="BE5" t="inlineStr">
         <is>
-          <t>0.2189</t>
+          <t>0.1474</t>
         </is>
       </c>
       <c r="BF5" t="inlineStr">
         <is>
-          <t>29.3</t>
+          <t>37.54</t>
         </is>
       </c>
       <c r="BG5" t="inlineStr">
@@ -7269,24 +7221,24 @@
       </c>
       <c r="B6" t="inlineStr">
         <is>
-          <t>665487</t>
+          <t>572233</t>
         </is>
       </c>
       <c r="C6" t="inlineStr">
         <is>
-          <t>Fernando Tatis Jr.</t>
+          <t>Christian Walker</t>
         </is>
       </c>
       <c r="D6" t="inlineStr">
         <is>
+          <t>HOU</t>
+        </is>
+      </c>
+      <c r="E6" t="inlineStr">
+        <is>
           <t>SD</t>
         </is>
       </c>
-      <c r="E6" t="inlineStr">
-        <is>
-          <t>HOU</t>
-        </is>
-      </c>
       <c r="F6" t="inlineStr">
         <is>
           <t>2026-08-10T00:20:00Z</t>
@@ -7299,17 +7251,17 @@
       </c>
       <c r="H6" t="inlineStr">
         <is>
-          <t>1</t>
+          <t>6</t>
         </is>
       </c>
       <c r="I6" t="inlineStr">
         <is>
-          <t>Cristian Javier</t>
+          <t>Randy Vásquez</t>
         </is>
       </c>
       <c r="J6" t="inlineStr">
         <is>
-          <t>664299</t>
+          <t>681190</t>
         </is>
       </c>
       <c r="K6" t="inlineStr">
@@ -7318,7 +7270,7 @@
         </is>
       </c>
       <c r="L6" t="n">
-        <v>55.2</v>
+        <v>54.8</v>
       </c>
       <c r="M6" t="inlineStr">
         <is>
@@ -7332,26 +7284,26 @@
       </c>
       <c r="O6" t="inlineStr">
         <is>
-          <t>Strong Barrel, Premium Lineup Spot</t>
+          <t>Strong Barrel</t>
         </is>
       </c>
       <c r="P6" t="n">
-        <v>51.8</v>
+        <v>42.9</v>
       </c>
       <c r="Q6" t="n">
-        <v>39</v>
+        <v>62.7</v>
       </c>
       <c r="R6" t="n">
         <v>58.1</v>
       </c>
       <c r="S6" t="n">
-        <v>93.2</v>
+        <v>76.2</v>
       </c>
       <c r="T6" t="n">
         <v>50</v>
       </c>
       <c r="U6" t="n">
-        <v>50.8</v>
+        <v>33.9</v>
       </c>
       <c r="V6" t="inlineStr">
         <is>
@@ -7365,7 +7317,7 @@
       </c>
       <c r="X6" t="inlineStr">
         <is>
-          <t>1</t>
+          <t>6</t>
         </is>
       </c>
       <c r="Y6" t="inlineStr">
@@ -7403,127 +7355,127 @@
       </c>
       <c r="AH6" t="inlineStr">
         <is>
-          <t>6</t>
+          <t>9</t>
         </is>
       </c>
       <c r="AI6" t="inlineStr">
         <is>
-          <t>28</t>
+          <t>26</t>
         </is>
       </c>
       <c r="AJ6" t="inlineStr">
         <is>
-          <t>2</t>
+          <t>0</t>
         </is>
       </c>
       <c r="AK6" t="inlineStr">
         <is>
-          <t>Hot streak: 2 HR in last 7 games</t>
+          <t>Contact streak: 9/26 over last 7 games</t>
         </is>
       </c>
       <c r="AL6" t="inlineStr">
         <is>
-          <t>same-side matchup; pitcher baseline 7.7% barrel, 3.7 HR allowed</t>
+          <t>same-side matchup; pitcher baseline 11.0% barrel, 14.6 HR allowed</t>
         </is>
       </c>
       <c r="AM6" t="inlineStr">
         <is>
-          <t>EV profile; pitcher allows elevated contact</t>
+          <t>neutral batted-ball profile; pitcher fly-ball pressure modest</t>
         </is>
       </c>
       <c r="AN6" t="inlineStr">
         <is>
-          <t>11.0</t>
+          <t>10.59</t>
         </is>
       </c>
       <c r="AO6" t="inlineStr">
         <is>
-          <t>52.29</t>
+          <t>43.51</t>
         </is>
       </c>
       <c r="AP6" t="inlineStr">
         <is>
-          <t>92.53</t>
+          <t>89.92</t>
         </is>
       </c>
       <c r="AQ6" t="inlineStr">
         <is>
-          <t>104.2616</t>
+          <t>101.6508</t>
         </is>
       </c>
       <c r="AR6" t="inlineStr">
         <is>
-          <t>0.4593</t>
+          <t>0.4042</t>
         </is>
       </c>
       <c r="AS6" t="inlineStr">
         <is>
-          <t>0.1785</t>
+          <t>0.175</t>
         </is>
       </c>
       <c r="AT6" t="inlineStr">
         <is>
-          <t>0.3602</t>
+          <t>0.3098</t>
         </is>
       </c>
       <c r="AU6" t="inlineStr">
         <is>
-          <t>75.51</t>
+          <t>74.31</t>
         </is>
       </c>
       <c r="AV6" t="inlineStr">
         <is>
-          <t>57.7</t>
+          <t>43.55</t>
         </is>
       </c>
       <c r="AW6" t="inlineStr">
         <is>
-          <t>34.24</t>
+          <t>43.04</t>
         </is>
       </c>
       <c r="AX6" t="inlineStr">
         <is>
-          <t>21.87</t>
+          <t>28.42</t>
         </is>
       </c>
       <c r="AY6" t="inlineStr">
         <is>
-          <t>14.5</t>
+          <t>23.5</t>
         </is>
       </c>
       <c r="AZ6" t="inlineStr">
         <is>
-          <t>0.143</t>
+          <t>0.2075</t>
         </is>
       </c>
       <c r="BA6" t="inlineStr">
         <is>
-          <t>7.69</t>
+          <t>11.04</t>
         </is>
       </c>
       <c r="BB6" t="inlineStr">
         <is>
-          <t>37.81</t>
+          <t>43.01</t>
         </is>
       </c>
       <c r="BC6" t="inlineStr">
         <is>
-          <t>89.39</t>
+          <t>90.71</t>
         </is>
       </c>
       <c r="BD6" t="inlineStr">
         <is>
-          <t>0.3942</t>
+          <t>0.5055</t>
         </is>
       </c>
       <c r="BE6" t="inlineStr">
         <is>
-          <t>0.1474</t>
+          <t>0.2189</t>
         </is>
       </c>
       <c r="BF6" t="inlineStr">
         <is>
-          <t>37.54</t>
+          <t>29.3</t>
         </is>
       </c>
       <c r="BG6" t="inlineStr">
@@ -7549,24 +7501,24 @@
       </c>
       <c r="B7" t="inlineStr">
         <is>
-          <t>662139</t>
+          <t>592518</t>
         </is>
       </c>
       <c r="C7" t="inlineStr">
         <is>
-          <t>Daulton Varsho</t>
+          <t>Manny Machado</t>
         </is>
       </c>
       <c r="D7" t="inlineStr">
         <is>
+          <t>SD</t>
+        </is>
+      </c>
+      <c r="E7" t="inlineStr">
+        <is>
           <t>HOU</t>
         </is>
       </c>
-      <c r="E7" t="inlineStr">
-        <is>
-          <t>SD</t>
-        </is>
-      </c>
       <c r="F7" t="inlineStr">
         <is>
           <t>2026-08-10T00:20:00Z</t>
@@ -7579,17 +7531,17 @@
       </c>
       <c r="H7" t="inlineStr">
         <is>
-          <t>4</t>
+          <t>3</t>
         </is>
       </c>
       <c r="I7" t="inlineStr">
         <is>
-          <t>Randy Vásquez</t>
+          <t>Cristian Javier</t>
         </is>
       </c>
       <c r="J7" t="inlineStr">
         <is>
-          <t>681190</t>
+          <t>664299</t>
         </is>
       </c>
       <c r="K7" t="inlineStr">
@@ -7598,7 +7550,7 @@
         </is>
       </c>
       <c r="L7" t="n">
-        <v>54.8</v>
+        <v>53.3</v>
       </c>
       <c r="M7" t="inlineStr">
         <is>
@@ -7612,62 +7564,58 @@
       </c>
       <c r="O7" t="inlineStr">
         <is>
-          <t>Projected Lineup, Premium Lineup Spot, Platoon Edge</t>
+          <t>Strong Barrel, Premium Lineup Spot</t>
         </is>
       </c>
       <c r="P7" t="n">
-        <v>33.6</v>
+        <v>50.3</v>
       </c>
       <c r="Q7" t="n">
-        <v>62.7</v>
+        <v>39</v>
       </c>
       <c r="R7" t="n">
         <v>58.1</v>
       </c>
       <c r="S7" t="n">
-        <v>90.40000000000001</v>
+        <v>96.59999999999999</v>
       </c>
       <c r="T7" t="n">
-        <v>80</v>
+        <v>50</v>
       </c>
       <c r="U7" t="n">
-        <v>0.8</v>
+        <v>12</v>
       </c>
       <c r="V7" t="inlineStr">
         <is>
+          <t>Yes</t>
+        </is>
+      </c>
+      <c r="W7" t="inlineStr">
+        <is>
+          <t>Yes</t>
+        </is>
+      </c>
+      <c r="X7" t="inlineStr">
+        <is>
+          <t>3</t>
+        </is>
+      </c>
+      <c r="Y7" t="inlineStr">
+        <is>
+          <t>Yes</t>
+        </is>
+      </c>
+      <c r="Z7" t="inlineStr">
+        <is>
           <t>No</t>
         </is>
       </c>
-      <c r="W7" t="inlineStr">
-        <is>
-          <t>No</t>
-        </is>
-      </c>
-      <c r="X7" t="inlineStr">
-        <is>
-          <t>4</t>
-        </is>
-      </c>
-      <c r="Y7" t="inlineStr">
-        <is>
-          <t>Yes</t>
-        </is>
-      </c>
-      <c r="Z7" t="inlineStr">
-        <is>
-          <t>Yes</t>
-        </is>
-      </c>
       <c r="AA7" t="inlineStr">
         <is>
-          <t>RotoWire projected lineup; MLB probable pitchers</t>
-        </is>
-      </c>
-      <c r="AB7" t="inlineStr">
-        <is>
-          <t>lineup projected / unconfirmed</t>
-        </is>
-      </c>
+          <t>MLB Stats API; RotoWire</t>
+        </is>
+      </c>
+      <c r="AB7" t="inlineStr"/>
       <c r="AC7" t="inlineStr">
         <is>
           <t>H:2026/2025 P:2026/2025</t>
@@ -7687,12 +7635,12 @@
       </c>
       <c r="AH7" t="inlineStr">
         <is>
-          <t>3</t>
+          <t>5</t>
         </is>
       </c>
       <c r="AI7" t="inlineStr">
         <is>
-          <t>24</t>
+          <t>25</t>
         </is>
       </c>
       <c r="AJ7" t="inlineStr">
@@ -7702,112 +7650,112 @@
       </c>
       <c r="AK7" t="inlineStr">
         <is>
-          <t>Last 7 games: 3/24, 0 HR</t>
+          <t>Last 7 games: 5/25, 0 HR</t>
         </is>
       </c>
       <c r="AL7" t="inlineStr">
         <is>
-          <t>platoon edge; pitcher baseline 11.0% barrel, 14.6 HR allowed</t>
+          <t>same-side matchup; pitcher baseline 7.7% barrel, 3.7 HR allowed</t>
         </is>
       </c>
       <c r="AM7" t="inlineStr">
         <is>
-          <t>neutral batted-ball profile; pitcher fly-ball pressure modest</t>
+          <t>neutral batted-ball profile; pitcher allows elevated contact</t>
         </is>
       </c>
       <c r="AN7" t="inlineStr">
         <is>
-          <t>9.04</t>
+          <t>11.22</t>
         </is>
       </c>
       <c r="AO7" t="inlineStr">
         <is>
-          <t>37.64</t>
+          <t>46.32</t>
         </is>
       </c>
       <c r="AP7" t="inlineStr">
         <is>
-          <t>87.31</t>
+          <t>91.36</t>
         </is>
       </c>
       <c r="AQ7" t="inlineStr">
         <is>
-          <t>99.33</t>
+          <t>101.8619</t>
         </is>
       </c>
       <c r="AR7" t="inlineStr">
         <is>
-          <t>0.3967</t>
+          <t>0.4502</t>
         </is>
       </c>
       <c r="AS7" t="inlineStr">
         <is>
-          <t>0.1634</t>
+          <t>0.2002</t>
         </is>
       </c>
       <c r="AT7" t="inlineStr">
         <is>
-          <t>0.3018</t>
+          <t>0.3368</t>
         </is>
       </c>
       <c r="AU7" t="inlineStr">
         <is>
-          <t>73.78</t>
+          <t>74.64</t>
         </is>
       </c>
       <c r="AV7" t="inlineStr">
         <is>
-          <t>37.09</t>
+          <t>44.44</t>
         </is>
       </c>
       <c r="AW7" t="inlineStr">
         <is>
-          <t>42.2</t>
+          <t>40.5</t>
         </is>
       </c>
       <c r="AX7" t="inlineStr">
         <is>
-          <t>28.96</t>
+          <t>28.85</t>
         </is>
       </c>
       <c r="AY7" t="inlineStr">
         <is>
-          <t>10.9</t>
+          <t>24.2</t>
         </is>
       </c>
       <c r="AZ7" t="inlineStr">
         <is>
-          <t>0.1812</t>
+          <t>0.2018</t>
         </is>
       </c>
       <c r="BA7" t="inlineStr">
         <is>
-          <t>11.04</t>
+          <t>7.69</t>
         </is>
       </c>
       <c r="BB7" t="inlineStr">
         <is>
-          <t>43.01</t>
+          <t>37.81</t>
         </is>
       </c>
       <c r="BC7" t="inlineStr">
         <is>
-          <t>90.71</t>
+          <t>89.39</t>
         </is>
       </c>
       <c r="BD7" t="inlineStr">
         <is>
-          <t>0.5055</t>
+          <t>0.3942</t>
         </is>
       </c>
       <c r="BE7" t="inlineStr">
         <is>
-          <t>0.2189</t>
+          <t>0.1474</t>
         </is>
       </c>
       <c r="BF7" t="inlineStr">
         <is>
-          <t>29.3</t>
+          <t>37.54</t>
         </is>
       </c>
       <c r="BG7" t="inlineStr">
@@ -7833,24 +7781,24 @@
       </c>
       <c r="B8" t="inlineStr">
         <is>
-          <t>592518</t>
+          <t>665161</t>
         </is>
       </c>
       <c r="C8" t="inlineStr">
         <is>
-          <t>Manny Machado</t>
+          <t>Jeremy Peña</t>
         </is>
       </c>
       <c r="D8" t="inlineStr">
         <is>
+          <t>HOU</t>
+        </is>
+      </c>
+      <c r="E8" t="inlineStr">
+        <is>
           <t>SD</t>
         </is>
       </c>
-      <c r="E8" t="inlineStr">
-        <is>
-          <t>HOU</t>
-        </is>
-      </c>
       <c r="F8" t="inlineStr">
         <is>
           <t>2026-08-10T00:20:00Z</t>
@@ -7863,17 +7811,17 @@
       </c>
       <c r="H8" t="inlineStr">
         <is>
-          <t>3</t>
+          <t>1</t>
         </is>
       </c>
       <c r="I8" t="inlineStr">
         <is>
-          <t>Cristian Javier</t>
+          <t>Randy Vásquez</t>
         </is>
       </c>
       <c r="J8" t="inlineStr">
         <is>
-          <t>664299</t>
+          <t>681190</t>
         </is>
       </c>
       <c r="K8" t="inlineStr">
@@ -7882,7 +7830,7 @@
         </is>
       </c>
       <c r="L8" t="n">
-        <v>53.3</v>
+        <v>52.9</v>
       </c>
       <c r="M8" t="inlineStr">
         <is>
@@ -7896,26 +7844,26 @@
       </c>
       <c r="O8" t="inlineStr">
         <is>
-          <t>Strong Barrel, Premium Lineup Spot</t>
+          <t>Premium Lineup Spot</t>
         </is>
       </c>
       <c r="P8" t="n">
-        <v>50.3</v>
+        <v>31.1</v>
       </c>
       <c r="Q8" t="n">
-        <v>39</v>
+        <v>62.7</v>
       </c>
       <c r="R8" t="n">
         <v>58.1</v>
       </c>
       <c r="S8" t="n">
-        <v>96.59999999999999</v>
+        <v>93.2</v>
       </c>
       <c r="T8" t="n">
         <v>50</v>
       </c>
       <c r="U8" t="n">
-        <v>12</v>
+        <v>26.2</v>
       </c>
       <c r="V8" t="inlineStr">
         <is>
@@ -7929,7 +7877,7 @@
       </c>
       <c r="X8" t="inlineStr">
         <is>
-          <t>3</t>
+          <t>1</t>
         </is>
       </c>
       <c r="Y8" t="inlineStr">
@@ -7972,122 +7920,122 @@
       </c>
       <c r="AI8" t="inlineStr">
         <is>
-          <t>25</t>
+          <t>29</t>
         </is>
       </c>
       <c r="AJ8" t="inlineStr">
         <is>
-          <t>0</t>
+          <t>1</t>
         </is>
       </c>
       <c r="AK8" t="inlineStr">
         <is>
-          <t>Last 7 games: 5/25, 0 HR</t>
+          <t>Last 7 games: 5/29, 1 HR</t>
         </is>
       </c>
       <c r="AL8" t="inlineStr">
         <is>
-          <t>same-side matchup; pitcher baseline 7.7% barrel, 3.7 HR allowed</t>
+          <t>same-side matchup; pitcher baseline 11.0% barrel, 14.6 HR allowed</t>
         </is>
       </c>
       <c r="AM8" t="inlineStr">
         <is>
-          <t>neutral batted-ball profile; pitcher allows elevated contact</t>
+          <t>neutral batted-ball profile; pitcher fly-ball pressure modest</t>
         </is>
       </c>
       <c r="AN8" t="inlineStr">
         <is>
-          <t>11.22</t>
+          <t>6.31</t>
         </is>
       </c>
       <c r="AO8" t="inlineStr">
         <is>
-          <t>46.32</t>
+          <t>41.64</t>
         </is>
       </c>
       <c r="AP8" t="inlineStr">
         <is>
-          <t>91.36</t>
+          <t>88.41</t>
         </is>
       </c>
       <c r="AQ8" t="inlineStr">
         <is>
-          <t>101.8619</t>
+          <t>100.0639</t>
         </is>
       </c>
       <c r="AR8" t="inlineStr">
         <is>
-          <t>0.4502</t>
+          <t>0.4404</t>
         </is>
       </c>
       <c r="AS8" t="inlineStr">
         <is>
-          <t>0.2002</t>
+          <t>0.1522</t>
         </is>
       </c>
       <c r="AT8" t="inlineStr">
         <is>
-          <t>0.3368</t>
+          <t>0.3466</t>
         </is>
       </c>
       <c r="AU8" t="inlineStr">
         <is>
-          <t>74.64</t>
+          <t>72.23</t>
         </is>
       </c>
       <c r="AV8" t="inlineStr">
         <is>
-          <t>44.44</t>
+          <t>13.99</t>
         </is>
       </c>
       <c r="AW8" t="inlineStr">
         <is>
-          <t>40.5</t>
+          <t>46.06</t>
         </is>
       </c>
       <c r="AX8" t="inlineStr">
         <is>
-          <t>28.85</t>
+          <t>23.45</t>
         </is>
       </c>
       <c r="AY8" t="inlineStr">
         <is>
-          <t>24.2</t>
+          <t>14.2</t>
         </is>
       </c>
       <c r="AZ8" t="inlineStr">
         <is>
-          <t>0.2018</t>
+          <t>0.187</t>
         </is>
       </c>
       <c r="BA8" t="inlineStr">
         <is>
-          <t>7.69</t>
+          <t>11.04</t>
         </is>
       </c>
       <c r="BB8" t="inlineStr">
         <is>
-          <t>37.81</t>
+          <t>43.01</t>
         </is>
       </c>
       <c r="BC8" t="inlineStr">
         <is>
-          <t>89.39</t>
+          <t>90.71</t>
         </is>
       </c>
       <c r="BD8" t="inlineStr">
         <is>
-          <t>0.3942</t>
+          <t>0.5055</t>
         </is>
       </c>
       <c r="BE8" t="inlineStr">
         <is>
-          <t>0.1474</t>
+          <t>0.2189</t>
         </is>
       </c>
       <c r="BF8" t="inlineStr">
         <is>
-          <t>37.54</t>
+          <t>29.3</t>
         </is>
       </c>
       <c r="BG8" t="inlineStr">
@@ -8113,24 +8061,24 @@
       </c>
       <c r="B9" t="inlineStr">
         <is>
-          <t>665161</t>
+          <t>664034</t>
         </is>
       </c>
       <c r="C9" t="inlineStr">
         <is>
-          <t>Jeremy Pena</t>
+          <t>Ty France</t>
         </is>
       </c>
       <c r="D9" t="inlineStr">
         <is>
+          <t>SD</t>
+        </is>
+      </c>
+      <c r="E9" t="inlineStr">
+        <is>
           <t>HOU</t>
         </is>
       </c>
-      <c r="E9" t="inlineStr">
-        <is>
-          <t>SD</t>
-        </is>
-      </c>
       <c r="F9" t="inlineStr">
         <is>
           <t>2026-08-10T00:20:00Z</t>
@@ -8143,17 +8091,17 @@
       </c>
       <c r="H9" t="inlineStr">
         <is>
-          <t>1</t>
+          <t>4</t>
         </is>
       </c>
       <c r="I9" t="inlineStr">
         <is>
-          <t>Randy Vásquez</t>
+          <t>Cristian Javier</t>
         </is>
       </c>
       <c r="J9" t="inlineStr">
         <is>
-          <t>681190</t>
+          <t>664299</t>
         </is>
       </c>
       <c r="K9" t="inlineStr">
@@ -8162,7 +8110,7 @@
         </is>
       </c>
       <c r="L9" t="n">
-        <v>52.3</v>
+        <v>51.4</v>
       </c>
       <c r="M9" t="inlineStr">
         <is>
@@ -8176,62 +8124,58 @@
       </c>
       <c r="O9" t="inlineStr">
         <is>
-          <t>Projected Lineup, Premium Lineup Spot</t>
+          <t>Strong Barrel, Premium Lineup Spot</t>
         </is>
       </c>
       <c r="P9" t="n">
-        <v>31.1</v>
+        <v>45.1</v>
       </c>
       <c r="Q9" t="n">
-        <v>62.7</v>
+        <v>39</v>
       </c>
       <c r="R9" t="n">
         <v>58.1</v>
       </c>
       <c r="S9" t="n">
-        <v>88.7</v>
+        <v>94.90000000000001</v>
       </c>
       <c r="T9" t="n">
         <v>50</v>
       </c>
       <c r="U9" t="n">
-        <v>26.2</v>
+        <v>13.3</v>
       </c>
       <c r="V9" t="inlineStr">
         <is>
+          <t>Yes</t>
+        </is>
+      </c>
+      <c r="W9" t="inlineStr">
+        <is>
+          <t>Yes</t>
+        </is>
+      </c>
+      <c r="X9" t="inlineStr">
+        <is>
+          <t>4</t>
+        </is>
+      </c>
+      <c r="Y9" t="inlineStr">
+        <is>
+          <t>Yes</t>
+        </is>
+      </c>
+      <c r="Z9" t="inlineStr">
+        <is>
           <t>No</t>
         </is>
       </c>
-      <c r="W9" t="inlineStr">
-        <is>
-          <t>No</t>
-        </is>
-      </c>
-      <c r="X9" t="inlineStr">
-        <is>
-          <t>1</t>
-        </is>
-      </c>
-      <c r="Y9" t="inlineStr">
-        <is>
-          <t>Yes</t>
-        </is>
-      </c>
-      <c r="Z9" t="inlineStr">
-        <is>
-          <t>Yes</t>
-        </is>
-      </c>
       <c r="AA9" t="inlineStr">
         <is>
-          <t>RotoWire projected lineup; MLB probable pitchers</t>
-        </is>
-      </c>
-      <c r="AB9" t="inlineStr">
-        <is>
-          <t>lineup projected / unconfirmed</t>
-        </is>
-      </c>
+          <t>MLB Stats API; RotoWire</t>
+        </is>
+      </c>
+      <c r="AB9" t="inlineStr"/>
       <c r="AC9" t="inlineStr">
         <is>
           <t>H:2026/2025 P:2026/2025</t>
@@ -8256,122 +8200,122 @@
       </c>
       <c r="AI9" t="inlineStr">
         <is>
-          <t>29</t>
+          <t>24</t>
         </is>
       </c>
       <c r="AJ9" t="inlineStr">
         <is>
-          <t>1</t>
+          <t>0</t>
         </is>
       </c>
       <c r="AK9" t="inlineStr">
         <is>
-          <t>Last 7 games: 5/29, 1 HR</t>
+          <t>Last 7 games: 5/24, 0 HR</t>
         </is>
       </c>
       <c r="AL9" t="inlineStr">
         <is>
-          <t>same-side matchup; pitcher baseline 11.0% barrel, 14.6 HR allowed</t>
+          <t>same-side matchup; pitcher baseline 7.7% barrel, 3.7 HR allowed</t>
         </is>
       </c>
       <c r="AM9" t="inlineStr">
         <is>
-          <t>neutral batted-ball profile; pitcher fly-ball pressure modest</t>
+          <t>neutral batted-ball profile; pitcher allows elevated contact</t>
         </is>
       </c>
       <c r="AN9" t="inlineStr">
         <is>
-          <t>6.31</t>
+          <t>10.01</t>
         </is>
       </c>
       <c r="AO9" t="inlineStr">
         <is>
-          <t>41.64</t>
+          <t>47.63</t>
         </is>
       </c>
       <c r="AP9" t="inlineStr">
         <is>
-          <t>88.41</t>
+          <t>91.46</t>
         </is>
       </c>
       <c r="AQ9" t="inlineStr">
         <is>
-          <t>100.0639</t>
+          <t>101.3479</t>
         </is>
       </c>
       <c r="AR9" t="inlineStr">
         <is>
-          <t>0.4404</t>
+          <t>0.4376</t>
         </is>
       </c>
       <c r="AS9" t="inlineStr">
         <is>
-          <t>0.1522</t>
+          <t>0.1828</t>
         </is>
       </c>
       <c r="AT9" t="inlineStr">
         <is>
-          <t>0.3466</t>
+          <t>0.3301</t>
         </is>
       </c>
       <c r="AU9" t="inlineStr">
         <is>
-          <t>72.23</t>
+          <t>71.7</t>
         </is>
       </c>
       <c r="AV9" t="inlineStr">
         <is>
-          <t>13.99</t>
+          <t>18.48</t>
         </is>
       </c>
       <c r="AW9" t="inlineStr">
         <is>
-          <t>46.06</t>
+          <t>36.22</t>
         </is>
       </c>
       <c r="AX9" t="inlineStr">
         <is>
-          <t>23.45</t>
+          <t>24.76</t>
         </is>
       </c>
       <c r="AY9" t="inlineStr">
         <is>
-          <t>14.2</t>
+          <t>13.3</t>
         </is>
       </c>
       <c r="AZ9" t="inlineStr">
         <is>
-          <t>0.187</t>
+          <t>0.1933</t>
         </is>
       </c>
       <c r="BA9" t="inlineStr">
         <is>
-          <t>11.04</t>
+          <t>7.69</t>
         </is>
       </c>
       <c r="BB9" t="inlineStr">
         <is>
-          <t>43.01</t>
+          <t>37.81</t>
         </is>
       </c>
       <c r="BC9" t="inlineStr">
         <is>
-          <t>90.71</t>
+          <t>89.39</t>
         </is>
       </c>
       <c r="BD9" t="inlineStr">
         <is>
-          <t>0.5055</t>
+          <t>0.3942</t>
         </is>
       </c>
       <c r="BE9" t="inlineStr">
         <is>
-          <t>0.2189</t>
+          <t>0.1474</t>
         </is>
       </c>
       <c r="BF9" t="inlineStr">
         <is>
-          <t>29.3</t>
+          <t>37.54</t>
         </is>
       </c>
       <c r="BG9" t="inlineStr">
@@ -8397,12 +8341,12 @@
       </c>
       <c r="B10" t="inlineStr">
         <is>
-          <t>701358</t>
+          <t>662139</t>
         </is>
       </c>
       <c r="C10" t="inlineStr">
         <is>
-          <t>Cam Smith</t>
+          <t>Daulton Varsho</t>
         </is>
       </c>
       <c r="D10" t="inlineStr">
@@ -8427,7 +8371,7 @@
       </c>
       <c r="H10" t="inlineStr">
         <is>
-          <t>9</t>
+          <t>7</t>
         </is>
       </c>
       <c r="I10" t="inlineStr">
@@ -8446,7 +8390,7 @@
         </is>
       </c>
       <c r="L10" t="n">
-        <v>51.9</v>
+        <v>51.1</v>
       </c>
       <c r="M10" t="inlineStr">
         <is>
@@ -8460,11 +8404,11 @@
       </c>
       <c r="O10" t="inlineStr">
         <is>
-          <t>Projected Lineup, Strong Barrel, Hot Hitter/Streak</t>
+          <t>Platoon Edge</t>
         </is>
       </c>
       <c r="P10" t="n">
-        <v>42.2</v>
+        <v>33.6</v>
       </c>
       <c r="Q10" t="n">
         <v>62.7</v>
@@ -8473,49 +8417,45 @@
         <v>58.1</v>
       </c>
       <c r="S10" t="n">
-        <v>40.2</v>
+        <v>64.3</v>
       </c>
       <c r="T10" t="n">
-        <v>50</v>
+        <v>80</v>
       </c>
       <c r="U10" t="n">
-        <v>81.7</v>
+        <v>0.8</v>
       </c>
       <c r="V10" t="inlineStr">
         <is>
+          <t>Yes</t>
+        </is>
+      </c>
+      <c r="W10" t="inlineStr">
+        <is>
+          <t>Yes</t>
+        </is>
+      </c>
+      <c r="X10" t="inlineStr">
+        <is>
+          <t>7</t>
+        </is>
+      </c>
+      <c r="Y10" t="inlineStr">
+        <is>
+          <t>Yes</t>
+        </is>
+      </c>
+      <c r="Z10" t="inlineStr">
+        <is>
           <t>No</t>
         </is>
       </c>
-      <c r="W10" t="inlineStr">
-        <is>
-          <t>No</t>
-        </is>
-      </c>
-      <c r="X10" t="inlineStr">
-        <is>
-          <t>9</t>
-        </is>
-      </c>
-      <c r="Y10" t="inlineStr">
-        <is>
-          <t>Yes</t>
-        </is>
-      </c>
-      <c r="Z10" t="inlineStr">
-        <is>
-          <t>Yes</t>
-        </is>
-      </c>
       <c r="AA10" t="inlineStr">
         <is>
-          <t>RotoWire projected lineup; MLB probable pitchers</t>
-        </is>
-      </c>
-      <c r="AB10" t="inlineStr">
-        <is>
-          <t>lineup projected / unconfirmed</t>
-        </is>
-      </c>
+          <t>MLB Stats API; RotoWire</t>
+        </is>
+      </c>
+      <c r="AB10" t="inlineStr"/>
       <c r="AC10" t="inlineStr">
         <is>
           <t>H:2026/2025 P:2026/2025</t>
@@ -8535,27 +8475,27 @@
       </c>
       <c r="AH10" t="inlineStr">
         <is>
-          <t>10</t>
+          <t>3</t>
         </is>
       </c>
       <c r="AI10" t="inlineStr">
         <is>
-          <t>23</t>
+          <t>24</t>
         </is>
       </c>
       <c r="AJ10" t="inlineStr">
         <is>
-          <t>2</t>
+          <t>0</t>
         </is>
       </c>
       <c r="AK10" t="inlineStr">
         <is>
-          <t>Hot streak: 2 HR in last 7 games</t>
+          <t>Last 7 games: 3/24, 0 HR</t>
         </is>
       </c>
       <c r="AL10" t="inlineStr">
         <is>
-          <t>same-side matchup; pitcher baseline 11.0% barrel, 14.6 HR allowed</t>
+          <t>platoon edge; pitcher baseline 11.0% barrel, 14.6 HR allowed</t>
         </is>
       </c>
       <c r="AM10" t="inlineStr">
@@ -8565,67 +8505,67 @@
       </c>
       <c r="AN10" t="inlineStr">
         <is>
-          <t>10.19</t>
+          <t>9.04</t>
         </is>
       </c>
       <c r="AO10" t="inlineStr">
         <is>
-          <t>43.46</t>
+          <t>37.64</t>
         </is>
       </c>
       <c r="AP10" t="inlineStr">
         <is>
-          <t>88.95</t>
+          <t>87.31</t>
         </is>
       </c>
       <c r="AQ10" t="inlineStr">
         <is>
-          <t>101.5346</t>
+          <t>99.33</t>
         </is>
       </c>
       <c r="AR10" t="inlineStr">
         <is>
-          <t>0.418</t>
+          <t>0.3967</t>
         </is>
       </c>
       <c r="AS10" t="inlineStr">
         <is>
-          <t>0.1753</t>
+          <t>0.1634</t>
         </is>
       </c>
       <c r="AT10" t="inlineStr">
         <is>
-          <t>0.3215</t>
+          <t>0.3018</t>
         </is>
       </c>
       <c r="AU10" t="inlineStr">
         <is>
-          <t>76.67</t>
+          <t>73.78</t>
         </is>
       </c>
       <c r="AV10" t="inlineStr">
         <is>
-          <t>68.11</t>
+          <t>37.09</t>
         </is>
       </c>
       <c r="AW10" t="inlineStr">
         <is>
-          <t>37.42</t>
+          <t>42.2</t>
         </is>
       </c>
       <c r="AX10" t="inlineStr">
         <is>
-          <t>25.14</t>
+          <t>28.96</t>
         </is>
       </c>
       <c r="AY10" t="inlineStr">
         <is>
-          <t>13.2</t>
+          <t>10.9</t>
         </is>
       </c>
       <c r="AZ10" t="inlineStr">
         <is>
-          <t>0.1542</t>
+          <t>0.1812</t>
         </is>
       </c>
       <c r="BA10" t="inlineStr">
@@ -8681,24 +8621,24 @@
       </c>
       <c r="B11" t="inlineStr">
         <is>
-          <t>664034</t>
+          <t>514888</t>
         </is>
       </c>
       <c r="C11" t="inlineStr">
         <is>
-          <t>Ty France</t>
+          <t>Jose Altuve</t>
         </is>
       </c>
       <c r="D11" t="inlineStr">
         <is>
+          <t>HOU</t>
+        </is>
+      </c>
+      <c r="E11" t="inlineStr">
+        <is>
           <t>SD</t>
         </is>
       </c>
-      <c r="E11" t="inlineStr">
-        <is>
-          <t>HOU</t>
-        </is>
-      </c>
       <c r="F11" t="inlineStr">
         <is>
           <t>2026-08-10T00:20:00Z</t>
@@ -8716,12 +8656,12 @@
       </c>
       <c r="I11" t="inlineStr">
         <is>
-          <t>Cristian Javier</t>
+          <t>Randy Vásquez</t>
         </is>
       </c>
       <c r="J11" t="inlineStr">
         <is>
-          <t>664299</t>
+          <t>681190</t>
         </is>
       </c>
       <c r="K11" t="inlineStr">
@@ -8730,7 +8670,7 @@
         </is>
       </c>
       <c r="L11" t="n">
-        <v>51.4</v>
+        <v>49.7</v>
       </c>
       <c r="M11" t="inlineStr">
         <is>
@@ -8744,14 +8684,14 @@
       </c>
       <c r="O11" t="inlineStr">
         <is>
-          <t>Strong Barrel, Premium Lineup Spot</t>
+          <t>Premium Lineup Spot</t>
         </is>
       </c>
       <c r="P11" t="n">
-        <v>45.1</v>
+        <v>15.5</v>
       </c>
       <c r="Q11" t="n">
-        <v>39</v>
+        <v>62.7</v>
       </c>
       <c r="R11" t="n">
         <v>58.1</v>
@@ -8763,7 +8703,7 @@
         <v>50</v>
       </c>
       <c r="U11" t="n">
-        <v>13.3</v>
+        <v>61.4</v>
       </c>
       <c r="V11" t="inlineStr">
         <is>
@@ -8815,127 +8755,127 @@
       </c>
       <c r="AH11" t="inlineStr">
         <is>
-          <t>5</t>
+          <t>11</t>
         </is>
       </c>
       <c r="AI11" t="inlineStr">
         <is>
-          <t>24</t>
+          <t>27</t>
         </is>
       </c>
       <c r="AJ11" t="inlineStr">
         <is>
-          <t>0</t>
+          <t>1</t>
         </is>
       </c>
       <c r="AK11" t="inlineStr">
         <is>
-          <t>Last 7 games: 5/24, 0 HR</t>
+          <t>Contact streak: 11/27 over last 7 games</t>
         </is>
       </c>
       <c r="AL11" t="inlineStr">
         <is>
-          <t>same-side matchup; pitcher baseline 7.7% barrel, 3.7 HR allowed</t>
+          <t>same-side matchup; pitcher baseline 11.0% barrel, 14.6 HR allowed</t>
         </is>
       </c>
       <c r="AM11" t="inlineStr">
         <is>
-          <t>neutral batted-ball profile; pitcher allows elevated contact</t>
+          <t>neutral batted-ball profile; pitcher fly-ball pressure modest</t>
         </is>
       </c>
       <c r="AN11" t="inlineStr">
         <is>
-          <t>10.01</t>
+          <t>5.57</t>
         </is>
       </c>
       <c r="AO11" t="inlineStr">
         <is>
-          <t>47.63</t>
+          <t>31.88</t>
         </is>
       </c>
       <c r="AP11" t="inlineStr">
         <is>
-          <t>91.46</t>
+          <t>85.52</t>
         </is>
       </c>
       <c r="AQ11" t="inlineStr">
         <is>
-          <t>101.3479</t>
+          <t>97.1381</t>
         </is>
       </c>
       <c r="AR11" t="inlineStr">
         <is>
-          <t>0.4376</t>
+          <t>0.3511</t>
         </is>
       </c>
       <c r="AS11" t="inlineStr">
         <is>
-          <t>0.1828</t>
+          <t>0.1225</t>
         </is>
       </c>
       <c r="AT11" t="inlineStr">
         <is>
-          <t>0.3301</t>
+          <t>0.286</t>
         </is>
       </c>
       <c r="AU11" t="inlineStr">
         <is>
-          <t>71.7</t>
+          <t>69.07</t>
         </is>
       </c>
       <c r="AV11" t="inlineStr">
         <is>
-          <t>18.48</t>
+          <t>9.78</t>
         </is>
       </c>
       <c r="AW11" t="inlineStr">
         <is>
-          <t>36.22</t>
+          <t>46.2</t>
         </is>
       </c>
       <c r="AX11" t="inlineStr">
         <is>
-          <t>24.76</t>
+          <t>22.3</t>
         </is>
       </c>
       <c r="AY11" t="inlineStr">
         <is>
-          <t>13.3</t>
+          <t>16.9</t>
         </is>
       </c>
       <c r="AZ11" t="inlineStr">
         <is>
-          <t>0.1933</t>
+          <t>0.1602</t>
         </is>
       </c>
       <c r="BA11" t="inlineStr">
         <is>
-          <t>7.69</t>
+          <t>11.04</t>
         </is>
       </c>
       <c r="BB11" t="inlineStr">
         <is>
-          <t>37.81</t>
+          <t>43.01</t>
         </is>
       </c>
       <c r="BC11" t="inlineStr">
         <is>
-          <t>89.39</t>
+          <t>90.71</t>
         </is>
       </c>
       <c r="BD11" t="inlineStr">
         <is>
-          <t>0.3942</t>
+          <t>0.5055</t>
         </is>
       </c>
       <c r="BE11" t="inlineStr">
         <is>
-          <t>0.1474</t>
+          <t>0.2189</t>
         </is>
       </c>
       <c r="BF11" t="inlineStr">
         <is>
-          <t>37.54</t>
+          <t>29.3</t>
         </is>
       </c>
       <c r="BG11" t="inlineStr">
@@ -9010,7 +8950,7 @@
         </is>
       </c>
       <c r="L12" t="n">
-        <v>48</v>
+        <v>48.6</v>
       </c>
       <c r="M12" t="inlineStr">
         <is>
@@ -9024,7 +8964,7 @@
       </c>
       <c r="O12" t="inlineStr">
         <is>
-          <t>Projected Lineup, Premium Lineup Spot</t>
+          <t>Premium Lineup Spot</t>
         </is>
       </c>
       <c r="P12" t="n">
@@ -9037,7 +8977,7 @@
         <v>58.1</v>
       </c>
       <c r="S12" t="n">
-        <v>92.09999999999999</v>
+        <v>96.59999999999999</v>
       </c>
       <c r="T12" t="n">
         <v>50</v>
@@ -9047,39 +8987,35 @@
       </c>
       <c r="V12" t="inlineStr">
         <is>
+          <t>Yes</t>
+        </is>
+      </c>
+      <c r="W12" t="inlineStr">
+        <is>
+          <t>Yes</t>
+        </is>
+      </c>
+      <c r="X12" t="inlineStr">
+        <is>
+          <t>3</t>
+        </is>
+      </c>
+      <c r="Y12" t="inlineStr">
+        <is>
+          <t>Yes</t>
+        </is>
+      </c>
+      <c r="Z12" t="inlineStr">
+        <is>
           <t>No</t>
         </is>
       </c>
-      <c r="W12" t="inlineStr">
-        <is>
-          <t>No</t>
-        </is>
-      </c>
-      <c r="X12" t="inlineStr">
-        <is>
-          <t>3</t>
-        </is>
-      </c>
-      <c r="Y12" t="inlineStr">
-        <is>
-          <t>Yes</t>
-        </is>
-      </c>
-      <c r="Z12" t="inlineStr">
-        <is>
-          <t>Yes</t>
-        </is>
-      </c>
       <c r="AA12" t="inlineStr">
         <is>
-          <t>RotoWire projected lineup; MLB probable pitchers</t>
-        </is>
-      </c>
-      <c r="AB12" t="inlineStr">
-        <is>
-          <t>lineup projected / unconfirmed</t>
-        </is>
-      </c>
+          <t>MLB Stats API; RotoWire</t>
+        </is>
+      </c>
+      <c r="AB12" t="inlineStr"/>
       <c r="AC12" t="inlineStr">
         <is>
           <t>H:2026/2025 P:2026/2025</t>
@@ -9245,24 +9181,24 @@
       </c>
       <c r="B13" t="inlineStr">
         <is>
-          <t>514888</t>
+          <t>630105</t>
         </is>
       </c>
       <c r="C13" t="inlineStr">
         <is>
-          <t>Jose Altuve</t>
+          <t>Jake Cronenworth</t>
         </is>
       </c>
       <c r="D13" t="inlineStr">
         <is>
+          <t>SD</t>
+        </is>
+      </c>
+      <c r="E13" t="inlineStr">
+        <is>
           <t>HOU</t>
         </is>
       </c>
-      <c r="E13" t="inlineStr">
-        <is>
-          <t>SD</t>
-        </is>
-      </c>
       <c r="F13" t="inlineStr">
         <is>
           <t>2026-08-10T00:20:00Z</t>
@@ -9275,17 +9211,17 @@
       </c>
       <c r="H13" t="inlineStr">
         <is>
-          <t>6</t>
+          <t>2</t>
         </is>
       </c>
       <c r="I13" t="inlineStr">
         <is>
-          <t>Randy Vásquez</t>
+          <t>Cristian Javier</t>
         </is>
       </c>
       <c r="J13" t="inlineStr">
         <is>
-          <t>681190</t>
+          <t>664299</t>
         </is>
       </c>
       <c r="K13" t="inlineStr">
@@ -9294,7 +9230,7 @@
         </is>
       </c>
       <c r="L13" t="n">
-        <v>46.5</v>
+        <v>46.1</v>
       </c>
       <c r="M13" t="inlineStr">
         <is>
@@ -9308,62 +9244,58 @@
       </c>
       <c r="O13" t="inlineStr">
         <is>
-          <t>Projected Lineup</t>
+          <t>Premium Lineup Spot, Platoon Edge</t>
         </is>
       </c>
       <c r="P13" t="n">
-        <v>15.5</v>
+        <v>17.5</v>
       </c>
       <c r="Q13" t="n">
-        <v>62.7</v>
+        <v>39</v>
       </c>
       <c r="R13" t="n">
         <v>58.1</v>
       </c>
       <c r="S13" t="n">
-        <v>71.7</v>
+        <v>100</v>
       </c>
       <c r="T13" t="n">
-        <v>50</v>
+        <v>80</v>
       </c>
       <c r="U13" t="n">
-        <v>61.4</v>
+        <v>20.9</v>
       </c>
       <c r="V13" t="inlineStr">
         <is>
+          <t>Yes</t>
+        </is>
+      </c>
+      <c r="W13" t="inlineStr">
+        <is>
+          <t>Yes</t>
+        </is>
+      </c>
+      <c r="X13" t="inlineStr">
+        <is>
+          <t>2</t>
+        </is>
+      </c>
+      <c r="Y13" t="inlineStr">
+        <is>
+          <t>Yes</t>
+        </is>
+      </c>
+      <c r="Z13" t="inlineStr">
+        <is>
           <t>No</t>
         </is>
       </c>
-      <c r="W13" t="inlineStr">
-        <is>
-          <t>No</t>
-        </is>
-      </c>
-      <c r="X13" t="inlineStr">
-        <is>
-          <t>6</t>
-        </is>
-      </c>
-      <c r="Y13" t="inlineStr">
-        <is>
-          <t>Yes</t>
-        </is>
-      </c>
-      <c r="Z13" t="inlineStr">
-        <is>
-          <t>Yes</t>
-        </is>
-      </c>
       <c r="AA13" t="inlineStr">
         <is>
-          <t>RotoWire projected lineup; MLB probable pitchers</t>
-        </is>
-      </c>
-      <c r="AB13" t="inlineStr">
-        <is>
-          <t>lineup projected / unconfirmed</t>
-        </is>
-      </c>
+          <t>MLB Stats API; RotoWire</t>
+        </is>
+      </c>
+      <c r="AB13" t="inlineStr"/>
       <c r="AC13" t="inlineStr">
         <is>
           <t>H:2026/2025 P:2026/2025</t>
@@ -9383,7 +9315,7 @@
       </c>
       <c r="AH13" t="inlineStr">
         <is>
-          <t>11</t>
+          <t>7</t>
         </is>
       </c>
       <c r="AI13" t="inlineStr">
@@ -9393,117 +9325,117 @@
       </c>
       <c r="AJ13" t="inlineStr">
         <is>
-          <t>1</t>
+          <t>0</t>
         </is>
       </c>
       <c r="AK13" t="inlineStr">
         <is>
-          <t>Contact streak: 11/27 over last 7 games</t>
+          <t>Last 7 games: 7/27, 0 HR</t>
         </is>
       </c>
       <c r="AL13" t="inlineStr">
         <is>
-          <t>same-side matchup; pitcher baseline 11.0% barrel, 14.6 HR allowed</t>
+          <t>platoon edge; pitcher baseline 7.7% barrel, 3.7 HR allowed</t>
         </is>
       </c>
       <c r="AM13" t="inlineStr">
         <is>
-          <t>neutral batted-ball profile; pitcher fly-ball pressure modest</t>
+          <t>neutral batted-ball profile; pitcher allows elevated contact</t>
         </is>
       </c>
       <c r="AN13" t="inlineStr">
         <is>
-          <t>5.57</t>
+          <t>4.8</t>
         </is>
       </c>
       <c r="AO13" t="inlineStr">
         <is>
-          <t>31.88</t>
+          <t>33.75</t>
         </is>
       </c>
       <c r="AP13" t="inlineStr">
         <is>
-          <t>85.52</t>
+          <t>87.73</t>
         </is>
       </c>
       <c r="AQ13" t="inlineStr">
         <is>
-          <t>97.1381</t>
+          <t>98.1545</t>
         </is>
       </c>
       <c r="AR13" t="inlineStr">
         <is>
-          <t>0.3511</t>
+          <t>0.3355</t>
         </is>
       </c>
       <c r="AS13" t="inlineStr">
         <is>
-          <t>0.1225</t>
+          <t>0.1063</t>
         </is>
       </c>
       <c r="AT13" t="inlineStr">
         <is>
-          <t>0.286</t>
+          <t>0.3022</t>
         </is>
       </c>
       <c r="AU13" t="inlineStr">
         <is>
-          <t>69.07</t>
+          <t>71.39</t>
         </is>
       </c>
       <c r="AV13" t="inlineStr">
         <is>
-          <t>9.78</t>
+          <t>17.39</t>
         </is>
       </c>
       <c r="AW13" t="inlineStr">
         <is>
-          <t>46.2</t>
+          <t>31.54</t>
         </is>
       </c>
       <c r="AX13" t="inlineStr">
         <is>
-          <t>22.3</t>
+          <t>21.95</t>
         </is>
       </c>
       <c r="AY13" t="inlineStr">
         <is>
-          <t>16.9</t>
+          <t>5.4</t>
         </is>
       </c>
       <c r="AZ13" t="inlineStr">
         <is>
-          <t>0.1602</t>
+          <t>0.0876</t>
         </is>
       </c>
       <c r="BA13" t="inlineStr">
         <is>
-          <t>11.04</t>
+          <t>7.69</t>
         </is>
       </c>
       <c r="BB13" t="inlineStr">
         <is>
-          <t>43.01</t>
+          <t>37.81</t>
         </is>
       </c>
       <c r="BC13" t="inlineStr">
         <is>
-          <t>90.71</t>
+          <t>89.39</t>
         </is>
       </c>
       <c r="BD13" t="inlineStr">
         <is>
-          <t>0.5055</t>
+          <t>0.3942</t>
         </is>
       </c>
       <c r="BE13" t="inlineStr">
         <is>
-          <t>0.2189</t>
+          <t>0.1474</t>
         </is>
       </c>
       <c r="BF13" t="inlineStr">
         <is>
-          <t>29.3</t>
+          <t>37.54</t>
         </is>
       </c>
       <c r="BG13" t="inlineStr">
@@ -9529,24 +9461,24 @@
       </c>
       <c r="B14" t="inlineStr">
         <is>
-          <t>630105</t>
+          <t>673237</t>
         </is>
       </c>
       <c r="C14" t="inlineStr">
         <is>
-          <t>Jake Cronenworth</t>
+          <t>Yainer Diaz</t>
         </is>
       </c>
       <c r="D14" t="inlineStr">
         <is>
+          <t>HOU</t>
+        </is>
+      </c>
+      <c r="E14" t="inlineStr">
+        <is>
           <t>SD</t>
         </is>
       </c>
-      <c r="E14" t="inlineStr">
-        <is>
-          <t>HOU</t>
-        </is>
-      </c>
       <c r="F14" t="inlineStr">
         <is>
           <t>2026-08-10T00:20:00Z</t>
@@ -9559,17 +9491,17 @@
       </c>
       <c r="H14" t="inlineStr">
         <is>
-          <t>2</t>
+          <t>8</t>
         </is>
       </c>
       <c r="I14" t="inlineStr">
         <is>
-          <t>Cristian Javier</t>
+          <t>Randy Vásquez</t>
         </is>
       </c>
       <c r="J14" t="inlineStr">
         <is>
-          <t>664299</t>
+          <t>681190</t>
         </is>
       </c>
       <c r="K14" t="inlineStr">
@@ -9578,7 +9510,7 @@
         </is>
       </c>
       <c r="L14" t="n">
-        <v>46.1</v>
+        <v>45.9</v>
       </c>
       <c r="M14" t="inlineStr">
         <is>
@@ -9592,26 +9524,26 @@
       </c>
       <c r="O14" t="inlineStr">
         <is>
-          <t>Premium Lineup Spot, Platoon Edge</t>
+          <t>No major boost</t>
         </is>
       </c>
       <c r="P14" t="n">
-        <v>17.5</v>
+        <v>28.6</v>
       </c>
       <c r="Q14" t="n">
-        <v>39</v>
+        <v>62.7</v>
       </c>
       <c r="R14" t="n">
         <v>58.1</v>
       </c>
       <c r="S14" t="n">
-        <v>100</v>
+        <v>52.4</v>
       </c>
       <c r="T14" t="n">
-        <v>80</v>
+        <v>50</v>
       </c>
       <c r="U14" t="n">
-        <v>20.9</v>
+        <v>17.7</v>
       </c>
       <c r="V14" t="inlineStr">
         <is>
@@ -9625,7 +9557,7 @@
       </c>
       <c r="X14" t="inlineStr">
         <is>
-          <t>2</t>
+          <t>8</t>
         </is>
       </c>
       <c r="Y14" t="inlineStr">
@@ -9663,12 +9595,12 @@
       </c>
       <c r="AH14" t="inlineStr">
         <is>
-          <t>7</t>
+          <t>5</t>
         </is>
       </c>
       <c r="AI14" t="inlineStr">
         <is>
-          <t>27</t>
+          <t>21</t>
         </is>
       </c>
       <c r="AJ14" t="inlineStr">
@@ -9678,112 +9610,112 @@
       </c>
       <c r="AK14" t="inlineStr">
         <is>
-          <t>Last 7 games: 7/27, 0 HR</t>
+          <t>Last 7 games: 5/21, 0 HR</t>
         </is>
       </c>
       <c r="AL14" t="inlineStr">
         <is>
-          <t>platoon edge; pitcher baseline 7.7% barrel, 3.7 HR allowed</t>
+          <t>same-side matchup; pitcher baseline 11.0% barrel, 14.6 HR allowed</t>
         </is>
       </c>
       <c r="AM14" t="inlineStr">
         <is>
-          <t>neutral batted-ball profile; pitcher allows elevated contact</t>
+          <t>neutral batted-ball profile; pitcher fly-ball pressure modest</t>
         </is>
       </c>
       <c r="AN14" t="inlineStr">
         <is>
-          <t>4.8</t>
+          <t>6.66</t>
         </is>
       </c>
       <c r="AO14" t="inlineStr">
         <is>
-          <t>33.75</t>
+          <t>36.88</t>
         </is>
       </c>
       <c r="AP14" t="inlineStr">
         <is>
-          <t>87.73</t>
+          <t>88.22</t>
         </is>
       </c>
       <c r="AQ14" t="inlineStr">
         <is>
-          <t>98.1545</t>
+          <t>99.4273</t>
         </is>
       </c>
       <c r="AR14" t="inlineStr">
         <is>
-          <t>0.3355</t>
+          <t>0.4244</t>
         </is>
       </c>
       <c r="AS14" t="inlineStr">
         <is>
-          <t>0.1063</t>
+          <t>0.1557</t>
         </is>
       </c>
       <c r="AT14" t="inlineStr">
         <is>
-          <t>0.3022</t>
+          <t>0.3127</t>
         </is>
       </c>
       <c r="AU14" t="inlineStr">
         <is>
-          <t>71.39</t>
+          <t>72.48</t>
         </is>
       </c>
       <c r="AV14" t="inlineStr">
         <is>
-          <t>17.39</t>
+          <t>21.39</t>
         </is>
       </c>
       <c r="AW14" t="inlineStr">
         <is>
-          <t>31.54</t>
+          <t>36.35</t>
         </is>
       </c>
       <c r="AX14" t="inlineStr">
         <is>
-          <t>21.95</t>
+          <t>19.1</t>
         </is>
       </c>
       <c r="AY14" t="inlineStr">
         <is>
-          <t>5.4</t>
+          <t>11.6</t>
         </is>
       </c>
       <c r="AZ14" t="inlineStr">
         <is>
-          <t>0.0876</t>
+          <t>0.1533</t>
         </is>
       </c>
       <c r="BA14" t="inlineStr">
         <is>
-          <t>7.69</t>
+          <t>11.04</t>
         </is>
       </c>
       <c r="BB14" t="inlineStr">
         <is>
-          <t>37.81</t>
+          <t>43.01</t>
         </is>
       </c>
       <c r="BC14" t="inlineStr">
         <is>
-          <t>89.39</t>
+          <t>90.71</t>
         </is>
       </c>
       <c r="BD14" t="inlineStr">
         <is>
-          <t>0.3942</t>
+          <t>0.5055</t>
         </is>
       </c>
       <c r="BE14" t="inlineStr">
         <is>
-          <t>0.1474</t>
+          <t>0.2189</t>
         </is>
       </c>
       <c r="BF14" t="inlineStr">
         <is>
-          <t>37.54</t>
+          <t>29.3</t>
         </is>
       </c>
       <c r="BG14" t="inlineStr">
@@ -10089,12 +10021,12 @@
       </c>
       <c r="B16" t="inlineStr">
         <is>
-          <t>673237</t>
+          <t>664774</t>
         </is>
       </c>
       <c r="C16" t="inlineStr">
         <is>
-          <t>Yainer Diaz</t>
+          <t>LaMonte Wade Jr.</t>
         </is>
       </c>
       <c r="D16" t="inlineStr">
@@ -10119,7 +10051,7 @@
       </c>
       <c r="H16" t="inlineStr">
         <is>
-          <t>8</t>
+          <t>9</t>
         </is>
       </c>
       <c r="I16" t="inlineStr">
@@ -10138,7 +10070,7 @@
         </is>
       </c>
       <c r="L16" t="n">
-        <v>45.3</v>
+        <v>43.7</v>
       </c>
       <c r="M16" t="inlineStr">
         <is>
@@ -10152,11 +10084,11 @@
       </c>
       <c r="O16" t="inlineStr">
         <is>
-          <t>Projected Lineup</t>
+          <t>Platoon Edge</t>
         </is>
       </c>
       <c r="P16" t="n">
-        <v>28.6</v>
+        <v>13.9</v>
       </c>
       <c r="Q16" t="n">
         <v>62.7</v>
@@ -10165,49 +10097,45 @@
         <v>58.1</v>
       </c>
       <c r="S16" t="n">
-        <v>47.9</v>
+        <v>44.8</v>
       </c>
       <c r="T16" t="n">
-        <v>50</v>
+        <v>80</v>
       </c>
       <c r="U16" t="n">
-        <v>17.7</v>
+        <v>38.3</v>
       </c>
       <c r="V16" t="inlineStr">
         <is>
+          <t>Yes</t>
+        </is>
+      </c>
+      <c r="W16" t="inlineStr">
+        <is>
+          <t>Yes</t>
+        </is>
+      </c>
+      <c r="X16" t="inlineStr">
+        <is>
+          <t>9</t>
+        </is>
+      </c>
+      <c r="Y16" t="inlineStr">
+        <is>
+          <t>Yes</t>
+        </is>
+      </c>
+      <c r="Z16" t="inlineStr">
+        <is>
           <t>No</t>
         </is>
       </c>
-      <c r="W16" t="inlineStr">
-        <is>
-          <t>No</t>
-        </is>
-      </c>
-      <c r="X16" t="inlineStr">
-        <is>
-          <t>8</t>
-        </is>
-      </c>
-      <c r="Y16" t="inlineStr">
-        <is>
-          <t>Yes</t>
-        </is>
-      </c>
-      <c r="Z16" t="inlineStr">
-        <is>
-          <t>Yes</t>
-        </is>
-      </c>
       <c r="AA16" t="inlineStr">
         <is>
-          <t>RotoWire projected lineup; MLB probable pitchers</t>
-        </is>
-      </c>
-      <c r="AB16" t="inlineStr">
-        <is>
-          <t>lineup projected / unconfirmed</t>
-        </is>
-      </c>
+          <t>MLB Stats API; RotoWire</t>
+        </is>
+      </c>
+      <c r="AB16" t="inlineStr"/>
       <c r="AC16" t="inlineStr">
         <is>
           <t>H:2026/2025 P:2026/2025</t>
@@ -10227,12 +10155,12 @@
       </c>
       <c r="AH16" t="inlineStr">
         <is>
-          <t>5</t>
+          <t>6</t>
         </is>
       </c>
       <c r="AI16" t="inlineStr">
         <is>
-          <t>21</t>
+          <t>16</t>
         </is>
       </c>
       <c r="AJ16" t="inlineStr">
@@ -10242,12 +10170,12 @@
       </c>
       <c r="AK16" t="inlineStr">
         <is>
-          <t>Last 7 games: 5/21, 0 HR</t>
+          <t>Contact streak: 6/16 over last 7 games</t>
         </is>
       </c>
       <c r="AL16" t="inlineStr">
         <is>
-          <t>same-side matchup; pitcher baseline 11.0% barrel, 14.6 HR allowed</t>
+          <t>platoon edge; pitcher baseline 11.0% barrel, 14.6 HR allowed</t>
         </is>
       </c>
       <c r="AM16" t="inlineStr">
@@ -10257,67 +10185,67 @@
       </c>
       <c r="AN16" t="inlineStr">
         <is>
-          <t>6.66</t>
+          <t>4.01</t>
         </is>
       </c>
       <c r="AO16" t="inlineStr">
         <is>
-          <t>36.88</t>
+          <t>32.01</t>
         </is>
       </c>
       <c r="AP16" t="inlineStr">
         <is>
-          <t>88.22</t>
+          <t>86.76</t>
         </is>
       </c>
       <c r="AQ16" t="inlineStr">
         <is>
-          <t>99.4273</t>
+          <t>97.8228</t>
         </is>
       </c>
       <c r="AR16" t="inlineStr">
         <is>
-          <t>0.4244</t>
+          <t>0.2958</t>
         </is>
       </c>
       <c r="AS16" t="inlineStr">
         <is>
-          <t>0.1557</t>
+          <t>0.1013</t>
         </is>
       </c>
       <c r="AT16" t="inlineStr">
         <is>
-          <t>0.3127</t>
+          <t>0.2838</t>
         </is>
       </c>
       <c r="AU16" t="inlineStr">
         <is>
-          <t>72.48</t>
+          <t>70.98</t>
         </is>
       </c>
       <c r="AV16" t="inlineStr">
         <is>
-          <t>21.39</t>
+          <t>8.78</t>
         </is>
       </c>
       <c r="AW16" t="inlineStr">
         <is>
-          <t>36.35</t>
+          <t>38.82</t>
         </is>
       </c>
       <c r="AX16" t="inlineStr">
         <is>
-          <t>19.1</t>
+          <t>27.47</t>
         </is>
       </c>
       <c r="AY16" t="inlineStr">
         <is>
-          <t>11.6</t>
+          <t>2.0</t>
         </is>
       </c>
       <c r="AZ16" t="inlineStr">
         <is>
-          <t>0.1533</t>
+          <t>0.1248</t>
         </is>
       </c>
       <c r="BA16" t="inlineStr">

--- a/outputs/daily/hr_rankings_2026-08-09_remaining.xlsx
+++ b/outputs/daily/hr_rankings_2026-08-09_remaining.xlsx
@@ -784,7 +784,7 @@
         </is>
       </c>
       <c r="L2" t="n">
-        <v>74</v>
+        <v>72.5</v>
       </c>
       <c r="M2" t="inlineStr">
         <is>
@@ -808,7 +808,7 @@
         <v>62.7</v>
       </c>
       <c r="R2" t="n">
-        <v>58.1</v>
+        <v>48.1</v>
       </c>
       <c r="S2" t="n">
         <v>100</v>
@@ -994,12 +994,12 @@
       </c>
       <c r="BG2" t="inlineStr">
         <is>
-          <t>Out To RF</t>
+          <t>L To R</t>
         </is>
       </c>
       <c r="BH2" t="inlineStr">
         <is>
-          <t>75</t>
+          <t>80</t>
         </is>
       </c>
       <c r="BI2" t="inlineStr">
@@ -1064,7 +1064,7 @@
         </is>
       </c>
       <c r="L3" t="n">
-        <v>59</v>
+        <v>57.5</v>
       </c>
       <c r="M3" t="inlineStr">
         <is>
@@ -1088,7 +1088,7 @@
         <v>62.7</v>
       </c>
       <c r="R3" t="n">
-        <v>58.1</v>
+        <v>48.1</v>
       </c>
       <c r="S3" t="n">
         <v>86.40000000000001</v>
@@ -1274,12 +1274,12 @@
       </c>
       <c r="BG3" t="inlineStr">
         <is>
-          <t>Out To RF</t>
+          <t>L To R</t>
         </is>
       </c>
       <c r="BH3" t="inlineStr">
         <is>
-          <t>75</t>
+          <t>80</t>
         </is>
       </c>
       <c r="BI3" t="inlineStr">
@@ -1344,7 +1344,7 @@
         </is>
       </c>
       <c r="L4" t="n">
-        <v>56.9</v>
+        <v>55.4</v>
       </c>
       <c r="M4" t="inlineStr">
         <is>
@@ -1368,7 +1368,7 @@
         <v>39</v>
       </c>
       <c r="R4" t="n">
-        <v>58.1</v>
+        <v>48.1</v>
       </c>
       <c r="S4" t="n">
         <v>86.40000000000001</v>
@@ -1554,12 +1554,12 @@
       </c>
       <c r="BG4" t="inlineStr">
         <is>
-          <t>Out To RF</t>
+          <t>L To R</t>
         </is>
       </c>
       <c r="BH4" t="inlineStr">
         <is>
-          <t>75</t>
+          <t>80</t>
         </is>
       </c>
       <c r="BI4" t="inlineStr">
@@ -1624,7 +1624,7 @@
         </is>
       </c>
       <c r="L5" t="n">
-        <v>55.2</v>
+        <v>53.7</v>
       </c>
       <c r="M5" t="inlineStr">
         <is>
@@ -1648,7 +1648,7 @@
         <v>39</v>
       </c>
       <c r="R5" t="n">
-        <v>58.1</v>
+        <v>48.1</v>
       </c>
       <c r="S5" t="n">
         <v>93.2</v>
@@ -1834,12 +1834,12 @@
       </c>
       <c r="BG5" t="inlineStr">
         <is>
-          <t>Out To RF</t>
+          <t>L To R</t>
         </is>
       </c>
       <c r="BH5" t="inlineStr">
         <is>
-          <t>75</t>
+          <t>80</t>
         </is>
       </c>
       <c r="BI5" t="inlineStr">
@@ -1904,7 +1904,7 @@
         </is>
       </c>
       <c r="L6" t="n">
-        <v>54.8</v>
+        <v>53.3</v>
       </c>
       <c r="M6" t="inlineStr">
         <is>
@@ -1928,7 +1928,7 @@
         <v>62.7</v>
       </c>
       <c r="R6" t="n">
-        <v>58.1</v>
+        <v>48.1</v>
       </c>
       <c r="S6" t="n">
         <v>76.2</v>
@@ -2114,12 +2114,12 @@
       </c>
       <c r="BG6" t="inlineStr">
         <is>
-          <t>Out To RF</t>
+          <t>L To R</t>
         </is>
       </c>
       <c r="BH6" t="inlineStr">
         <is>
-          <t>75</t>
+          <t>80</t>
         </is>
       </c>
       <c r="BI6" t="inlineStr">
@@ -2184,7 +2184,7 @@
         </is>
       </c>
       <c r="L7" t="n">
-        <v>53.3</v>
+        <v>51.8</v>
       </c>
       <c r="M7" t="inlineStr">
         <is>
@@ -2208,7 +2208,7 @@
         <v>39</v>
       </c>
       <c r="R7" t="n">
-        <v>58.1</v>
+        <v>48.1</v>
       </c>
       <c r="S7" t="n">
         <v>96.59999999999999</v>
@@ -2394,12 +2394,12 @@
       </c>
       <c r="BG7" t="inlineStr">
         <is>
-          <t>Out To RF</t>
+          <t>L To R</t>
         </is>
       </c>
       <c r="BH7" t="inlineStr">
         <is>
-          <t>75</t>
+          <t>80</t>
         </is>
       </c>
       <c r="BI7" t="inlineStr">
@@ -2464,7 +2464,7 @@
         </is>
       </c>
       <c r="L8" t="n">
-        <v>52.9</v>
+        <v>51.4</v>
       </c>
       <c r="M8" t="inlineStr">
         <is>
@@ -2488,7 +2488,7 @@
         <v>62.7</v>
       </c>
       <c r="R8" t="n">
-        <v>58.1</v>
+        <v>48.1</v>
       </c>
       <c r="S8" t="n">
         <v>93.2</v>
@@ -2674,12 +2674,12 @@
       </c>
       <c r="BG8" t="inlineStr">
         <is>
-          <t>Out To RF</t>
+          <t>L To R</t>
         </is>
       </c>
       <c r="BH8" t="inlineStr">
         <is>
-          <t>75</t>
+          <t>80</t>
         </is>
       </c>
       <c r="BI8" t="inlineStr">
@@ -2744,7 +2744,7 @@
         </is>
       </c>
       <c r="L9" t="n">
-        <v>51.4</v>
+        <v>49.9</v>
       </c>
       <c r="M9" t="inlineStr">
         <is>
@@ -2768,7 +2768,7 @@
         <v>39</v>
       </c>
       <c r="R9" t="n">
-        <v>58.1</v>
+        <v>48.1</v>
       </c>
       <c r="S9" t="n">
         <v>94.90000000000001</v>
@@ -2954,12 +2954,12 @@
       </c>
       <c r="BG9" t="inlineStr">
         <is>
-          <t>Out To RF</t>
+          <t>L To R</t>
         </is>
       </c>
       <c r="BH9" t="inlineStr">
         <is>
-          <t>75</t>
+          <t>80</t>
         </is>
       </c>
       <c r="BI9" t="inlineStr">
@@ -3024,7 +3024,7 @@
         </is>
       </c>
       <c r="L10" t="n">
-        <v>51.1</v>
+        <v>49.6</v>
       </c>
       <c r="M10" t="inlineStr">
         <is>
@@ -3048,7 +3048,7 @@
         <v>62.7</v>
       </c>
       <c r="R10" t="n">
-        <v>58.1</v>
+        <v>48.1</v>
       </c>
       <c r="S10" t="n">
         <v>64.3</v>
@@ -3234,12 +3234,12 @@
       </c>
       <c r="BG10" t="inlineStr">
         <is>
-          <t>Out To RF</t>
+          <t>L To R</t>
         </is>
       </c>
       <c r="BH10" t="inlineStr">
         <is>
-          <t>75</t>
+          <t>80</t>
         </is>
       </c>
       <c r="BI10" t="inlineStr">
@@ -3304,7 +3304,7 @@
         </is>
       </c>
       <c r="L11" t="n">
-        <v>49.7</v>
+        <v>48.2</v>
       </c>
       <c r="M11" t="inlineStr">
         <is>
@@ -3328,7 +3328,7 @@
         <v>62.7</v>
       </c>
       <c r="R11" t="n">
-        <v>58.1</v>
+        <v>48.1</v>
       </c>
       <c r="S11" t="n">
         <v>94.90000000000001</v>
@@ -3514,12 +3514,12 @@
       </c>
       <c r="BG11" t="inlineStr">
         <is>
-          <t>Out To RF</t>
+          <t>L To R</t>
         </is>
       </c>
       <c r="BH11" t="inlineStr">
         <is>
-          <t>75</t>
+          <t>80</t>
         </is>
       </c>
       <c r="BI11" t="inlineStr">
@@ -3584,7 +3584,7 @@
         </is>
       </c>
       <c r="L12" t="n">
-        <v>48.6</v>
+        <v>47.1</v>
       </c>
       <c r="M12" t="inlineStr">
         <is>
@@ -3608,7 +3608,7 @@
         <v>62.7</v>
       </c>
       <c r="R12" t="n">
-        <v>58.1</v>
+        <v>48.1</v>
       </c>
       <c r="S12" t="n">
         <v>96.59999999999999</v>
@@ -3794,12 +3794,12 @@
       </c>
       <c r="BG12" t="inlineStr">
         <is>
-          <t>Out To RF</t>
+          <t>L To R</t>
         </is>
       </c>
       <c r="BH12" t="inlineStr">
         <is>
-          <t>75</t>
+          <t>80</t>
         </is>
       </c>
       <c r="BI12" t="inlineStr">
@@ -3864,7 +3864,7 @@
         </is>
       </c>
       <c r="L13" t="n">
-        <v>46.1</v>
+        <v>44.6</v>
       </c>
       <c r="M13" t="inlineStr">
         <is>
@@ -3888,7 +3888,7 @@
         <v>39</v>
       </c>
       <c r="R13" t="n">
-        <v>58.1</v>
+        <v>48.1</v>
       </c>
       <c r="S13" t="n">
         <v>100</v>
@@ -4074,12 +4074,12 @@
       </c>
       <c r="BG13" t="inlineStr">
         <is>
-          <t>Out To RF</t>
+          <t>L To R</t>
         </is>
       </c>
       <c r="BH13" t="inlineStr">
         <is>
-          <t>75</t>
+          <t>80</t>
         </is>
       </c>
       <c r="BI13" t="inlineStr">
@@ -4144,7 +4144,7 @@
         </is>
       </c>
       <c r="L14" t="n">
-        <v>45.9</v>
+        <v>44.4</v>
       </c>
       <c r="M14" t="inlineStr">
         <is>
@@ -4168,7 +4168,7 @@
         <v>62.7</v>
       </c>
       <c r="R14" t="n">
-        <v>58.1</v>
+        <v>48.1</v>
       </c>
       <c r="S14" t="n">
         <v>52.4</v>
@@ -4354,12 +4354,12 @@
       </c>
       <c r="BG14" t="inlineStr">
         <is>
-          <t>Out To RF</t>
+          <t>L To R</t>
         </is>
       </c>
       <c r="BH14" t="inlineStr">
         <is>
-          <t>75</t>
+          <t>80</t>
         </is>
       </c>
       <c r="BI14" t="inlineStr">
@@ -4424,7 +4424,7 @@
         </is>
       </c>
       <c r="L15" t="n">
-        <v>45.6</v>
+        <v>44.1</v>
       </c>
       <c r="M15" t="inlineStr">
         <is>
@@ -4448,7 +4448,7 @@
         <v>39</v>
       </c>
       <c r="R15" t="n">
-        <v>58.1</v>
+        <v>48.1</v>
       </c>
       <c r="S15" t="n">
         <v>64.3</v>
@@ -4634,12 +4634,12 @@
       </c>
       <c r="BG15" t="inlineStr">
         <is>
-          <t>Out To RF</t>
+          <t>L To R</t>
         </is>
       </c>
       <c r="BH15" t="inlineStr">
         <is>
-          <t>75</t>
+          <t>80</t>
         </is>
       </c>
       <c r="BI15" t="inlineStr">
@@ -4704,7 +4704,7 @@
         </is>
       </c>
       <c r="L16" t="n">
-        <v>43.7</v>
+        <v>42.2</v>
       </c>
       <c r="M16" t="inlineStr">
         <is>
@@ -4728,7 +4728,7 @@
         <v>62.7</v>
       </c>
       <c r="R16" t="n">
-        <v>58.1</v>
+        <v>48.1</v>
       </c>
       <c r="S16" t="n">
         <v>44.8</v>
@@ -4914,12 +4914,12 @@
       </c>
       <c r="BG16" t="inlineStr">
         <is>
-          <t>Out To RF</t>
+          <t>L To R</t>
         </is>
       </c>
       <c r="BH16" t="inlineStr">
         <is>
-          <t>75</t>
+          <t>80</t>
         </is>
       </c>
       <c r="BI16" t="inlineStr">
@@ -4984,7 +4984,7 @@
         </is>
       </c>
       <c r="L17" t="n">
-        <v>41.7</v>
+        <v>40.2</v>
       </c>
       <c r="M17" t="inlineStr">
         <is>
@@ -5008,7 +5008,7 @@
         <v>38.6</v>
       </c>
       <c r="R17" t="n">
-        <v>58.1</v>
+        <v>48.1</v>
       </c>
       <c r="S17" t="n">
         <v>76.2</v>
@@ -5194,12 +5194,12 @@
       </c>
       <c r="BG17" t="inlineStr">
         <is>
-          <t>Out To RF</t>
+          <t>L To R</t>
         </is>
       </c>
       <c r="BH17" t="inlineStr">
         <is>
-          <t>75</t>
+          <t>80</t>
         </is>
       </c>
       <c r="BI17" t="inlineStr">
@@ -5264,7 +5264,7 @@
         </is>
       </c>
       <c r="L18" t="n">
-        <v>39.6</v>
+        <v>38.1</v>
       </c>
       <c r="M18" t="inlineStr">
         <is>
@@ -5288,7 +5288,7 @@
         <v>39</v>
       </c>
       <c r="R18" t="n">
-        <v>58.1</v>
+        <v>48.1</v>
       </c>
       <c r="S18" t="n">
         <v>52.4</v>
@@ -5474,12 +5474,12 @@
       </c>
       <c r="BG18" t="inlineStr">
         <is>
-          <t>Out To RF</t>
+          <t>L To R</t>
         </is>
       </c>
       <c r="BH18" t="inlineStr">
         <is>
-          <t>75</t>
+          <t>80</t>
         </is>
       </c>
       <c r="BI18" t="inlineStr">
@@ -5544,7 +5544,7 @@
         </is>
       </c>
       <c r="L19" t="n">
-        <v>36.7</v>
+        <v>35.2</v>
       </c>
       <c r="M19" t="inlineStr">
         <is>
@@ -5568,7 +5568,7 @@
         <v>39</v>
       </c>
       <c r="R19" t="n">
-        <v>58.1</v>
+        <v>48.1</v>
       </c>
       <c r="S19" t="n">
         <v>44.8</v>
@@ -5754,12 +5754,12 @@
       </c>
       <c r="BG19" t="inlineStr">
         <is>
-          <t>Out To RF</t>
+          <t>L To R</t>
         </is>
       </c>
       <c r="BH19" t="inlineStr">
         <is>
-          <t>75</t>
+          <t>80</t>
         </is>
       </c>
       <c r="BI19" t="inlineStr">
@@ -6150,7 +6150,7 @@
         </is>
       </c>
       <c r="L2" t="n">
-        <v>74</v>
+        <v>72.5</v>
       </c>
       <c r="M2" t="inlineStr">
         <is>
@@ -6174,7 +6174,7 @@
         <v>62.7</v>
       </c>
       <c r="R2" t="n">
-        <v>58.1</v>
+        <v>48.1</v>
       </c>
       <c r="S2" t="n">
         <v>100</v>
@@ -6360,12 +6360,12 @@
       </c>
       <c r="BG2" t="inlineStr">
         <is>
-          <t>Out To RF</t>
+          <t>L To R</t>
         </is>
       </c>
       <c r="BH2" t="inlineStr">
         <is>
-          <t>75</t>
+          <t>80</t>
         </is>
       </c>
       <c r="BI2" t="inlineStr">
@@ -6430,7 +6430,7 @@
         </is>
       </c>
       <c r="L3" t="n">
-        <v>59</v>
+        <v>57.5</v>
       </c>
       <c r="M3" t="inlineStr">
         <is>
@@ -6454,7 +6454,7 @@
         <v>62.7</v>
       </c>
       <c r="R3" t="n">
-        <v>58.1</v>
+        <v>48.1</v>
       </c>
       <c r="S3" t="n">
         <v>86.40000000000001</v>
@@ -6640,12 +6640,12 @@
       </c>
       <c r="BG3" t="inlineStr">
         <is>
-          <t>Out To RF</t>
+          <t>L To R</t>
         </is>
       </c>
       <c r="BH3" t="inlineStr">
         <is>
-          <t>75</t>
+          <t>80</t>
         </is>
       </c>
       <c r="BI3" t="inlineStr">
@@ -6710,7 +6710,7 @@
         </is>
       </c>
       <c r="L4" t="n">
-        <v>56.9</v>
+        <v>55.4</v>
       </c>
       <c r="M4" t="inlineStr">
         <is>
@@ -6734,7 +6734,7 @@
         <v>39</v>
       </c>
       <c r="R4" t="n">
-        <v>58.1</v>
+        <v>48.1</v>
       </c>
       <c r="S4" t="n">
         <v>86.40000000000001</v>
@@ -6920,12 +6920,12 @@
       </c>
       <c r="BG4" t="inlineStr">
         <is>
-          <t>Out To RF</t>
+          <t>L To R</t>
         </is>
       </c>
       <c r="BH4" t="inlineStr">
         <is>
-          <t>75</t>
+          <t>80</t>
         </is>
       </c>
       <c r="BI4" t="inlineStr">
@@ -6990,7 +6990,7 @@
         </is>
       </c>
       <c r="L5" t="n">
-        <v>55.2</v>
+        <v>53.7</v>
       </c>
       <c r="M5" t="inlineStr">
         <is>
@@ -7014,7 +7014,7 @@
         <v>39</v>
       </c>
       <c r="R5" t="n">
-        <v>58.1</v>
+        <v>48.1</v>
       </c>
       <c r="S5" t="n">
         <v>93.2</v>
@@ -7200,12 +7200,12 @@
       </c>
       <c r="BG5" t="inlineStr">
         <is>
-          <t>Out To RF</t>
+          <t>L To R</t>
         </is>
       </c>
       <c r="BH5" t="inlineStr">
         <is>
-          <t>75</t>
+          <t>80</t>
         </is>
       </c>
       <c r="BI5" t="inlineStr">
@@ -7270,7 +7270,7 @@
         </is>
       </c>
       <c r="L6" t="n">
-        <v>54.8</v>
+        <v>53.3</v>
       </c>
       <c r="M6" t="inlineStr">
         <is>
@@ -7294,7 +7294,7 @@
         <v>62.7</v>
       </c>
       <c r="R6" t="n">
-        <v>58.1</v>
+        <v>48.1</v>
       </c>
       <c r="S6" t="n">
         <v>76.2</v>
@@ -7480,12 +7480,12 @@
       </c>
       <c r="BG6" t="inlineStr">
         <is>
-          <t>Out To RF</t>
+          <t>L To R</t>
         </is>
       </c>
       <c r="BH6" t="inlineStr">
         <is>
-          <t>75</t>
+          <t>80</t>
         </is>
       </c>
       <c r="BI6" t="inlineStr">
@@ -7550,7 +7550,7 @@
         </is>
       </c>
       <c r="L7" t="n">
-        <v>53.3</v>
+        <v>51.8</v>
       </c>
       <c r="M7" t="inlineStr">
         <is>
@@ -7574,7 +7574,7 @@
         <v>39</v>
       </c>
       <c r="R7" t="n">
-        <v>58.1</v>
+        <v>48.1</v>
       </c>
       <c r="S7" t="n">
         <v>96.59999999999999</v>
@@ -7760,12 +7760,12 @@
       </c>
       <c r="BG7" t="inlineStr">
         <is>
-          <t>Out To RF</t>
+          <t>L To R</t>
         </is>
       </c>
       <c r="BH7" t="inlineStr">
         <is>
-          <t>75</t>
+          <t>80</t>
         </is>
       </c>
       <c r="BI7" t="inlineStr">
@@ -7830,7 +7830,7 @@
         </is>
       </c>
       <c r="L8" t="n">
-        <v>52.9</v>
+        <v>51.4</v>
       </c>
       <c r="M8" t="inlineStr">
         <is>
@@ -7854,7 +7854,7 @@
         <v>62.7</v>
       </c>
       <c r="R8" t="n">
-        <v>58.1</v>
+        <v>48.1</v>
       </c>
       <c r="S8" t="n">
         <v>93.2</v>
@@ -8040,12 +8040,12 @@
       </c>
       <c r="BG8" t="inlineStr">
         <is>
-          <t>Out To RF</t>
+          <t>L To R</t>
         </is>
       </c>
       <c r="BH8" t="inlineStr">
         <is>
-          <t>75</t>
+          <t>80</t>
         </is>
       </c>
       <c r="BI8" t="inlineStr">
@@ -8110,7 +8110,7 @@
         </is>
       </c>
       <c r="L9" t="n">
-        <v>51.4</v>
+        <v>49.9</v>
       </c>
       <c r="M9" t="inlineStr">
         <is>
@@ -8134,7 +8134,7 @@
         <v>39</v>
       </c>
       <c r="R9" t="n">
-        <v>58.1</v>
+        <v>48.1</v>
       </c>
       <c r="S9" t="n">
         <v>94.90000000000001</v>
@@ -8320,12 +8320,12 @@
       </c>
       <c r="BG9" t="inlineStr">
         <is>
-          <t>Out To RF</t>
+          <t>L To R</t>
         </is>
       </c>
       <c r="BH9" t="inlineStr">
         <is>
-          <t>75</t>
+          <t>80</t>
         </is>
       </c>
       <c r="BI9" t="inlineStr">
@@ -8390,7 +8390,7 @@
         </is>
       </c>
       <c r="L10" t="n">
-        <v>51.1</v>
+        <v>49.6</v>
       </c>
       <c r="M10" t="inlineStr">
         <is>
@@ -8414,7 +8414,7 @@
         <v>62.7</v>
       </c>
       <c r="R10" t="n">
-        <v>58.1</v>
+        <v>48.1</v>
       </c>
       <c r="S10" t="n">
         <v>64.3</v>
@@ -8600,12 +8600,12 @@
       </c>
       <c r="BG10" t="inlineStr">
         <is>
-          <t>Out To RF</t>
+          <t>L To R</t>
         </is>
       </c>
       <c r="BH10" t="inlineStr">
         <is>
-          <t>75</t>
+          <t>80</t>
         </is>
       </c>
       <c r="BI10" t="inlineStr">
@@ -8670,7 +8670,7 @@
         </is>
       </c>
       <c r="L11" t="n">
-        <v>49.7</v>
+        <v>48.2</v>
       </c>
       <c r="M11" t="inlineStr">
         <is>
@@ -8694,7 +8694,7 @@
         <v>62.7</v>
       </c>
       <c r="R11" t="n">
-        <v>58.1</v>
+        <v>48.1</v>
       </c>
       <c r="S11" t="n">
         <v>94.90000000000001</v>
@@ -8880,12 +8880,12 @@
       </c>
       <c r="BG11" t="inlineStr">
         <is>
-          <t>Out To RF</t>
+          <t>L To R</t>
         </is>
       </c>
       <c r="BH11" t="inlineStr">
         <is>
-          <t>75</t>
+          <t>80</t>
         </is>
       </c>
       <c r="BI11" t="inlineStr">
@@ -8950,7 +8950,7 @@
         </is>
       </c>
       <c r="L12" t="n">
-        <v>48.6</v>
+        <v>47.1</v>
       </c>
       <c r="M12" t="inlineStr">
         <is>
@@ -8974,7 +8974,7 @@
         <v>62.7</v>
       </c>
       <c r="R12" t="n">
-        <v>58.1</v>
+        <v>48.1</v>
       </c>
       <c r="S12" t="n">
         <v>96.59999999999999</v>
@@ -9160,12 +9160,12 @@
       </c>
       <c r="BG12" t="inlineStr">
         <is>
-          <t>Out To RF</t>
+          <t>L To R</t>
         </is>
       </c>
       <c r="BH12" t="inlineStr">
         <is>
-          <t>75</t>
+          <t>80</t>
         </is>
       </c>
       <c r="BI12" t="inlineStr">
@@ -9230,7 +9230,7 @@
         </is>
       </c>
       <c r="L13" t="n">
-        <v>46.1</v>
+        <v>44.6</v>
       </c>
       <c r="M13" t="inlineStr">
         <is>
@@ -9254,7 +9254,7 @@
         <v>39</v>
       </c>
       <c r="R13" t="n">
-        <v>58.1</v>
+        <v>48.1</v>
       </c>
       <c r="S13" t="n">
         <v>100</v>
@@ -9440,12 +9440,12 @@
       </c>
       <c r="BG13" t="inlineStr">
         <is>
-          <t>Out To RF</t>
+          <t>L To R</t>
         </is>
       </c>
       <c r="BH13" t="inlineStr">
         <is>
-          <t>75</t>
+          <t>80</t>
         </is>
       </c>
       <c r="BI13" t="inlineStr">
@@ -9510,7 +9510,7 @@
         </is>
       </c>
       <c r="L14" t="n">
-        <v>45.9</v>
+        <v>44.4</v>
       </c>
       <c r="M14" t="inlineStr">
         <is>
@@ -9534,7 +9534,7 @@
         <v>62.7</v>
       </c>
       <c r="R14" t="n">
-        <v>58.1</v>
+        <v>48.1</v>
       </c>
       <c r="S14" t="n">
         <v>52.4</v>
@@ -9720,12 +9720,12 @@
       </c>
       <c r="BG14" t="inlineStr">
         <is>
-          <t>Out To RF</t>
+          <t>L To R</t>
         </is>
       </c>
       <c r="BH14" t="inlineStr">
         <is>
-          <t>75</t>
+          <t>80</t>
         </is>
       </c>
       <c r="BI14" t="inlineStr">
@@ -9790,7 +9790,7 @@
         </is>
       </c>
       <c r="L15" t="n">
-        <v>45.6</v>
+        <v>44.1</v>
       </c>
       <c r="M15" t="inlineStr">
         <is>
@@ -9814,7 +9814,7 @@
         <v>39</v>
       </c>
       <c r="R15" t="n">
-        <v>58.1</v>
+        <v>48.1</v>
       </c>
       <c r="S15" t="n">
         <v>64.3</v>
@@ -10000,12 +10000,12 @@
       </c>
       <c r="BG15" t="inlineStr">
         <is>
-          <t>Out To RF</t>
+          <t>L To R</t>
         </is>
       </c>
       <c r="BH15" t="inlineStr">
         <is>
-          <t>75</t>
+          <t>80</t>
         </is>
       </c>
       <c r="BI15" t="inlineStr">
@@ -10070,7 +10070,7 @@
         </is>
       </c>
       <c r="L16" t="n">
-        <v>43.7</v>
+        <v>42.2</v>
       </c>
       <c r="M16" t="inlineStr">
         <is>
@@ -10094,7 +10094,7 @@
         <v>62.7</v>
       </c>
       <c r="R16" t="n">
-        <v>58.1</v>
+        <v>48.1</v>
       </c>
       <c r="S16" t="n">
         <v>44.8</v>
@@ -10280,12 +10280,12 @@
       </c>
       <c r="BG16" t="inlineStr">
         <is>
-          <t>Out To RF</t>
+          <t>L To R</t>
         </is>
       </c>
       <c r="BH16" t="inlineStr">
         <is>
-          <t>75</t>
+          <t>80</t>
         </is>
       </c>
       <c r="BI16" t="inlineStr">
@@ -10350,7 +10350,7 @@
         </is>
       </c>
       <c r="L17" t="n">
-        <v>41.7</v>
+        <v>40.2</v>
       </c>
       <c r="M17" t="inlineStr">
         <is>
@@ -10374,7 +10374,7 @@
         <v>38.6</v>
       </c>
       <c r="R17" t="n">
-        <v>58.1</v>
+        <v>48.1</v>
       </c>
       <c r="S17" t="n">
         <v>76.2</v>
@@ -10560,12 +10560,12 @@
       </c>
       <c r="BG17" t="inlineStr">
         <is>
-          <t>Out To RF</t>
+          <t>L To R</t>
         </is>
       </c>
       <c r="BH17" t="inlineStr">
         <is>
-          <t>75</t>
+          <t>80</t>
         </is>
       </c>
       <c r="BI17" t="inlineStr">
@@ -10630,7 +10630,7 @@
         </is>
       </c>
       <c r="L18" t="n">
-        <v>39.6</v>
+        <v>38.1</v>
       </c>
       <c r="M18" t="inlineStr">
         <is>
@@ -10654,7 +10654,7 @@
         <v>39</v>
       </c>
       <c r="R18" t="n">
-        <v>58.1</v>
+        <v>48.1</v>
       </c>
       <c r="S18" t="n">
         <v>52.4</v>
@@ -10840,12 +10840,12 @@
       </c>
       <c r="BG18" t="inlineStr">
         <is>
-          <t>Out To RF</t>
+          <t>L To R</t>
         </is>
       </c>
       <c r="BH18" t="inlineStr">
         <is>
-          <t>75</t>
+          <t>80</t>
         </is>
       </c>
       <c r="BI18" t="inlineStr">
@@ -10910,7 +10910,7 @@
         </is>
       </c>
       <c r="L19" t="n">
-        <v>36.7</v>
+        <v>35.2</v>
       </c>
       <c r="M19" t="inlineStr">
         <is>
@@ -10934,7 +10934,7 @@
         <v>39</v>
       </c>
       <c r="R19" t="n">
-        <v>58.1</v>
+        <v>48.1</v>
       </c>
       <c r="S19" t="n">
         <v>44.8</v>
@@ -11120,12 +11120,12 @@
       </c>
       <c r="BG19" t="inlineStr">
         <is>
-          <t>Out To RF</t>
+          <t>L To R</t>
         </is>
       </c>
       <c r="BH19" t="inlineStr">
         <is>
-          <t>75</t>
+          <t>80</t>
         </is>
       </c>
       <c r="BI19" t="inlineStr">

--- a/outputs/daily/hr_rankings_2026-08-09_remaining.xlsx
+++ b/outputs/daily/hr_rankings_2026-08-09_remaining.xlsx
@@ -760,7 +760,7 @@
       </c>
       <c r="G2" t="inlineStr">
         <is>
-          <t>Pre-Game</t>
+          <t>Warmup</t>
         </is>
       </c>
       <c r="H2" t="inlineStr">
@@ -784,7 +784,7 @@
         </is>
       </c>
       <c r="L2" t="n">
-        <v>72.5</v>
+        <v>72.40000000000001</v>
       </c>
       <c r="M2" t="inlineStr">
         <is>
@@ -808,7 +808,7 @@
         <v>62.7</v>
       </c>
       <c r="R2" t="n">
-        <v>48.1</v>
+        <v>47.6</v>
       </c>
       <c r="S2" t="n">
         <v>100</v>
@@ -999,7 +999,7 @@
       </c>
       <c r="BH2" t="inlineStr">
         <is>
-          <t>80</t>
+          <t>79</t>
         </is>
       </c>
       <c r="BI2" t="inlineStr">
@@ -1040,7 +1040,7 @@
       </c>
       <c r="G3" t="inlineStr">
         <is>
-          <t>Pre-Game</t>
+          <t>Warmup</t>
         </is>
       </c>
       <c r="H3" t="inlineStr">
@@ -1064,7 +1064,7 @@
         </is>
       </c>
       <c r="L3" t="n">
-        <v>57.5</v>
+        <v>57.4</v>
       </c>
       <c r="M3" t="inlineStr">
         <is>
@@ -1088,7 +1088,7 @@
         <v>62.7</v>
       </c>
       <c r="R3" t="n">
-        <v>48.1</v>
+        <v>47.6</v>
       </c>
       <c r="S3" t="n">
         <v>86.40000000000001</v>
@@ -1279,7 +1279,7 @@
       </c>
       <c r="BH3" t="inlineStr">
         <is>
-          <t>80</t>
+          <t>79</t>
         </is>
       </c>
       <c r="BI3" t="inlineStr">
@@ -1320,7 +1320,7 @@
       </c>
       <c r="G4" t="inlineStr">
         <is>
-          <t>Pre-Game</t>
+          <t>Warmup</t>
         </is>
       </c>
       <c r="H4" t="inlineStr">
@@ -1344,7 +1344,7 @@
         </is>
       </c>
       <c r="L4" t="n">
-        <v>55.4</v>
+        <v>55.3</v>
       </c>
       <c r="M4" t="inlineStr">
         <is>
@@ -1368,7 +1368,7 @@
         <v>39</v>
       </c>
       <c r="R4" t="n">
-        <v>48.1</v>
+        <v>47.6</v>
       </c>
       <c r="S4" t="n">
         <v>86.40000000000001</v>
@@ -1559,7 +1559,7 @@
       </c>
       <c r="BH4" t="inlineStr">
         <is>
-          <t>80</t>
+          <t>79</t>
         </is>
       </c>
       <c r="BI4" t="inlineStr">
@@ -1600,7 +1600,7 @@
       </c>
       <c r="G5" t="inlineStr">
         <is>
-          <t>Pre-Game</t>
+          <t>Warmup</t>
         </is>
       </c>
       <c r="H5" t="inlineStr">
@@ -1648,7 +1648,7 @@
         <v>39</v>
       </c>
       <c r="R5" t="n">
-        <v>48.1</v>
+        <v>47.6</v>
       </c>
       <c r="S5" t="n">
         <v>93.2</v>
@@ -1839,7 +1839,7 @@
       </c>
       <c r="BH5" t="inlineStr">
         <is>
-          <t>80</t>
+          <t>79</t>
         </is>
       </c>
       <c r="BI5" t="inlineStr">
@@ -1880,7 +1880,7 @@
       </c>
       <c r="G6" t="inlineStr">
         <is>
-          <t>Pre-Game</t>
+          <t>Warmup</t>
         </is>
       </c>
       <c r="H6" t="inlineStr">
@@ -1904,7 +1904,7 @@
         </is>
       </c>
       <c r="L6" t="n">
-        <v>53.3</v>
+        <v>53.2</v>
       </c>
       <c r="M6" t="inlineStr">
         <is>
@@ -1928,7 +1928,7 @@
         <v>62.7</v>
       </c>
       <c r="R6" t="n">
-        <v>48.1</v>
+        <v>47.6</v>
       </c>
       <c r="S6" t="n">
         <v>76.2</v>
@@ -2119,7 +2119,7 @@
       </c>
       <c r="BH6" t="inlineStr">
         <is>
-          <t>80</t>
+          <t>79</t>
         </is>
       </c>
       <c r="BI6" t="inlineStr">
@@ -2160,7 +2160,7 @@
       </c>
       <c r="G7" t="inlineStr">
         <is>
-          <t>Pre-Game</t>
+          <t>Warmup</t>
         </is>
       </c>
       <c r="H7" t="inlineStr">
@@ -2184,7 +2184,7 @@
         </is>
       </c>
       <c r="L7" t="n">
-        <v>51.8</v>
+        <v>51.7</v>
       </c>
       <c r="M7" t="inlineStr">
         <is>
@@ -2208,7 +2208,7 @@
         <v>39</v>
       </c>
       <c r="R7" t="n">
-        <v>48.1</v>
+        <v>47.6</v>
       </c>
       <c r="S7" t="n">
         <v>96.59999999999999</v>
@@ -2399,7 +2399,7 @@
       </c>
       <c r="BH7" t="inlineStr">
         <is>
-          <t>80</t>
+          <t>79</t>
         </is>
       </c>
       <c r="BI7" t="inlineStr">
@@ -2440,7 +2440,7 @@
       </c>
       <c r="G8" t="inlineStr">
         <is>
-          <t>Pre-Game</t>
+          <t>Warmup</t>
         </is>
       </c>
       <c r="H8" t="inlineStr">
@@ -2464,7 +2464,7 @@
         </is>
       </c>
       <c r="L8" t="n">
-        <v>51.4</v>
+        <v>51.3</v>
       </c>
       <c r="M8" t="inlineStr">
         <is>
@@ -2488,7 +2488,7 @@
         <v>62.7</v>
       </c>
       <c r="R8" t="n">
-        <v>48.1</v>
+        <v>47.6</v>
       </c>
       <c r="S8" t="n">
         <v>93.2</v>
@@ -2679,7 +2679,7 @@
       </c>
       <c r="BH8" t="inlineStr">
         <is>
-          <t>80</t>
+          <t>79</t>
         </is>
       </c>
       <c r="BI8" t="inlineStr">
@@ -2720,7 +2720,7 @@
       </c>
       <c r="G9" t="inlineStr">
         <is>
-          <t>Pre-Game</t>
+          <t>Warmup</t>
         </is>
       </c>
       <c r="H9" t="inlineStr">
@@ -2744,7 +2744,7 @@
         </is>
       </c>
       <c r="L9" t="n">
-        <v>49.9</v>
+        <v>49.8</v>
       </c>
       <c r="M9" t="inlineStr">
         <is>
@@ -2768,7 +2768,7 @@
         <v>39</v>
       </c>
       <c r="R9" t="n">
-        <v>48.1</v>
+        <v>47.6</v>
       </c>
       <c r="S9" t="n">
         <v>94.90000000000001</v>
@@ -2959,7 +2959,7 @@
       </c>
       <c r="BH9" t="inlineStr">
         <is>
-          <t>80</t>
+          <t>79</t>
         </is>
       </c>
       <c r="BI9" t="inlineStr">
@@ -3000,7 +3000,7 @@
       </c>
       <c r="G10" t="inlineStr">
         <is>
-          <t>Pre-Game</t>
+          <t>Warmup</t>
         </is>
       </c>
       <c r="H10" t="inlineStr">
@@ -3024,7 +3024,7 @@
         </is>
       </c>
       <c r="L10" t="n">
-        <v>49.6</v>
+        <v>49.5</v>
       </c>
       <c r="M10" t="inlineStr">
         <is>
@@ -3048,7 +3048,7 @@
         <v>62.7</v>
       </c>
       <c r="R10" t="n">
-        <v>48.1</v>
+        <v>47.6</v>
       </c>
       <c r="S10" t="n">
         <v>64.3</v>
@@ -3239,7 +3239,7 @@
       </c>
       <c r="BH10" t="inlineStr">
         <is>
-          <t>80</t>
+          <t>79</t>
         </is>
       </c>
       <c r="BI10" t="inlineStr">
@@ -3280,7 +3280,7 @@
       </c>
       <c r="G11" t="inlineStr">
         <is>
-          <t>Pre-Game</t>
+          <t>Warmup</t>
         </is>
       </c>
       <c r="H11" t="inlineStr">
@@ -3328,7 +3328,7 @@
         <v>62.7</v>
       </c>
       <c r="R11" t="n">
-        <v>48.1</v>
+        <v>47.6</v>
       </c>
       <c r="S11" t="n">
         <v>94.90000000000001</v>
@@ -3519,7 +3519,7 @@
       </c>
       <c r="BH11" t="inlineStr">
         <is>
-          <t>80</t>
+          <t>79</t>
         </is>
       </c>
       <c r="BI11" t="inlineStr">
@@ -3560,7 +3560,7 @@
       </c>
       <c r="G12" t="inlineStr">
         <is>
-          <t>Pre-Game</t>
+          <t>Warmup</t>
         </is>
       </c>
       <c r="H12" t="inlineStr">
@@ -3584,7 +3584,7 @@
         </is>
       </c>
       <c r="L12" t="n">
-        <v>47.1</v>
+        <v>47</v>
       </c>
       <c r="M12" t="inlineStr">
         <is>
@@ -3608,7 +3608,7 @@
         <v>62.7</v>
       </c>
       <c r="R12" t="n">
-        <v>48.1</v>
+        <v>47.6</v>
       </c>
       <c r="S12" t="n">
         <v>96.59999999999999</v>
@@ -3799,7 +3799,7 @@
       </c>
       <c r="BH12" t="inlineStr">
         <is>
-          <t>80</t>
+          <t>79</t>
         </is>
       </c>
       <c r="BI12" t="inlineStr">
@@ -3840,7 +3840,7 @@
       </c>
       <c r="G13" t="inlineStr">
         <is>
-          <t>Pre-Game</t>
+          <t>Warmup</t>
         </is>
       </c>
       <c r="H13" t="inlineStr">
@@ -3864,7 +3864,7 @@
         </is>
       </c>
       <c r="L13" t="n">
-        <v>44.6</v>
+        <v>44.5</v>
       </c>
       <c r="M13" t="inlineStr">
         <is>
@@ -3888,7 +3888,7 @@
         <v>39</v>
       </c>
       <c r="R13" t="n">
-        <v>48.1</v>
+        <v>47.6</v>
       </c>
       <c r="S13" t="n">
         <v>100</v>
@@ -4079,7 +4079,7 @@
       </c>
       <c r="BH13" t="inlineStr">
         <is>
-          <t>80</t>
+          <t>79</t>
         </is>
       </c>
       <c r="BI13" t="inlineStr">
@@ -4120,7 +4120,7 @@
       </c>
       <c r="G14" t="inlineStr">
         <is>
-          <t>Pre-Game</t>
+          <t>Warmup</t>
         </is>
       </c>
       <c r="H14" t="inlineStr">
@@ -4168,7 +4168,7 @@
         <v>62.7</v>
       </c>
       <c r="R14" t="n">
-        <v>48.1</v>
+        <v>47.6</v>
       </c>
       <c r="S14" t="n">
         <v>52.4</v>
@@ -4359,7 +4359,7 @@
       </c>
       <c r="BH14" t="inlineStr">
         <is>
-          <t>80</t>
+          <t>79</t>
         </is>
       </c>
       <c r="BI14" t="inlineStr">
@@ -4400,7 +4400,7 @@
       </c>
       <c r="G15" t="inlineStr">
         <is>
-          <t>Pre-Game</t>
+          <t>Warmup</t>
         </is>
       </c>
       <c r="H15" t="inlineStr">
@@ -4424,7 +4424,7 @@
         </is>
       </c>
       <c r="L15" t="n">
-        <v>44.1</v>
+        <v>44</v>
       </c>
       <c r="M15" t="inlineStr">
         <is>
@@ -4448,7 +4448,7 @@
         <v>39</v>
       </c>
       <c r="R15" t="n">
-        <v>48.1</v>
+        <v>47.6</v>
       </c>
       <c r="S15" t="n">
         <v>64.3</v>
@@ -4639,7 +4639,7 @@
       </c>
       <c r="BH15" t="inlineStr">
         <is>
-          <t>80</t>
+          <t>79</t>
         </is>
       </c>
       <c r="BI15" t="inlineStr">
@@ -4680,7 +4680,7 @@
       </c>
       <c r="G16" t="inlineStr">
         <is>
-          <t>Pre-Game</t>
+          <t>Warmup</t>
         </is>
       </c>
       <c r="H16" t="inlineStr">
@@ -4704,7 +4704,7 @@
         </is>
       </c>
       <c r="L16" t="n">
-        <v>42.2</v>
+        <v>42.1</v>
       </c>
       <c r="M16" t="inlineStr">
         <is>
@@ -4728,7 +4728,7 @@
         <v>62.7</v>
       </c>
       <c r="R16" t="n">
-        <v>48.1</v>
+        <v>47.6</v>
       </c>
       <c r="S16" t="n">
         <v>44.8</v>
@@ -4919,7 +4919,7 @@
       </c>
       <c r="BH16" t="inlineStr">
         <is>
-          <t>80</t>
+          <t>79</t>
         </is>
       </c>
       <c r="BI16" t="inlineStr">
@@ -4960,7 +4960,7 @@
       </c>
       <c r="G17" t="inlineStr">
         <is>
-          <t>Pre-Game</t>
+          <t>Warmup</t>
         </is>
       </c>
       <c r="H17" t="inlineStr">
@@ -4984,7 +4984,7 @@
         </is>
       </c>
       <c r="L17" t="n">
-        <v>40.2</v>
+        <v>40.1</v>
       </c>
       <c r="M17" t="inlineStr">
         <is>
@@ -5008,7 +5008,7 @@
         <v>38.6</v>
       </c>
       <c r="R17" t="n">
-        <v>48.1</v>
+        <v>47.6</v>
       </c>
       <c r="S17" t="n">
         <v>76.2</v>
@@ -5199,7 +5199,7 @@
       </c>
       <c r="BH17" t="inlineStr">
         <is>
-          <t>80</t>
+          <t>79</t>
         </is>
       </c>
       <c r="BI17" t="inlineStr">
@@ -5240,7 +5240,7 @@
       </c>
       <c r="G18" t="inlineStr">
         <is>
-          <t>Pre-Game</t>
+          <t>Warmup</t>
         </is>
       </c>
       <c r="H18" t="inlineStr">
@@ -5288,7 +5288,7 @@
         <v>39</v>
       </c>
       <c r="R18" t="n">
-        <v>48.1</v>
+        <v>47.6</v>
       </c>
       <c r="S18" t="n">
         <v>52.4</v>
@@ -5479,7 +5479,7 @@
       </c>
       <c r="BH18" t="inlineStr">
         <is>
-          <t>80</t>
+          <t>79</t>
         </is>
       </c>
       <c r="BI18" t="inlineStr">
@@ -5520,7 +5520,7 @@
       </c>
       <c r="G19" t="inlineStr">
         <is>
-          <t>Pre-Game</t>
+          <t>Warmup</t>
         </is>
       </c>
       <c r="H19" t="inlineStr">
@@ -5544,7 +5544,7 @@
         </is>
       </c>
       <c r="L19" t="n">
-        <v>35.2</v>
+        <v>35.1</v>
       </c>
       <c r="M19" t="inlineStr">
         <is>
@@ -5568,7 +5568,7 @@
         <v>39</v>
       </c>
       <c r="R19" t="n">
-        <v>48.1</v>
+        <v>47.6</v>
       </c>
       <c r="S19" t="n">
         <v>44.8</v>
@@ -5759,7 +5759,7 @@
       </c>
       <c r="BH19" t="inlineStr">
         <is>
-          <t>80</t>
+          <t>79</t>
         </is>
       </c>
       <c r="BI19" t="inlineStr">
@@ -6126,7 +6126,7 @@
       </c>
       <c r="G2" t="inlineStr">
         <is>
-          <t>Pre-Game</t>
+          <t>Warmup</t>
         </is>
       </c>
       <c r="H2" t="inlineStr">
@@ -6150,7 +6150,7 @@
         </is>
       </c>
       <c r="L2" t="n">
-        <v>72.5</v>
+        <v>72.40000000000001</v>
       </c>
       <c r="M2" t="inlineStr">
         <is>
@@ -6174,7 +6174,7 @@
         <v>62.7</v>
       </c>
       <c r="R2" t="n">
-        <v>48.1</v>
+        <v>47.6</v>
       </c>
       <c r="S2" t="n">
         <v>100</v>
@@ -6365,7 +6365,7 @@
       </c>
       <c r="BH2" t="inlineStr">
         <is>
-          <t>80</t>
+          <t>79</t>
         </is>
       </c>
       <c r="BI2" t="inlineStr">
@@ -6406,7 +6406,7 @@
       </c>
       <c r="G3" t="inlineStr">
         <is>
-          <t>Pre-Game</t>
+          <t>Warmup</t>
         </is>
       </c>
       <c r="H3" t="inlineStr">
@@ -6430,7 +6430,7 @@
         </is>
       </c>
       <c r="L3" t="n">
-        <v>57.5</v>
+        <v>57.4</v>
       </c>
       <c r="M3" t="inlineStr">
         <is>
@@ -6454,7 +6454,7 @@
         <v>62.7</v>
       </c>
       <c r="R3" t="n">
-        <v>48.1</v>
+        <v>47.6</v>
       </c>
       <c r="S3" t="n">
         <v>86.40000000000001</v>
@@ -6645,7 +6645,7 @@
       </c>
       <c r="BH3" t="inlineStr">
         <is>
-          <t>80</t>
+          <t>79</t>
         </is>
       </c>
       <c r="BI3" t="inlineStr">
@@ -6686,7 +6686,7 @@
       </c>
       <c r="G4" t="inlineStr">
         <is>
-          <t>Pre-Game</t>
+          <t>Warmup</t>
         </is>
       </c>
       <c r="H4" t="inlineStr">
@@ -6710,7 +6710,7 @@
         </is>
       </c>
       <c r="L4" t="n">
-        <v>55.4</v>
+        <v>55.3</v>
       </c>
       <c r="M4" t="inlineStr">
         <is>
@@ -6734,7 +6734,7 @@
         <v>39</v>
       </c>
       <c r="R4" t="n">
-        <v>48.1</v>
+        <v>47.6</v>
       </c>
       <c r="S4" t="n">
         <v>86.40000000000001</v>
@@ -6925,7 +6925,7 @@
       </c>
       <c r="BH4" t="inlineStr">
         <is>
-          <t>80</t>
+          <t>79</t>
         </is>
       </c>
       <c r="BI4" t="inlineStr">
@@ -6966,7 +6966,7 @@
       </c>
       <c r="G5" t="inlineStr">
         <is>
-          <t>Pre-Game</t>
+          <t>Warmup</t>
         </is>
       </c>
       <c r="H5" t="inlineStr">
@@ -7014,7 +7014,7 @@
         <v>39</v>
       </c>
       <c r="R5" t="n">
-        <v>48.1</v>
+        <v>47.6</v>
       </c>
       <c r="S5" t="n">
         <v>93.2</v>
@@ -7205,7 +7205,7 @@
       </c>
       <c r="BH5" t="inlineStr">
         <is>
-          <t>80</t>
+          <t>79</t>
         </is>
       </c>
       <c r="BI5" t="inlineStr">
@@ -7246,7 +7246,7 @@
       </c>
       <c r="G6" t="inlineStr">
         <is>
-          <t>Pre-Game</t>
+          <t>Warmup</t>
         </is>
       </c>
       <c r="H6" t="inlineStr">
@@ -7270,7 +7270,7 @@
         </is>
       </c>
       <c r="L6" t="n">
-        <v>53.3</v>
+        <v>53.2</v>
       </c>
       <c r="M6" t="inlineStr">
         <is>
@@ -7294,7 +7294,7 @@
         <v>62.7</v>
       </c>
       <c r="R6" t="n">
-        <v>48.1</v>
+        <v>47.6</v>
       </c>
       <c r="S6" t="n">
         <v>76.2</v>
@@ -7485,7 +7485,7 @@
       </c>
       <c r="BH6" t="inlineStr">
         <is>
-          <t>80</t>
+          <t>79</t>
         </is>
       </c>
       <c r="BI6" t="inlineStr">
@@ -7526,7 +7526,7 @@
       </c>
       <c r="G7" t="inlineStr">
         <is>
-          <t>Pre-Game</t>
+          <t>Warmup</t>
         </is>
       </c>
       <c r="H7" t="inlineStr">
@@ -7550,7 +7550,7 @@
         </is>
       </c>
       <c r="L7" t="n">
-        <v>51.8</v>
+        <v>51.7</v>
       </c>
       <c r="M7" t="inlineStr">
         <is>
@@ -7574,7 +7574,7 @@
         <v>39</v>
       </c>
       <c r="R7" t="n">
-        <v>48.1</v>
+        <v>47.6</v>
       </c>
       <c r="S7" t="n">
         <v>96.59999999999999</v>
@@ -7765,7 +7765,7 @@
       </c>
       <c r="BH7" t="inlineStr">
         <is>
-          <t>80</t>
+          <t>79</t>
         </is>
       </c>
       <c r="BI7" t="inlineStr">
@@ -7806,7 +7806,7 @@
       </c>
       <c r="G8" t="inlineStr">
         <is>
-          <t>Pre-Game</t>
+          <t>Warmup</t>
         </is>
       </c>
       <c r="H8" t="inlineStr">
@@ -7830,7 +7830,7 @@
         </is>
       </c>
       <c r="L8" t="n">
-        <v>51.4</v>
+        <v>51.3</v>
       </c>
       <c r="M8" t="inlineStr">
         <is>
@@ -7854,7 +7854,7 @@
         <v>62.7</v>
       </c>
       <c r="R8" t="n">
-        <v>48.1</v>
+        <v>47.6</v>
       </c>
       <c r="S8" t="n">
         <v>93.2</v>
@@ -8045,7 +8045,7 @@
       </c>
       <c r="BH8" t="inlineStr">
         <is>
-          <t>80</t>
+          <t>79</t>
         </is>
       </c>
       <c r="BI8" t="inlineStr">
@@ -8086,7 +8086,7 @@
       </c>
       <c r="G9" t="inlineStr">
         <is>
-          <t>Pre-Game</t>
+          <t>Warmup</t>
         </is>
       </c>
       <c r="H9" t="inlineStr">
@@ -8110,7 +8110,7 @@
         </is>
       </c>
       <c r="L9" t="n">
-        <v>49.9</v>
+        <v>49.8</v>
       </c>
       <c r="M9" t="inlineStr">
         <is>
@@ -8134,7 +8134,7 @@
         <v>39</v>
       </c>
       <c r="R9" t="n">
-        <v>48.1</v>
+        <v>47.6</v>
       </c>
       <c r="S9" t="n">
         <v>94.90000000000001</v>
@@ -8325,7 +8325,7 @@
       </c>
       <c r="BH9" t="inlineStr">
         <is>
-          <t>80</t>
+          <t>79</t>
         </is>
       </c>
       <c r="BI9" t="inlineStr">
@@ -8366,7 +8366,7 @@
       </c>
       <c r="G10" t="inlineStr">
         <is>
-          <t>Pre-Game</t>
+          <t>Warmup</t>
         </is>
       </c>
       <c r="H10" t="inlineStr">
@@ -8390,7 +8390,7 @@
         </is>
       </c>
       <c r="L10" t="n">
-        <v>49.6</v>
+        <v>49.5</v>
       </c>
       <c r="M10" t="inlineStr">
         <is>
@@ -8414,7 +8414,7 @@
         <v>62.7</v>
       </c>
       <c r="R10" t="n">
-        <v>48.1</v>
+        <v>47.6</v>
       </c>
       <c r="S10" t="n">
         <v>64.3</v>
@@ -8605,7 +8605,7 @@
       </c>
       <c r="BH10" t="inlineStr">
         <is>
-          <t>80</t>
+          <t>79</t>
         </is>
       </c>
       <c r="BI10" t="inlineStr">
@@ -8646,7 +8646,7 @@
       </c>
       <c r="G11" t="inlineStr">
         <is>
-          <t>Pre-Game</t>
+          <t>Warmup</t>
         </is>
       </c>
       <c r="H11" t="inlineStr">
@@ -8694,7 +8694,7 @@
         <v>62.7</v>
       </c>
       <c r="R11" t="n">
-        <v>48.1</v>
+        <v>47.6</v>
       </c>
       <c r="S11" t="n">
         <v>94.90000000000001</v>
@@ -8885,7 +8885,7 @@
       </c>
       <c r="BH11" t="inlineStr">
         <is>
-          <t>80</t>
+          <t>79</t>
         </is>
       </c>
       <c r="BI11" t="inlineStr">
@@ -8926,7 +8926,7 @@
       </c>
       <c r="G12" t="inlineStr">
         <is>
-          <t>Pre-Game</t>
+          <t>Warmup</t>
         </is>
       </c>
       <c r="H12" t="inlineStr">
@@ -8950,7 +8950,7 @@
         </is>
       </c>
       <c r="L12" t="n">
-        <v>47.1</v>
+        <v>47</v>
       </c>
       <c r="M12" t="inlineStr">
         <is>
@@ -8974,7 +8974,7 @@
         <v>62.7</v>
       </c>
       <c r="R12" t="n">
-        <v>48.1</v>
+        <v>47.6</v>
       </c>
       <c r="S12" t="n">
         <v>96.59999999999999</v>
@@ -9165,7 +9165,7 @@
       </c>
       <c r="BH12" t="inlineStr">
         <is>
-          <t>80</t>
+          <t>79</t>
         </is>
       </c>
       <c r="BI12" t="inlineStr">
@@ -9206,7 +9206,7 @@
       </c>
       <c r="G13" t="inlineStr">
         <is>
-          <t>Pre-Game</t>
+          <t>Warmup</t>
         </is>
       </c>
       <c r="H13" t="inlineStr">
@@ -9230,7 +9230,7 @@
         </is>
       </c>
       <c r="L13" t="n">
-        <v>44.6</v>
+        <v>44.5</v>
       </c>
       <c r="M13" t="inlineStr">
         <is>
@@ -9254,7 +9254,7 @@
         <v>39</v>
       </c>
       <c r="R13" t="n">
-        <v>48.1</v>
+        <v>47.6</v>
       </c>
       <c r="S13" t="n">
         <v>100</v>
@@ -9445,7 +9445,7 @@
       </c>
       <c r="BH13" t="inlineStr">
         <is>
-          <t>80</t>
+          <t>79</t>
         </is>
       </c>
       <c r="BI13" t="inlineStr">
@@ -9486,7 +9486,7 @@
       </c>
       <c r="G14" t="inlineStr">
         <is>
-          <t>Pre-Game</t>
+          <t>Warmup</t>
         </is>
       </c>
       <c r="H14" t="inlineStr">
@@ -9534,7 +9534,7 @@
         <v>62.7</v>
       </c>
       <c r="R14" t="n">
-        <v>48.1</v>
+        <v>47.6</v>
       </c>
       <c r="S14" t="n">
         <v>52.4</v>
@@ -9725,7 +9725,7 @@
       </c>
       <c r="BH14" t="inlineStr">
         <is>
-          <t>80</t>
+          <t>79</t>
         </is>
       </c>
       <c r="BI14" t="inlineStr">
@@ -9766,7 +9766,7 @@
       </c>
       <c r="G15" t="inlineStr">
         <is>
-          <t>Pre-Game</t>
+          <t>Warmup</t>
         </is>
       </c>
       <c r="H15" t="inlineStr">
@@ -9790,7 +9790,7 @@
         </is>
       </c>
       <c r="L15" t="n">
-        <v>44.1</v>
+        <v>44</v>
       </c>
       <c r="M15" t="inlineStr">
         <is>
@@ -9814,7 +9814,7 @@
         <v>39</v>
       </c>
       <c r="R15" t="n">
-        <v>48.1</v>
+        <v>47.6</v>
       </c>
       <c r="S15" t="n">
         <v>64.3</v>
@@ -10005,7 +10005,7 @@
       </c>
       <c r="BH15" t="inlineStr">
         <is>
-          <t>80</t>
+          <t>79</t>
         </is>
       </c>
       <c r="BI15" t="inlineStr">
@@ -10046,7 +10046,7 @@
       </c>
       <c r="G16" t="inlineStr">
         <is>
-          <t>Pre-Game</t>
+          <t>Warmup</t>
         </is>
       </c>
       <c r="H16" t="inlineStr">
@@ -10070,7 +10070,7 @@
         </is>
       </c>
       <c r="L16" t="n">
-        <v>42.2</v>
+        <v>42.1</v>
       </c>
       <c r="M16" t="inlineStr">
         <is>
@@ -10094,7 +10094,7 @@
         <v>62.7</v>
       </c>
       <c r="R16" t="n">
-        <v>48.1</v>
+        <v>47.6</v>
       </c>
       <c r="S16" t="n">
         <v>44.8</v>
@@ -10285,7 +10285,7 @@
       </c>
       <c r="BH16" t="inlineStr">
         <is>
-          <t>80</t>
+          <t>79</t>
         </is>
       </c>
       <c r="BI16" t="inlineStr">
@@ -10326,7 +10326,7 @@
       </c>
       <c r="G17" t="inlineStr">
         <is>
-          <t>Pre-Game</t>
+          <t>Warmup</t>
         </is>
       </c>
       <c r="H17" t="inlineStr">
@@ -10350,7 +10350,7 @@
         </is>
       </c>
       <c r="L17" t="n">
-        <v>40.2</v>
+        <v>40.1</v>
       </c>
       <c r="M17" t="inlineStr">
         <is>
@@ -10374,7 +10374,7 @@
         <v>38.6</v>
       </c>
       <c r="R17" t="n">
-        <v>48.1</v>
+        <v>47.6</v>
       </c>
       <c r="S17" t="n">
         <v>76.2</v>
@@ -10565,7 +10565,7 @@
       </c>
       <c r="BH17" t="inlineStr">
         <is>
-          <t>80</t>
+          <t>79</t>
         </is>
       </c>
       <c r="BI17" t="inlineStr">
@@ -10606,7 +10606,7 @@
       </c>
       <c r="G18" t="inlineStr">
         <is>
-          <t>Pre-Game</t>
+          <t>Warmup</t>
         </is>
       </c>
       <c r="H18" t="inlineStr">
@@ -10654,7 +10654,7 @@
         <v>39</v>
       </c>
       <c r="R18" t="n">
-        <v>48.1</v>
+        <v>47.6</v>
       </c>
       <c r="S18" t="n">
         <v>52.4</v>
@@ -10845,7 +10845,7 @@
       </c>
       <c r="BH18" t="inlineStr">
         <is>
-          <t>80</t>
+          <t>79</t>
         </is>
       </c>
       <c r="BI18" t="inlineStr">
@@ -10886,7 +10886,7 @@
       </c>
       <c r="G19" t="inlineStr">
         <is>
-          <t>Pre-Game</t>
+          <t>Warmup</t>
         </is>
       </c>
       <c r="H19" t="inlineStr">
@@ -10910,7 +10910,7 @@
         </is>
       </c>
       <c r="L19" t="n">
-        <v>35.2</v>
+        <v>35.1</v>
       </c>
       <c r="M19" t="inlineStr">
         <is>
@@ -10934,7 +10934,7 @@
         <v>39</v>
       </c>
       <c r="R19" t="n">
-        <v>48.1</v>
+        <v>47.6</v>
       </c>
       <c r="S19" t="n">
         <v>44.8</v>
@@ -11125,7 +11125,7 @@
       </c>
       <c r="BH19" t="inlineStr">
         <is>
-          <t>80</t>
+          <t>79</t>
         </is>
       </c>
       <c r="BI19" t="inlineStr">
